--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121468979</v>
+        <v>121469004</v>
       </c>
       <c r="B2" t="n">
         <v>78604</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486282</v>
+        <v>486442</v>
       </c>
       <c r="R2" t="n">
-        <v>6829704</v>
+        <v>6829128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468961</v>
+        <v>121469045</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>78249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486376</v>
+        <v>486365</v>
       </c>
       <c r="R3" t="n">
-        <v>6829237</v>
+        <v>6829215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468976</v>
+        <v>121468927</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486293</v>
+        <v>486283</v>
       </c>
       <c r="R4" t="n">
-        <v>6829631</v>
+        <v>6829532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468974</v>
+        <v>121468987</v>
       </c>
       <c r="B5" t="n">
         <v>78604</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486301</v>
+        <v>486271</v>
       </c>
       <c r="R5" t="n">
-        <v>6829606</v>
+        <v>6829568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121469045</v>
+        <v>121468938</v>
       </c>
       <c r="B6" t="n">
-        <v>78249</v>
+        <v>78638</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486365</v>
+        <v>486329</v>
       </c>
       <c r="R6" t="n">
-        <v>6829215</v>
+        <v>6829484</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468939</v>
+        <v>121468958</v>
       </c>
       <c r="B7" t="n">
-        <v>79193</v>
+        <v>80561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486265</v>
+        <v>486278</v>
       </c>
       <c r="R7" t="n">
-        <v>6829735</v>
+        <v>6829675</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121469012</v>
+        <v>121468996</v>
       </c>
       <c r="B8" t="n">
         <v>78604</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486315</v>
+        <v>486242</v>
       </c>
       <c r="R8" t="n">
-        <v>6829368</v>
+        <v>6829317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468982</v>
+        <v>121468968</v>
       </c>
       <c r="B9" t="n">
         <v>78604</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486213</v>
+        <v>486325</v>
       </c>
       <c r="R9" t="n">
-        <v>6829765</v>
+        <v>6829578</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469010</v>
+        <v>121468918</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486366</v>
+        <v>486321</v>
       </c>
       <c r="R10" t="n">
-        <v>6829228</v>
+        <v>6829248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468958</v>
+        <v>121469009</v>
       </c>
       <c r="B11" t="n">
-        <v>80561</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486278</v>
+        <v>486396</v>
       </c>
       <c r="R11" t="n">
-        <v>6829675</v>
+        <v>6829190</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469044</v>
+        <v>121468966</v>
       </c>
       <c r="B12" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486236</v>
+        <v>486335</v>
       </c>
       <c r="R12" t="n">
-        <v>6829512</v>
+        <v>6829590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469028</v>
+        <v>121468935</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486375</v>
+        <v>486323</v>
       </c>
       <c r="R13" t="n">
-        <v>6829566</v>
+        <v>6829408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469017</v>
+        <v>121468995</v>
       </c>
       <c r="B14" t="n">
         <v>78604</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486335</v>
+        <v>486256</v>
       </c>
       <c r="R14" t="n">
-        <v>6829435</v>
+        <v>6829523</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468973</v>
+        <v>121469046</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486298</v>
+        <v>486324</v>
       </c>
       <c r="R15" t="n">
-        <v>6829599</v>
+        <v>6829398</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469021</v>
+        <v>121468978</v>
       </c>
       <c r="B16" t="n">
         <v>78604</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486328</v>
+        <v>486279</v>
       </c>
       <c r="R16" t="n">
-        <v>6829486</v>
+        <v>6829687</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469047</v>
+        <v>121468946</v>
       </c>
       <c r="B17" t="n">
-        <v>77536</v>
+        <v>57504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,34 +2221,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486258</v>
+        <v>486392</v>
       </c>
       <c r="R17" t="n">
-        <v>6829343</v>
+        <v>6829119</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2319,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468999</v>
+        <v>121468983</v>
       </c>
       <c r="B18" t="n">
         <v>78604</v>
@@ -2347,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486352</v>
+        <v>486213</v>
       </c>
       <c r="R18" t="n">
-        <v>6829165</v>
+        <v>6829683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469001</v>
+        <v>121468929</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2437,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486374</v>
+        <v>486309</v>
       </c>
       <c r="R19" t="n">
-        <v>6829123</v>
+        <v>6829581</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121468967</v>
+        <v>121468922</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486329</v>
+        <v>486376</v>
       </c>
       <c r="R20" t="n">
-        <v>6829590</v>
+        <v>6829237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468998</v>
+        <v>121468943</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486366</v>
+        <v>486250</v>
       </c>
       <c r="R21" t="n">
-        <v>6829176</v>
+        <v>6829400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468917</v>
+        <v>121469010</v>
       </c>
       <c r="B22" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2743,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486305</v>
+        <v>486366</v>
       </c>
       <c r="R22" t="n">
-        <v>6829222</v>
+        <v>6829228</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468922</v>
+        <v>121468954</v>
       </c>
       <c r="B23" t="n">
-        <v>79222</v>
+        <v>8432</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,38 +2841,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486376</v>
+        <v>486213</v>
       </c>
       <c r="R23" t="n">
-        <v>6829237</v>
+        <v>6829562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,6 +2922,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2919,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469008</v>
+        <v>121468934</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2957,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486416</v>
+        <v>486318</v>
       </c>
       <c r="R24" t="n">
-        <v>6829192</v>
+        <v>6829376</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3043,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468968</v>
+        <v>121468977</v>
       </c>
       <c r="B25" t="n">
         <v>78604</v>
@@ -3061,10 +3083,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486325</v>
+        <v>486269</v>
       </c>
       <c r="R25" t="n">
-        <v>6829578</v>
+        <v>6829656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3145,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468984</v>
+        <v>121468967</v>
       </c>
       <c r="B26" t="n">
         <v>78604</v>
@@ -3163,10 +3185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486202</v>
+        <v>486329</v>
       </c>
       <c r="R26" t="n">
-        <v>6829676</v>
+        <v>6829590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3247,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469043</v>
+        <v>121468955</v>
       </c>
       <c r="B27" t="n">
-        <v>78249</v>
+        <v>78341</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3263,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3287,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486291</v>
+        <v>486321</v>
       </c>
       <c r="R27" t="n">
-        <v>6829537</v>
+        <v>6829248</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3349,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469025</v>
+        <v>121469006</v>
       </c>
       <c r="B28" t="n">
         <v>78604</v>
@@ -3367,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486353</v>
+        <v>486437</v>
       </c>
       <c r="R28" t="n">
-        <v>6829553</v>
+        <v>6829175</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3451,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469018</v>
+        <v>121469024</v>
       </c>
       <c r="B29" t="n">
         <v>78604</v>
@@ -3469,10 +3491,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486306</v>
+        <v>486351</v>
       </c>
       <c r="R29" t="n">
-        <v>6829450</v>
+        <v>6829541</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3553,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468985</v>
+        <v>121469035</v>
       </c>
       <c r="B30" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3569,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3593,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486183</v>
+        <v>486278</v>
       </c>
       <c r="R30" t="n">
-        <v>6829659</v>
+        <v>6829675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468959</v>
+        <v>121469043</v>
       </c>
       <c r="B31" t="n">
-        <v>80561</v>
+        <v>78249</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3671,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3695,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486437</v>
+        <v>486291</v>
       </c>
       <c r="R31" t="n">
-        <v>6829174</v>
+        <v>6829537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3757,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468970</v>
+        <v>121469027</v>
       </c>
       <c r="B32" t="n">
         <v>78604</v>
@@ -3775,10 +3797,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486315</v>
+        <v>486370</v>
       </c>
       <c r="R32" t="n">
-        <v>6829584</v>
+        <v>6829559</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,7 +3859,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469024</v>
+        <v>121469018</v>
       </c>
       <c r="B33" t="n">
         <v>78604</v>
@@ -3877,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486351</v>
+        <v>486306</v>
       </c>
       <c r="R33" t="n">
-        <v>6829541</v>
+        <v>6829450</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3961,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468940</v>
+        <v>121468931</v>
       </c>
       <c r="B34" t="n">
-        <v>79193</v>
+        <v>78638</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3977,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +4001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486207</v>
+        <v>486202</v>
       </c>
       <c r="R34" t="n">
-        <v>6829684</v>
+        <v>6829676</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469007</v>
+        <v>121468937</v>
       </c>
       <c r="B35" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4079,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4103,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486432</v>
+        <v>486310</v>
       </c>
       <c r="R35" t="n">
-        <v>6829183</v>
+        <v>6829463</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468933</v>
+        <v>121469028</v>
       </c>
       <c r="B36" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4181,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4205,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486317</v>
+        <v>486375</v>
       </c>
       <c r="R36" t="n">
-        <v>6829373</v>
+        <v>6829566</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4267,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469015</v>
+        <v>121468928</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4283,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4307,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486323</v>
+        <v>486313</v>
       </c>
       <c r="R37" t="n">
-        <v>6829408</v>
+        <v>6829466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4369,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468955</v>
+        <v>121469012</v>
       </c>
       <c r="B38" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4385,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4409,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486321</v>
+        <v>486315</v>
       </c>
       <c r="R38" t="n">
-        <v>6829248</v>
+        <v>6829368</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4471,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468946</v>
+        <v>121468992</v>
       </c>
       <c r="B39" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,46 +4487,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486392</v>
+        <v>486291</v>
       </c>
       <c r="R39" t="n">
-        <v>6829119</v>
+        <v>6829537</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4665,10 +4675,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468915</v>
+        <v>121468940</v>
       </c>
       <c r="B41" t="n">
-        <v>79222</v>
+        <v>79193</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4681,21 +4691,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4705,10 +4715,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486223</v>
+        <v>486207</v>
       </c>
       <c r="R41" t="n">
-        <v>6829705</v>
+        <v>6829684</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4767,10 +4777,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468934</v>
+        <v>121469005</v>
       </c>
       <c r="B42" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4783,21 +4793,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4807,10 +4817,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486318</v>
+        <v>486438</v>
       </c>
       <c r="R42" t="n">
-        <v>6829376</v>
+        <v>6829156</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4869,10 +4879,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468993</v>
+        <v>121468921</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4885,21 +4895,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4909,10 +4919,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486272</v>
+        <v>486365</v>
       </c>
       <c r="R43" t="n">
-        <v>6829527</v>
+        <v>6829163</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,10 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469036</v>
+        <v>121468932</v>
       </c>
       <c r="B44" t="n">
-        <v>78249</v>
+        <v>78638</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4987,21 +4997,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,7 +5024,7 @@
         <v>486261</v>
       </c>
       <c r="R44" t="n">
-        <v>6829744</v>
+        <v>6829525</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5073,7 +5083,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469020</v>
+        <v>121469019</v>
       </c>
       <c r="B45" t="n">
         <v>78604</v>
@@ -5113,10 +5123,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486312</v>
+        <v>486309</v>
       </c>
       <c r="R45" t="n">
-        <v>6829467</v>
+        <v>6829468</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5175,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468928</v>
+        <v>121469015</v>
       </c>
       <c r="B46" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5191,21 +5201,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5215,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486313</v>
+        <v>486323</v>
       </c>
       <c r="R46" t="n">
-        <v>6829466</v>
+        <v>6829408</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,10 +5287,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468932</v>
+        <v>121468984</v>
       </c>
       <c r="B47" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5293,21 +5303,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5317,10 +5327,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486261</v>
+        <v>486202</v>
       </c>
       <c r="R47" t="n">
-        <v>6829525</v>
+        <v>6829676</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,7 +5389,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468975</v>
+        <v>121469025</v>
       </c>
       <c r="B48" t="n">
         <v>78604</v>
@@ -5419,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486298</v>
+        <v>486353</v>
       </c>
       <c r="R48" t="n">
-        <v>6829621</v>
+        <v>6829553</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5481,7 +5491,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468971</v>
+        <v>121468970</v>
       </c>
       <c r="B49" t="n">
         <v>78604</v>
@@ -5521,10 +5531,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486309</v>
+        <v>486315</v>
       </c>
       <c r="R49" t="n">
-        <v>6829581</v>
+        <v>6829584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5583,7 +5593,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469005</v>
+        <v>121468986</v>
       </c>
       <c r="B50" t="n">
         <v>78604</v>
@@ -5623,10 +5633,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486438</v>
+        <v>486259</v>
       </c>
       <c r="R50" t="n">
-        <v>6829156</v>
+        <v>6829565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5685,10 +5695,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469046</v>
+        <v>121468971</v>
       </c>
       <c r="B51" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5701,21 +5711,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5725,10 +5735,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486324</v>
+        <v>486309</v>
       </c>
       <c r="R51" t="n">
-        <v>6829398</v>
+        <v>6829581</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5787,7 +5797,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468942</v>
+        <v>121468944</v>
       </c>
       <c r="B52" t="n">
         <v>79193</v>
@@ -5827,10 +5837,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486165</v>
+        <v>486255</v>
       </c>
       <c r="R52" t="n">
-        <v>6829633</v>
+        <v>6829395</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5889,10 +5899,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468986</v>
+        <v>121469034</v>
       </c>
       <c r="B53" t="n">
-        <v>78604</v>
+        <v>88031</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5905,21 +5915,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5929,10 +5939,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486259</v>
+        <v>486298</v>
       </c>
       <c r="R53" t="n">
-        <v>6829565</v>
+        <v>6829599</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5991,7 +6001,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469009</v>
+        <v>121468993</v>
       </c>
       <c r="B54" t="n">
         <v>78604</v>
@@ -6031,10 +6041,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486396</v>
+        <v>486272</v>
       </c>
       <c r="R54" t="n">
-        <v>6829190</v>
+        <v>6829527</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6093,7 +6103,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121468992</v>
+        <v>121469021</v>
       </c>
       <c r="B55" t="n">
         <v>78604</v>
@@ -6133,10 +6143,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486291</v>
+        <v>486328</v>
       </c>
       <c r="R55" t="n">
-        <v>6829537</v>
+        <v>6829486</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,10 +6205,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468941</v>
+        <v>121469047</v>
       </c>
       <c r="B56" t="n">
-        <v>79193</v>
+        <v>77536</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6211,21 +6221,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6235,10 +6245,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486174</v>
+        <v>486258</v>
       </c>
       <c r="R56" t="n">
-        <v>6829641</v>
+        <v>6829343</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6297,10 +6307,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468936</v>
+        <v>121468939</v>
       </c>
       <c r="B57" t="n">
-        <v>78638</v>
+        <v>79193</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6313,21 +6323,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6337,10 +6347,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486335</v>
+        <v>486265</v>
       </c>
       <c r="R57" t="n">
-        <v>6829435</v>
+        <v>6829735</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6399,7 +6409,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468969</v>
+        <v>121468999</v>
       </c>
       <c r="B58" t="n">
         <v>78604</v>
@@ -6439,10 +6449,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486317</v>
+        <v>486352</v>
       </c>
       <c r="R58" t="n">
-        <v>6829572</v>
+        <v>6829165</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6603,10 +6613,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468944</v>
+        <v>121468933</v>
       </c>
       <c r="B60" t="n">
-        <v>79193</v>
+        <v>78638</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6619,21 +6629,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6643,10 +6653,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486255</v>
+        <v>486317</v>
       </c>
       <c r="R60" t="n">
-        <v>6829395</v>
+        <v>6829373</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6705,10 +6715,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468921</v>
+        <v>121468994</v>
       </c>
       <c r="B61" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6721,21 +6731,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6745,10 +6755,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486365</v>
+        <v>486261</v>
       </c>
       <c r="R61" t="n">
-        <v>6829163</v>
+        <v>6829525</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6807,7 +6817,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469023</v>
+        <v>121468998</v>
       </c>
       <c r="B62" t="n">
         <v>78604</v>
@@ -6847,10 +6857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486362</v>
+        <v>486366</v>
       </c>
       <c r="R62" t="n">
-        <v>6829525</v>
+        <v>6829176</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6909,10 +6919,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468996</v>
+        <v>121468917</v>
       </c>
       <c r="B63" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6925,21 +6935,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6949,10 +6959,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486242</v>
+        <v>486305</v>
       </c>
       <c r="R63" t="n">
-        <v>6829317</v>
+        <v>6829222</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,7 +7021,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468994</v>
+        <v>121468975</v>
       </c>
       <c r="B64" t="n">
         <v>78604</v>
@@ -7051,10 +7061,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486261</v>
+        <v>486298</v>
       </c>
       <c r="R64" t="n">
-        <v>6829525</v>
+        <v>6829621</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7215,10 +7225,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468914</v>
+        <v>121468969</v>
       </c>
       <c r="B66" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7231,21 +7241,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7317,10 +7327,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468954</v>
+        <v>121469001</v>
       </c>
       <c r="B67" t="n">
-        <v>8432</v>
+        <v>78604</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7329,47 +7339,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486213</v>
+        <v>486374</v>
       </c>
       <c r="R67" t="n">
-        <v>6829562</v>
+        <v>6829123</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7410,7 +7411,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7429,7 +7429,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468929</v>
+        <v>121468936</v>
       </c>
       <c r="B68" t="n">
         <v>78638</v>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486309</v>
+        <v>486335</v>
       </c>
       <c r="R68" t="n">
-        <v>6829581</v>
+        <v>6829435</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468966</v>
+        <v>121468914</v>
       </c>
       <c r="B69" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7547,21 +7547,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486335</v>
+        <v>486317</v>
       </c>
       <c r="R69" t="n">
-        <v>6829590</v>
+        <v>6829572</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7633,10 +7633,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469034</v>
+        <v>121468985</v>
       </c>
       <c r="B70" t="n">
-        <v>88031</v>
+        <v>78604</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7649,21 +7649,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486298</v>
+        <v>486183</v>
       </c>
       <c r="R70" t="n">
-        <v>6829599</v>
+        <v>6829659</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7735,10 +7735,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468931</v>
+        <v>121468976</v>
       </c>
       <c r="B71" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7751,21 +7751,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486202</v>
+        <v>486293</v>
       </c>
       <c r="R71" t="n">
-        <v>6829676</v>
+        <v>6829631</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468977</v>
+        <v>121469036</v>
       </c>
       <c r="B72" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7853,21 +7853,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486269</v>
+        <v>486261</v>
       </c>
       <c r="R72" t="n">
-        <v>6829656</v>
+        <v>6829744</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468927</v>
+        <v>121468919</v>
       </c>
       <c r="B73" t="n">
-        <v>74710</v>
+        <v>79222</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7955,21 +7955,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486283</v>
+        <v>486341</v>
       </c>
       <c r="R73" t="n">
-        <v>6829532</v>
+        <v>6829217</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468937</v>
+        <v>121469017</v>
       </c>
       <c r="B74" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8057,21 +8057,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486310</v>
+        <v>486335</v>
       </c>
       <c r="R74" t="n">
-        <v>6829463</v>
+        <v>6829435</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8143,10 +8143,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468943</v>
+        <v>121468959</v>
       </c>
       <c r="B75" t="n">
-        <v>79193</v>
+        <v>80561</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486250</v>
+        <v>486437</v>
       </c>
       <c r="R75" t="n">
-        <v>6829400</v>
+        <v>6829174</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468957</v>
+        <v>121468982</v>
       </c>
       <c r="B76" t="n">
-        <v>8432</v>
+        <v>78604</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8257,47 +8257,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486210</v>
+        <v>486213</v>
       </c>
       <c r="R76" t="n">
-        <v>6829556</v>
+        <v>6829765</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8338,7 +8329,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8357,10 +8347,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468995</v>
+        <v>121468941</v>
       </c>
       <c r="B77" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8373,21 +8363,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8397,10 +8387,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486256</v>
+        <v>486174</v>
       </c>
       <c r="R77" t="n">
-        <v>6829523</v>
+        <v>6829641</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8459,10 +8449,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468919</v>
+        <v>121469020</v>
       </c>
       <c r="B78" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8475,21 +8465,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8499,10 +8489,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486341</v>
+        <v>486312</v>
       </c>
       <c r="R78" t="n">
-        <v>6829217</v>
+        <v>6829467</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8561,10 +8551,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469019</v>
+        <v>121468957</v>
       </c>
       <c r="B79" t="n">
-        <v>78604</v>
+        <v>8432</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8573,38 +8563,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486309</v>
+        <v>486210</v>
       </c>
       <c r="R79" t="n">
-        <v>6829468</v>
+        <v>6829556</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,6 +8644,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468918</v>
+        <v>121468979</v>
       </c>
       <c r="B80" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486321</v>
+        <v>486282</v>
       </c>
       <c r="R80" t="n">
-        <v>6829248</v>
+        <v>6829704</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469027</v>
+        <v>121468961</v>
       </c>
       <c r="B81" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486370</v>
+        <v>486376</v>
       </c>
       <c r="R81" t="n">
-        <v>6829559</v>
+        <v>6829237</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468991</v>
+        <v>121468915</v>
       </c>
       <c r="B82" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8883,21 +8883,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486297</v>
+        <v>486223</v>
       </c>
       <c r="R82" t="n">
-        <v>6829538</v>
+        <v>6829705</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,10 +8969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468938</v>
+        <v>121469044</v>
       </c>
       <c r="B83" t="n">
-        <v>78638</v>
+        <v>78249</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8985,21 +8985,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486329</v>
+        <v>486236</v>
       </c>
       <c r="R83" t="n">
-        <v>6829484</v>
+        <v>6829512</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,7 +9071,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468987</v>
+        <v>121468973</v>
       </c>
       <c r="B84" t="n">
         <v>78604</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486271</v>
+        <v>486298</v>
       </c>
       <c r="R84" t="n">
-        <v>6829568</v>
+        <v>6829599</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121468983</v>
+        <v>121468991</v>
       </c>
       <c r="B85" t="n">
         <v>78604</v>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486213</v>
+        <v>486297</v>
       </c>
       <c r="R85" t="n">
-        <v>6829683</v>
+        <v>6829538</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121468935</v>
+        <v>121469008</v>
       </c>
       <c r="B86" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9291,21 +9291,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486323</v>
+        <v>486416</v>
       </c>
       <c r="R86" t="n">
-        <v>6829408</v>
+        <v>6829192</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469035</v>
+        <v>121468942</v>
       </c>
       <c r="B87" t="n">
-        <v>78249</v>
+        <v>79193</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9393,21 +9393,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486278</v>
+        <v>486165</v>
       </c>
       <c r="R87" t="n">
-        <v>6829675</v>
+        <v>6829633</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,7 +9479,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469006</v>
+        <v>121469007</v>
       </c>
       <c r="B88" t="n">
         <v>78604</v>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486437</v>
+        <v>486432</v>
       </c>
       <c r="R88" t="n">
-        <v>6829175</v>
+        <v>6829183</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,7 +9581,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469004</v>
+        <v>121468974</v>
       </c>
       <c r="B89" t="n">
         <v>78604</v>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486442</v>
+        <v>486301</v>
       </c>
       <c r="R89" t="n">
-        <v>6829128</v>
+        <v>6829606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,7 +9683,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121468978</v>
+        <v>121469023</v>
       </c>
       <c r="B90" t="n">
         <v>78604</v>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486279</v>
+        <v>486362</v>
       </c>
       <c r="R90" t="n">
-        <v>6829687</v>
+        <v>6829525</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121469004</v>
+        <v>121469047</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>77536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486442</v>
+        <v>486258</v>
       </c>
       <c r="R2" t="n">
-        <v>6829128</v>
+        <v>6829343</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121469045</v>
+        <v>121469015</v>
       </c>
       <c r="B3" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486365</v>
+        <v>486323</v>
       </c>
       <c r="R3" t="n">
-        <v>6829215</v>
+        <v>6829408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468927</v>
+        <v>121468935</v>
       </c>
       <c r="B4" t="n">
-        <v>74710</v>
+        <v>78638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486283</v>
+        <v>486323</v>
       </c>
       <c r="R4" t="n">
-        <v>6829532</v>
+        <v>6829408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468987</v>
+        <v>121468955</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486271</v>
+        <v>486321</v>
       </c>
       <c r="R5" t="n">
-        <v>6829568</v>
+        <v>6829248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468938</v>
+        <v>121468921</v>
       </c>
       <c r="B6" t="n">
-        <v>78638</v>
+        <v>79222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486329</v>
+        <v>486365</v>
       </c>
       <c r="R6" t="n">
-        <v>6829484</v>
+        <v>6829163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468958</v>
+        <v>121468967</v>
       </c>
       <c r="B7" t="n">
-        <v>80561</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486278</v>
+        <v>486329</v>
       </c>
       <c r="R7" t="n">
-        <v>6829675</v>
+        <v>6829590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468996</v>
+        <v>121468968</v>
       </c>
       <c r="B8" t="n">
         <v>78604</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486242</v>
+        <v>486325</v>
       </c>
       <c r="R8" t="n">
-        <v>6829317</v>
+        <v>6829578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468968</v>
+        <v>121468937</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486325</v>
+        <v>486310</v>
       </c>
       <c r="R9" t="n">
-        <v>6829578</v>
+        <v>6829463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468918</v>
+        <v>121469004</v>
       </c>
       <c r="B10" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486321</v>
+        <v>486442</v>
       </c>
       <c r="R10" t="n">
-        <v>6829248</v>
+        <v>6829128</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469009</v>
+        <v>121468973</v>
       </c>
       <c r="B11" t="n">
         <v>78604</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486396</v>
+        <v>486298</v>
       </c>
       <c r="R11" t="n">
-        <v>6829190</v>
+        <v>6829599</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468966</v>
+        <v>121468989</v>
       </c>
       <c r="B12" t="n">
         <v>78604</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486335</v>
+        <v>486302</v>
       </c>
       <c r="R12" t="n">
-        <v>6829590</v>
+        <v>6829539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121468935</v>
+        <v>121469024</v>
       </c>
       <c r="B13" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486323</v>
+        <v>486351</v>
       </c>
       <c r="R13" t="n">
-        <v>6829408</v>
+        <v>6829541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468995</v>
+        <v>121468985</v>
       </c>
       <c r="B14" t="n">
         <v>78604</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486256</v>
+        <v>486183</v>
       </c>
       <c r="R14" t="n">
-        <v>6829523</v>
+        <v>6829659</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469046</v>
+        <v>121468932</v>
       </c>
       <c r="B15" t="n">
-        <v>78249</v>
+        <v>78638</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486324</v>
+        <v>486261</v>
       </c>
       <c r="R15" t="n">
-        <v>6829398</v>
+        <v>6829525</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468978</v>
+        <v>121469008</v>
       </c>
       <c r="B16" t="n">
         <v>78604</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486279</v>
+        <v>486416</v>
       </c>
       <c r="R16" t="n">
-        <v>6829687</v>
+        <v>6829192</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468946</v>
+        <v>121468966</v>
       </c>
       <c r="B17" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,46 +2221,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486392</v>
+        <v>486335</v>
       </c>
       <c r="R17" t="n">
-        <v>6829119</v>
+        <v>6829590</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2319,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468983</v>
+        <v>121469005</v>
       </c>
       <c r="B18" t="n">
         <v>78604</v>
@@ -2359,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486213</v>
+        <v>486438</v>
       </c>
       <c r="R18" t="n">
-        <v>6829683</v>
+        <v>6829156</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468929</v>
+        <v>121468944</v>
       </c>
       <c r="B19" t="n">
-        <v>78638</v>
+        <v>79193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486309</v>
+        <v>486255</v>
       </c>
       <c r="R19" t="n">
-        <v>6829581</v>
+        <v>6829395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121468922</v>
+        <v>121469012</v>
       </c>
       <c r="B20" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2539,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486376</v>
+        <v>486315</v>
       </c>
       <c r="R20" t="n">
-        <v>6829237</v>
+        <v>6829368</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468943</v>
+        <v>121468974</v>
       </c>
       <c r="B21" t="n">
-        <v>79193</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486250</v>
+        <v>486301</v>
       </c>
       <c r="R21" t="n">
-        <v>6829400</v>
+        <v>6829606</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469010</v>
+        <v>121469013</v>
       </c>
       <c r="B22" t="n">
         <v>78604</v>
@@ -2767,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486366</v>
+        <v>486318</v>
       </c>
       <c r="R22" t="n">
-        <v>6829228</v>
+        <v>6829376</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468954</v>
+        <v>121468996</v>
       </c>
       <c r="B23" t="n">
-        <v>8432</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2841,47 +2829,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486213</v>
+        <v>486242</v>
       </c>
       <c r="R23" t="n">
-        <v>6829562</v>
+        <v>6829317</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2901,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2941,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468934</v>
+        <v>121468979</v>
       </c>
       <c r="B24" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2957,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486318</v>
+        <v>486282</v>
       </c>
       <c r="R24" t="n">
-        <v>6829376</v>
+        <v>6829704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3043,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468977</v>
+        <v>121468947</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3059,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3083,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486269</v>
+        <v>486213</v>
       </c>
       <c r="R25" t="n">
-        <v>6829656</v>
+        <v>6829765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468967</v>
+        <v>121468942</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3161,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3185,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486329</v>
+        <v>486165</v>
       </c>
       <c r="R26" t="n">
-        <v>6829590</v>
+        <v>6829633</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121468955</v>
+        <v>121468977</v>
       </c>
       <c r="B27" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3263,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3287,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486321</v>
+        <v>486269</v>
       </c>
       <c r="R27" t="n">
-        <v>6829248</v>
+        <v>6829656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3349,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469006</v>
+        <v>121469021</v>
       </c>
       <c r="B28" t="n">
         <v>78604</v>
@@ -3389,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486437</v>
+        <v>486328</v>
       </c>
       <c r="R28" t="n">
-        <v>6829175</v>
+        <v>6829486</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469024</v>
+        <v>121469028</v>
       </c>
       <c r="B29" t="n">
         <v>78604</v>
@@ -3491,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486351</v>
+        <v>486375</v>
       </c>
       <c r="R29" t="n">
-        <v>6829541</v>
+        <v>6829566</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469035</v>
+        <v>121468976</v>
       </c>
       <c r="B30" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3569,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3593,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486278</v>
+        <v>486293</v>
       </c>
       <c r="R30" t="n">
-        <v>6829675</v>
+        <v>6829631</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469043</v>
+        <v>121468982</v>
       </c>
       <c r="B31" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3671,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3695,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486291</v>
+        <v>486213</v>
       </c>
       <c r="R31" t="n">
-        <v>6829537</v>
+        <v>6829765</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469027</v>
+        <v>121469006</v>
       </c>
       <c r="B32" t="n">
         <v>78604</v>
@@ -3797,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486370</v>
+        <v>486437</v>
       </c>
       <c r="R32" t="n">
-        <v>6829559</v>
+        <v>6829175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469018</v>
+        <v>121469044</v>
       </c>
       <c r="B33" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3875,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486306</v>
+        <v>486236</v>
       </c>
       <c r="R33" t="n">
-        <v>6829450</v>
+        <v>6829512</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3961,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468931</v>
+        <v>121468959</v>
       </c>
       <c r="B34" t="n">
-        <v>78638</v>
+        <v>80561</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3977,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4001,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486202</v>
+        <v>486437</v>
       </c>
       <c r="R34" t="n">
-        <v>6829676</v>
+        <v>6829174</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4063,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468937</v>
+        <v>121468936</v>
       </c>
       <c r="B35" t="n">
         <v>78638</v>
@@ -4103,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486310</v>
+        <v>486335</v>
       </c>
       <c r="R35" t="n">
-        <v>6829463</v>
+        <v>6829435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469028</v>
+        <v>121468914</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4181,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4205,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486375</v>
+        <v>486317</v>
       </c>
       <c r="R36" t="n">
-        <v>6829566</v>
+        <v>6829572</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4267,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121468928</v>
+        <v>121468984</v>
       </c>
       <c r="B37" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4283,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4307,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486313</v>
+        <v>486202</v>
       </c>
       <c r="R37" t="n">
-        <v>6829466</v>
+        <v>6829676</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469012</v>
+        <v>121468929</v>
       </c>
       <c r="B38" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4385,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4409,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486315</v>
+        <v>486309</v>
       </c>
       <c r="R38" t="n">
-        <v>6829368</v>
+        <v>6829581</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468992</v>
+        <v>121469034</v>
       </c>
       <c r="B39" t="n">
-        <v>78604</v>
+        <v>88031</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4487,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4511,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486291</v>
+        <v>486298</v>
       </c>
       <c r="R39" t="n">
-        <v>6829537</v>
+        <v>6829599</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4573,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469013</v>
+        <v>121469046</v>
       </c>
       <c r="B40" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4589,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4613,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486318</v>
+        <v>486324</v>
       </c>
       <c r="R40" t="n">
-        <v>6829376</v>
+        <v>6829398</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4675,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468940</v>
+        <v>121468915</v>
       </c>
       <c r="B41" t="n">
-        <v>79193</v>
+        <v>79222</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4691,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4715,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486207</v>
+        <v>486223</v>
       </c>
       <c r="R41" t="n">
-        <v>6829684</v>
+        <v>6829705</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4777,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469005</v>
+        <v>121469035</v>
       </c>
       <c r="B42" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4817,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486438</v>
+        <v>486278</v>
       </c>
       <c r="R42" t="n">
-        <v>6829156</v>
+        <v>6829675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468921</v>
+        <v>121468931</v>
       </c>
       <c r="B43" t="n">
-        <v>79222</v>
+        <v>78638</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4919,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486365</v>
+        <v>486202</v>
       </c>
       <c r="R43" t="n">
-        <v>6829163</v>
+        <v>6829676</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4981,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468932</v>
+        <v>121468922</v>
       </c>
       <c r="B44" t="n">
-        <v>78638</v>
+        <v>79222</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4997,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5021,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486261</v>
+        <v>486376</v>
       </c>
       <c r="R44" t="n">
-        <v>6829525</v>
+        <v>6829237</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5083,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469019</v>
+        <v>121468958</v>
       </c>
       <c r="B45" t="n">
-        <v>78604</v>
+        <v>80561</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5099,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5123,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486309</v>
+        <v>486278</v>
       </c>
       <c r="R45" t="n">
-        <v>6829468</v>
+        <v>6829675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5185,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469015</v>
+        <v>121469027</v>
       </c>
       <c r="B46" t="n">
         <v>78604</v>
@@ -5225,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486323</v>
+        <v>486370</v>
       </c>
       <c r="R46" t="n">
-        <v>6829408</v>
+        <v>6829559</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468984</v>
+        <v>121468992</v>
       </c>
       <c r="B47" t="n">
         <v>78604</v>
@@ -5327,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486202</v>
+        <v>486291</v>
       </c>
       <c r="R47" t="n">
-        <v>6829676</v>
+        <v>6829537</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469025</v>
+        <v>121469018</v>
       </c>
       <c r="B48" t="n">
         <v>78604</v>
@@ -5429,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486353</v>
+        <v>486306</v>
       </c>
       <c r="R48" t="n">
-        <v>6829553</v>
+        <v>6829450</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,7 +5469,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468970</v>
+        <v>121468978</v>
       </c>
       <c r="B49" t="n">
         <v>78604</v>
@@ -5531,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486315</v>
+        <v>486279</v>
       </c>
       <c r="R49" t="n">
-        <v>6829584</v>
+        <v>6829687</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5593,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121468986</v>
+        <v>121468991</v>
       </c>
       <c r="B50" t="n">
         <v>78604</v>
@@ -5633,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486259</v>
+        <v>486297</v>
       </c>
       <c r="R50" t="n">
-        <v>6829565</v>
+        <v>6829538</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468971</v>
+        <v>121468919</v>
       </c>
       <c r="B51" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5711,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5735,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486309</v>
+        <v>486341</v>
       </c>
       <c r="R51" t="n">
-        <v>6829581</v>
+        <v>6829217</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5797,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468944</v>
+        <v>121468934</v>
       </c>
       <c r="B52" t="n">
-        <v>79193</v>
+        <v>78638</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5813,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5837,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486255</v>
+        <v>486318</v>
       </c>
       <c r="R52" t="n">
-        <v>6829395</v>
+        <v>6829376</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5899,10 +5877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469034</v>
+        <v>121468957</v>
       </c>
       <c r="B53" t="n">
-        <v>88031</v>
+        <v>8432</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5911,38 +5889,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486298</v>
+        <v>486210</v>
       </c>
       <c r="R53" t="n">
-        <v>6829599</v>
+        <v>6829556</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5983,6 +5970,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6001,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468993</v>
+        <v>121468943</v>
       </c>
       <c r="B54" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6017,21 +6005,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6041,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486272</v>
+        <v>486250</v>
       </c>
       <c r="R54" t="n">
-        <v>6829527</v>
+        <v>6829400</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6103,7 +6091,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469021</v>
+        <v>121469023</v>
       </c>
       <c r="B55" t="n">
         <v>78604</v>
@@ -6143,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486328</v>
+        <v>486362</v>
       </c>
       <c r="R55" t="n">
-        <v>6829486</v>
+        <v>6829525</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6205,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469047</v>
+        <v>121469010</v>
       </c>
       <c r="B56" t="n">
-        <v>77536</v>
+        <v>78604</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6221,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6245,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486258</v>
+        <v>486366</v>
       </c>
       <c r="R56" t="n">
-        <v>6829343</v>
+        <v>6829228</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6307,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468939</v>
+        <v>121469001</v>
       </c>
       <c r="B57" t="n">
-        <v>79193</v>
+        <v>78604</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6323,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6347,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486265</v>
+        <v>486374</v>
       </c>
       <c r="R57" t="n">
-        <v>6829735</v>
+        <v>6829123</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6409,7 +6397,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468999</v>
+        <v>121468994</v>
       </c>
       <c r="B58" t="n">
         <v>78604</v>
@@ -6449,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486352</v>
+        <v>486261</v>
       </c>
       <c r="R58" t="n">
-        <v>6829165</v>
+        <v>6829525</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6511,7 +6499,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468989</v>
+        <v>121468969</v>
       </c>
       <c r="B59" t="n">
         <v>78604</v>
@@ -6551,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486302</v>
+        <v>486317</v>
       </c>
       <c r="R59" t="n">
-        <v>6829539</v>
+        <v>6829572</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6613,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468933</v>
+        <v>121468999</v>
       </c>
       <c r="B60" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6629,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6653,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486317</v>
+        <v>486352</v>
       </c>
       <c r="R60" t="n">
-        <v>6829373</v>
+        <v>6829165</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6715,10 +6703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468994</v>
+        <v>121469036</v>
       </c>
       <c r="B61" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6731,21 +6719,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,7 +6746,7 @@
         <v>486261</v>
       </c>
       <c r="R61" t="n">
-        <v>6829525</v>
+        <v>6829744</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6817,10 +6805,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468998</v>
+        <v>121468917</v>
       </c>
       <c r="B62" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6833,21 +6821,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6857,10 +6845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486366</v>
+        <v>486305</v>
       </c>
       <c r="R62" t="n">
-        <v>6829176</v>
+        <v>6829222</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6919,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468917</v>
+        <v>121469007</v>
       </c>
       <c r="B63" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6935,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6959,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486305</v>
+        <v>486432</v>
       </c>
       <c r="R63" t="n">
-        <v>6829222</v>
+        <v>6829183</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7021,7 +7009,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468975</v>
+        <v>121468983</v>
       </c>
       <c r="B64" t="n">
         <v>78604</v>
@@ -7061,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486298</v>
+        <v>486213</v>
       </c>
       <c r="R64" t="n">
-        <v>6829621</v>
+        <v>6829683</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7123,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468947</v>
+        <v>121468961</v>
       </c>
       <c r="B65" t="n">
-        <v>57504</v>
+        <v>78340</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7139,21 +7127,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7163,10 +7151,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486213</v>
+        <v>486376</v>
       </c>
       <c r="R65" t="n">
-        <v>6829765</v>
+        <v>6829237</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7225,7 +7213,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468969</v>
+        <v>121468971</v>
       </c>
       <c r="B66" t="n">
         <v>78604</v>
@@ -7265,10 +7253,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486317</v>
+        <v>486309</v>
       </c>
       <c r="R66" t="n">
-        <v>6829572</v>
+        <v>6829581</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7327,7 +7315,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469001</v>
+        <v>121469009</v>
       </c>
       <c r="B67" t="n">
         <v>78604</v>
@@ -7367,10 +7355,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486374</v>
+        <v>486396</v>
       </c>
       <c r="R67" t="n">
-        <v>6829123</v>
+        <v>6829190</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7429,10 +7417,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468936</v>
+        <v>121468998</v>
       </c>
       <c r="B68" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7445,21 +7433,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7469,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486335</v>
+        <v>486366</v>
       </c>
       <c r="R68" t="n">
-        <v>6829435</v>
+        <v>6829176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7531,7 +7519,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468914</v>
+        <v>121468918</v>
       </c>
       <c r="B69" t="n">
         <v>79222</v>
@@ -7571,10 +7559,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486317</v>
+        <v>486321</v>
       </c>
       <c r="R69" t="n">
-        <v>6829572</v>
+        <v>6829248</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7633,10 +7621,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468985</v>
+        <v>121468954</v>
       </c>
       <c r="B70" t="n">
-        <v>78604</v>
+        <v>8432</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7645,38 +7633,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486183</v>
+        <v>486213</v>
       </c>
       <c r="R70" t="n">
-        <v>6829659</v>
+        <v>6829562</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7717,6 +7714,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7735,10 +7733,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468976</v>
+        <v>121468933</v>
       </c>
       <c r="B71" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7751,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486293</v>
+        <v>486317</v>
       </c>
       <c r="R71" t="n">
-        <v>6829631</v>
+        <v>6829373</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7837,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469036</v>
+        <v>121469017</v>
       </c>
       <c r="B72" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7853,21 +7851,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7877,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486261</v>
+        <v>486335</v>
       </c>
       <c r="R72" t="n">
-        <v>6829744</v>
+        <v>6829435</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7939,10 +7937,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468919</v>
+        <v>121469025</v>
       </c>
       <c r="B73" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7955,21 +7953,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7979,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486341</v>
+        <v>486353</v>
       </c>
       <c r="R73" t="n">
-        <v>6829217</v>
+        <v>6829553</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8041,7 +8039,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469017</v>
+        <v>121468970</v>
       </c>
       <c r="B74" t="n">
         <v>78604</v>
@@ -8081,10 +8079,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486335</v>
+        <v>486315</v>
       </c>
       <c r="R74" t="n">
-        <v>6829435</v>
+        <v>6829584</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8143,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468959</v>
+        <v>121469020</v>
       </c>
       <c r="B75" t="n">
-        <v>80561</v>
+        <v>78604</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8159,21 +8157,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8183,10 +8181,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486437</v>
+        <v>486312</v>
       </c>
       <c r="R75" t="n">
-        <v>6829174</v>
+        <v>6829467</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8245,10 +8243,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468982</v>
+        <v>121468927</v>
       </c>
       <c r="B76" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8261,21 +8259,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8285,10 +8283,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486213</v>
+        <v>486283</v>
       </c>
       <c r="R76" t="n">
-        <v>6829765</v>
+        <v>6829532</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8347,10 +8345,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468941</v>
+        <v>121468987</v>
       </c>
       <c r="B77" t="n">
-        <v>79193</v>
+        <v>78604</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8363,21 +8361,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8387,10 +8385,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486174</v>
+        <v>486271</v>
       </c>
       <c r="R77" t="n">
-        <v>6829641</v>
+        <v>6829568</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8449,7 +8447,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469020</v>
+        <v>121468986</v>
       </c>
       <c r="B78" t="n">
         <v>78604</v>
@@ -8489,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486312</v>
+        <v>486259</v>
       </c>
       <c r="R78" t="n">
-        <v>6829467</v>
+        <v>6829565</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8551,10 +8549,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468957</v>
+        <v>121468941</v>
       </c>
       <c r="B79" t="n">
-        <v>8432</v>
+        <v>79193</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8563,47 +8561,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486210</v>
+        <v>486174</v>
       </c>
       <c r="R79" t="n">
-        <v>6829556</v>
+        <v>6829641</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8644,7 +8633,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8663,10 +8651,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468979</v>
+        <v>121468940</v>
       </c>
       <c r="B80" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8667,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8691,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486282</v>
+        <v>486207</v>
       </c>
       <c r="R80" t="n">
-        <v>6829704</v>
+        <v>6829684</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8753,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468961</v>
+        <v>121469019</v>
       </c>
       <c r="B81" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,21 +8769,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486376</v>
+        <v>486309</v>
       </c>
       <c r="R81" t="n">
-        <v>6829237</v>
+        <v>6829468</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,10 +8855,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468915</v>
+        <v>121468928</v>
       </c>
       <c r="B82" t="n">
-        <v>79222</v>
+        <v>74710</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8883,21 +8871,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8907,10 +8895,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486223</v>
+        <v>486313</v>
       </c>
       <c r="R82" t="n">
-        <v>6829705</v>
+        <v>6829466</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,10 +8957,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469044</v>
+        <v>121468946</v>
       </c>
       <c r="B83" t="n">
-        <v>78249</v>
+        <v>57504</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8985,34 +8973,46 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486236</v>
+        <v>486392</v>
       </c>
       <c r="R83" t="n">
-        <v>6829512</v>
+        <v>6829119</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468973</v>
+        <v>121469045</v>
       </c>
       <c r="B84" t="n">
-        <v>78604</v>
+        <v>78249</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9087,21 +9087,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486298</v>
+        <v>486365</v>
       </c>
       <c r="R84" t="n">
-        <v>6829599</v>
+        <v>6829215</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121468991</v>
+        <v>121468938</v>
       </c>
       <c r="B85" t="n">
-        <v>78604</v>
+        <v>78638</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486297</v>
+        <v>486329</v>
       </c>
       <c r="R85" t="n">
-        <v>6829538</v>
+        <v>6829484</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469008</v>
+        <v>121468939</v>
       </c>
       <c r="B86" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9291,21 +9291,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486416</v>
+        <v>486265</v>
       </c>
       <c r="R86" t="n">
-        <v>6829192</v>
+        <v>6829735</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468942</v>
+        <v>121469043</v>
       </c>
       <c r="B87" t="n">
-        <v>79193</v>
+        <v>78249</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9393,21 +9393,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486165</v>
+        <v>486291</v>
       </c>
       <c r="R87" t="n">
-        <v>6829633</v>
+        <v>6829537</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,7 +9479,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469007</v>
+        <v>121468995</v>
       </c>
       <c r="B88" t="n">
         <v>78604</v>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486432</v>
+        <v>486256</v>
       </c>
       <c r="R88" t="n">
-        <v>6829183</v>
+        <v>6829523</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,7 +9581,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468974</v>
+        <v>121468993</v>
       </c>
       <c r="B89" t="n">
         <v>78604</v>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486301</v>
+        <v>486272</v>
       </c>
       <c r="R89" t="n">
-        <v>6829606</v>
+        <v>6829527</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,7 +9683,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469023</v>
+        <v>121468975</v>
       </c>
       <c r="B90" t="n">
         <v>78604</v>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486362</v>
+        <v>486298</v>
       </c>
       <c r="R90" t="n">
-        <v>6829525</v>
+        <v>6829621</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121469047</v>
+        <v>121468919</v>
       </c>
       <c r="B2" t="n">
-        <v>77536</v>
+        <v>79225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486258</v>
+        <v>486341</v>
       </c>
       <c r="R2" t="n">
-        <v>6829343</v>
+        <v>6829217</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121469015</v>
+        <v>121468989</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486323</v>
+        <v>486302</v>
       </c>
       <c r="R3" t="n">
-        <v>6829408</v>
+        <v>6829539</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468935</v>
+        <v>121468915</v>
       </c>
       <c r="B4" t="n">
-        <v>78638</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486323</v>
+        <v>486223</v>
       </c>
       <c r="R4" t="n">
-        <v>6829408</v>
+        <v>6829705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468955</v>
+        <v>121468939</v>
       </c>
       <c r="B5" t="n">
-        <v>78341</v>
+        <v>79196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486321</v>
+        <v>486265</v>
       </c>
       <c r="R5" t="n">
-        <v>6829248</v>
+        <v>6829735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468921</v>
+        <v>121469034</v>
       </c>
       <c r="B6" t="n">
-        <v>79222</v>
+        <v>88034</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486365</v>
+        <v>486298</v>
       </c>
       <c r="R6" t="n">
-        <v>6829163</v>
+        <v>6829599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468967</v>
+        <v>121468958</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>80564</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486329</v>
+        <v>486278</v>
       </c>
       <c r="R7" t="n">
-        <v>6829590</v>
+        <v>6829675</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468968</v>
+        <v>121469012</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486325</v>
+        <v>486315</v>
       </c>
       <c r="R8" t="n">
-        <v>6829578</v>
+        <v>6829368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468937</v>
+        <v>121469020</v>
       </c>
       <c r="B9" t="n">
-        <v>78638</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486310</v>
+        <v>486312</v>
       </c>
       <c r="R9" t="n">
-        <v>6829463</v>
+        <v>6829467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469004</v>
+        <v>121468983</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486442</v>
+        <v>486213</v>
       </c>
       <c r="R10" t="n">
-        <v>6829128</v>
+        <v>6829683</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468973</v>
+        <v>121468993</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486298</v>
+        <v>486272</v>
       </c>
       <c r="R11" t="n">
-        <v>6829599</v>
+        <v>6829527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468989</v>
+        <v>121468969</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486302</v>
+        <v>486317</v>
       </c>
       <c r="R12" t="n">
-        <v>6829539</v>
+        <v>6829572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469024</v>
+        <v>121468999</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486351</v>
+        <v>486352</v>
       </c>
       <c r="R13" t="n">
-        <v>6829541</v>
+        <v>6829165</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468985</v>
+        <v>121469010</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486183</v>
+        <v>486366</v>
       </c>
       <c r="R14" t="n">
-        <v>6829659</v>
+        <v>6829228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468932</v>
+        <v>121468917</v>
       </c>
       <c r="B15" t="n">
-        <v>78638</v>
+        <v>79225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486261</v>
+        <v>486305</v>
       </c>
       <c r="R15" t="n">
-        <v>6829525</v>
+        <v>6829222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121469008</v>
+        <v>121468966</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486416</v>
+        <v>486335</v>
       </c>
       <c r="R16" t="n">
-        <v>6829192</v>
+        <v>6829590</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468966</v>
+        <v>121468914</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486335</v>
+        <v>486317</v>
       </c>
       <c r="R17" t="n">
-        <v>6829590</v>
+        <v>6829572</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469005</v>
+        <v>121468978</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486438</v>
+        <v>486279</v>
       </c>
       <c r="R18" t="n">
-        <v>6829156</v>
+        <v>6829687</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468944</v>
+        <v>121469005</v>
       </c>
       <c r="B19" t="n">
-        <v>79193</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486255</v>
+        <v>486438</v>
       </c>
       <c r="R19" t="n">
-        <v>6829395</v>
+        <v>6829156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469012</v>
+        <v>121468954</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>8435</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,38 +2523,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486315</v>
+        <v>486213</v>
       </c>
       <c r="R20" t="n">
-        <v>6829368</v>
+        <v>6829562</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,6 +2604,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2613,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468974</v>
+        <v>121468931</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486301</v>
+        <v>486202</v>
       </c>
       <c r="R21" t="n">
-        <v>6829606</v>
+        <v>6829676</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469013</v>
+        <v>121468934</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468996</v>
+        <v>121468994</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486242</v>
+        <v>486261</v>
       </c>
       <c r="R23" t="n">
-        <v>6829317</v>
+        <v>6829525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468979</v>
+        <v>121469024</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486282</v>
+        <v>486351</v>
       </c>
       <c r="R24" t="n">
-        <v>6829704</v>
+        <v>6829541</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468947</v>
+        <v>121468976</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486213</v>
+        <v>486293</v>
       </c>
       <c r="R25" t="n">
-        <v>6829765</v>
+        <v>6829631</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468942</v>
+        <v>121468940</v>
       </c>
       <c r="B26" t="n">
-        <v>79193</v>
+        <v>79196</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486165</v>
+        <v>486207</v>
       </c>
       <c r="R26" t="n">
-        <v>6829633</v>
+        <v>6829684</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121468977</v>
+        <v>121468992</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486269</v>
+        <v>486291</v>
       </c>
       <c r="R27" t="n">
-        <v>6829656</v>
+        <v>6829537</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469021</v>
+        <v>121468995</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3367,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486328</v>
+        <v>486256</v>
       </c>
       <c r="R28" t="n">
-        <v>6829486</v>
+        <v>6829523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469028</v>
+        <v>121469007</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486375</v>
+        <v>486432</v>
       </c>
       <c r="R29" t="n">
-        <v>6829566</v>
+        <v>6829183</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468976</v>
+        <v>121469008</v>
       </c>
       <c r="B30" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486293</v>
+        <v>486416</v>
       </c>
       <c r="R30" t="n">
-        <v>6829631</v>
+        <v>6829192</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468982</v>
+        <v>121468985</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486213</v>
+        <v>486183</v>
       </c>
       <c r="R31" t="n">
-        <v>6829765</v>
+        <v>6829659</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469006</v>
+        <v>121468933</v>
       </c>
       <c r="B32" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486437</v>
+        <v>486317</v>
       </c>
       <c r="R32" t="n">
-        <v>6829175</v>
+        <v>6829373</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469044</v>
+        <v>121468959</v>
       </c>
       <c r="B33" t="n">
-        <v>78249</v>
+        <v>80564</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486236</v>
+        <v>486437</v>
       </c>
       <c r="R33" t="n">
-        <v>6829512</v>
+        <v>6829174</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468959</v>
+        <v>121469044</v>
       </c>
       <c r="B34" t="n">
-        <v>80561</v>
+        <v>78252</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486437</v>
+        <v>486236</v>
       </c>
       <c r="R34" t="n">
-        <v>6829174</v>
+        <v>6829512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468936</v>
+        <v>121469046</v>
       </c>
       <c r="B35" t="n">
-        <v>78638</v>
+        <v>78252</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4067,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486335</v>
+        <v>486324</v>
       </c>
       <c r="R35" t="n">
-        <v>6829435</v>
+        <v>6829398</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468914</v>
+        <v>121469013</v>
       </c>
       <c r="B36" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4169,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486317</v>
+        <v>486318</v>
       </c>
       <c r="R36" t="n">
-        <v>6829572</v>
+        <v>6829376</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121468984</v>
+        <v>121468927</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4271,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486202</v>
+        <v>486283</v>
       </c>
       <c r="R37" t="n">
-        <v>6829676</v>
+        <v>6829532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468929</v>
+        <v>121468982</v>
       </c>
       <c r="B38" t="n">
-        <v>78638</v>
+        <v>78607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4373,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486309</v>
+        <v>486213</v>
       </c>
       <c r="R38" t="n">
-        <v>6829581</v>
+        <v>6829765</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469034</v>
+        <v>121468918</v>
       </c>
       <c r="B39" t="n">
-        <v>88031</v>
+        <v>79225</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4475,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486298</v>
+        <v>486321</v>
       </c>
       <c r="R39" t="n">
-        <v>6829599</v>
+        <v>6829248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469046</v>
+        <v>121468947</v>
       </c>
       <c r="B40" t="n">
-        <v>78249</v>
+        <v>57507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486324</v>
+        <v>486213</v>
       </c>
       <c r="R40" t="n">
-        <v>6829398</v>
+        <v>6829765</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468915</v>
+        <v>121469021</v>
       </c>
       <c r="B41" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4679,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486223</v>
+        <v>486328</v>
       </c>
       <c r="R41" t="n">
-        <v>6829705</v>
+        <v>6829486</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469035</v>
+        <v>121469025</v>
       </c>
       <c r="B42" t="n">
-        <v>78249</v>
+        <v>78607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486278</v>
+        <v>486353</v>
       </c>
       <c r="R42" t="n">
-        <v>6829675</v>
+        <v>6829553</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468931</v>
+        <v>121468955</v>
       </c>
       <c r="B43" t="n">
-        <v>78638</v>
+        <v>78344</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4883,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486202</v>
+        <v>486321</v>
       </c>
       <c r="R43" t="n">
-        <v>6829676</v>
+        <v>6829248</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468922</v>
+        <v>121468929</v>
       </c>
       <c r="B44" t="n">
-        <v>79222</v>
+        <v>78641</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4985,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486376</v>
+        <v>486309</v>
       </c>
       <c r="R44" t="n">
-        <v>6829237</v>
+        <v>6829581</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5071,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468958</v>
+        <v>121468979</v>
       </c>
       <c r="B45" t="n">
-        <v>80561</v>
+        <v>78607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5087,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5111,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486278</v>
+        <v>486282</v>
       </c>
       <c r="R45" t="n">
-        <v>6829675</v>
+        <v>6829704</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469027</v>
+        <v>121468932</v>
       </c>
       <c r="B46" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,21 +5189,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486370</v>
+        <v>486261</v>
       </c>
       <c r="R46" t="n">
-        <v>6829559</v>
+        <v>6829525</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,10 +5275,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468992</v>
+        <v>121469035</v>
       </c>
       <c r="B47" t="n">
-        <v>78604</v>
+        <v>78252</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5281,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486291</v>
+        <v>486278</v>
       </c>
       <c r="R47" t="n">
-        <v>6829537</v>
+        <v>6829675</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469018</v>
+        <v>121469027</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486306</v>
+        <v>486370</v>
       </c>
       <c r="R48" t="n">
-        <v>6829450</v>
+        <v>6829559</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5479,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468978</v>
+        <v>121468977</v>
       </c>
       <c r="B49" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486279</v>
+        <v>486269</v>
       </c>
       <c r="R49" t="n">
-        <v>6829687</v>
+        <v>6829656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121468991</v>
+        <v>121469004</v>
       </c>
       <c r="B50" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,10 +5621,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486297</v>
+        <v>486442</v>
       </c>
       <c r="R50" t="n">
-        <v>6829538</v>
+        <v>6829128</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5683,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468919</v>
+        <v>121469006</v>
       </c>
       <c r="B51" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5699,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486341</v>
+        <v>486437</v>
       </c>
       <c r="R51" t="n">
-        <v>6829217</v>
+        <v>6829175</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5785,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468934</v>
+        <v>121468961</v>
       </c>
       <c r="B52" t="n">
-        <v>78638</v>
+        <v>78343</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5801,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486318</v>
+        <v>486376</v>
       </c>
       <c r="R52" t="n">
-        <v>6829376</v>
+        <v>6829237</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5877,10 +5887,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468957</v>
+        <v>121469018</v>
       </c>
       <c r="B53" t="n">
-        <v>8432</v>
+        <v>78607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5889,47 +5899,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486210</v>
+        <v>486306</v>
       </c>
       <c r="R53" t="n">
-        <v>6829556</v>
+        <v>6829450</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5970,7 +5971,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5989,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468943</v>
+        <v>121469001</v>
       </c>
       <c r="B54" t="n">
-        <v>79193</v>
+        <v>78607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +6005,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486250</v>
+        <v>486374</v>
       </c>
       <c r="R54" t="n">
-        <v>6829400</v>
+        <v>6829123</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469023</v>
+        <v>121468970</v>
       </c>
       <c r="B55" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486362</v>
+        <v>486315</v>
       </c>
       <c r="R55" t="n">
-        <v>6829525</v>
+        <v>6829584</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469010</v>
+        <v>121468941</v>
       </c>
       <c r="B56" t="n">
-        <v>78604</v>
+        <v>79196</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486366</v>
+        <v>486174</v>
       </c>
       <c r="R56" t="n">
-        <v>6829228</v>
+        <v>6829641</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469001</v>
+        <v>121469023</v>
       </c>
       <c r="B57" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486374</v>
+        <v>486362</v>
       </c>
       <c r="R57" t="n">
-        <v>6829123</v>
+        <v>6829525</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468994</v>
+        <v>121468968</v>
       </c>
       <c r="B58" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486261</v>
+        <v>486325</v>
       </c>
       <c r="R58" t="n">
-        <v>6829525</v>
+        <v>6829578</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468969</v>
+        <v>121468987</v>
       </c>
       <c r="B59" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486317</v>
+        <v>486271</v>
       </c>
       <c r="R59" t="n">
-        <v>6829572</v>
+        <v>6829568</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468999</v>
+        <v>121468974</v>
       </c>
       <c r="B60" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486352</v>
+        <v>486301</v>
       </c>
       <c r="R60" t="n">
-        <v>6829165</v>
+        <v>6829606</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469036</v>
+        <v>121468922</v>
       </c>
       <c r="B61" t="n">
-        <v>78249</v>
+        <v>79225</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6719,21 +6719,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486261</v>
+        <v>486376</v>
       </c>
       <c r="R61" t="n">
-        <v>6829744</v>
+        <v>6829237</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6805,10 +6805,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468917</v>
+        <v>121468975</v>
       </c>
       <c r="B62" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6821,21 +6821,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486305</v>
+        <v>486298</v>
       </c>
       <c r="R62" t="n">
-        <v>6829222</v>
+        <v>6829621</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469007</v>
+        <v>121468957</v>
       </c>
       <c r="B63" t="n">
-        <v>78604</v>
+        <v>8435</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6919,38 +6919,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486432</v>
+        <v>486210</v>
       </c>
       <c r="R63" t="n">
-        <v>6829183</v>
+        <v>6829556</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6991,6 +7000,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7009,10 +7019,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468983</v>
+        <v>121468946</v>
       </c>
       <c r="B64" t="n">
-        <v>78604</v>
+        <v>57507</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7025,34 +7035,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486213</v>
+        <v>486392</v>
       </c>
       <c r="R64" t="n">
-        <v>6829683</v>
+        <v>6829119</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,10 +7133,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468961</v>
+        <v>121468928</v>
       </c>
       <c r="B65" t="n">
-        <v>78340</v>
+        <v>74713</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7127,21 +7149,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7151,10 +7173,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486376</v>
+        <v>486313</v>
       </c>
       <c r="R65" t="n">
-        <v>6829237</v>
+        <v>6829466</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,10 +7235,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468971</v>
+        <v>121468921</v>
       </c>
       <c r="B66" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7229,21 +7251,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7253,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486309</v>
+        <v>486365</v>
       </c>
       <c r="R66" t="n">
-        <v>6829581</v>
+        <v>6829163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7315,10 +7337,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469009</v>
+        <v>121468986</v>
       </c>
       <c r="B67" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7355,10 +7377,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486396</v>
+        <v>486259</v>
       </c>
       <c r="R67" t="n">
-        <v>6829190</v>
+        <v>6829565</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,10 +7439,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468998</v>
+        <v>121468984</v>
       </c>
       <c r="B68" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7457,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486366</v>
+        <v>486202</v>
       </c>
       <c r="R68" t="n">
-        <v>6829176</v>
+        <v>6829676</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7519,10 +7541,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468918</v>
+        <v>121468996</v>
       </c>
       <c r="B69" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7535,21 +7557,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7559,10 +7581,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486321</v>
+        <v>486242</v>
       </c>
       <c r="R69" t="n">
-        <v>6829248</v>
+        <v>6829317</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7621,10 +7643,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468954</v>
+        <v>121469028</v>
       </c>
       <c r="B70" t="n">
-        <v>8432</v>
+        <v>78607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7633,47 +7655,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486213</v>
+        <v>486375</v>
       </c>
       <c r="R70" t="n">
-        <v>6829562</v>
+        <v>6829566</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7714,7 +7727,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7733,10 +7745,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468933</v>
+        <v>121468971</v>
       </c>
       <c r="B71" t="n">
-        <v>78638</v>
+        <v>78607</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7749,21 +7761,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7785,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486317</v>
+        <v>486309</v>
       </c>
       <c r="R71" t="n">
-        <v>6829373</v>
+        <v>6829581</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7847,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469017</v>
+        <v>121468943</v>
       </c>
       <c r="B72" t="n">
-        <v>78604</v>
+        <v>79196</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7851,21 +7863,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7887,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486335</v>
+        <v>486250</v>
       </c>
       <c r="R72" t="n">
-        <v>6829435</v>
+        <v>6829400</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7937,10 +7949,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469025</v>
+        <v>121469009</v>
       </c>
       <c r="B73" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7977,10 +7989,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486353</v>
+        <v>486396</v>
       </c>
       <c r="R73" t="n">
-        <v>6829553</v>
+        <v>6829190</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8051,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468970</v>
+        <v>121468935</v>
       </c>
       <c r="B74" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8055,21 +8067,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8079,10 +8091,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486315</v>
+        <v>486323</v>
       </c>
       <c r="R74" t="n">
-        <v>6829584</v>
+        <v>6829408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8141,10 +8153,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469020</v>
+        <v>121469019</v>
       </c>
       <c r="B75" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8181,10 +8193,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486312</v>
+        <v>486309</v>
       </c>
       <c r="R75" t="n">
-        <v>6829467</v>
+        <v>6829468</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8243,10 +8255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468927</v>
+        <v>121468973</v>
       </c>
       <c r="B76" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8259,21 +8271,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8283,10 +8295,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486283</v>
+        <v>486298</v>
       </c>
       <c r="R76" t="n">
-        <v>6829532</v>
+        <v>6829599</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8345,10 +8357,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468987</v>
+        <v>121468937</v>
       </c>
       <c r="B77" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8361,21 +8373,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8385,10 +8397,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486271</v>
+        <v>486310</v>
       </c>
       <c r="R77" t="n">
-        <v>6829568</v>
+        <v>6829463</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8447,10 +8459,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468986</v>
+        <v>121468936</v>
       </c>
       <c r="B78" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8463,21 +8475,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8487,10 +8499,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486259</v>
+        <v>486335</v>
       </c>
       <c r="R78" t="n">
-        <v>6829565</v>
+        <v>6829435</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8549,10 +8561,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468941</v>
+        <v>121468942</v>
       </c>
       <c r="B79" t="n">
-        <v>79193</v>
+        <v>79196</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8589,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486174</v>
+        <v>486165</v>
       </c>
       <c r="R79" t="n">
-        <v>6829641</v>
+        <v>6829633</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8651,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468940</v>
+        <v>121468944</v>
       </c>
       <c r="B80" t="n">
-        <v>79193</v>
+        <v>79196</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8691,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486207</v>
+        <v>486255</v>
       </c>
       <c r="R80" t="n">
-        <v>6829684</v>
+        <v>6829395</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8753,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469019</v>
+        <v>121469045</v>
       </c>
       <c r="B81" t="n">
-        <v>78604</v>
+        <v>78252</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8769,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8793,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486309</v>
+        <v>486365</v>
       </c>
       <c r="R81" t="n">
-        <v>6829468</v>
+        <v>6829215</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8855,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468928</v>
+        <v>121468998</v>
       </c>
       <c r="B82" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8871,21 +8883,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8895,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486313</v>
+        <v>486366</v>
       </c>
       <c r="R82" t="n">
-        <v>6829466</v>
+        <v>6829176</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8957,10 +8969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468946</v>
+        <v>121469017</v>
       </c>
       <c r="B83" t="n">
-        <v>57504</v>
+        <v>78607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8973,46 +8985,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486392</v>
+        <v>486335</v>
       </c>
       <c r="R83" t="n">
-        <v>6829119</v>
+        <v>6829435</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469045</v>
+        <v>121468991</v>
       </c>
       <c r="B84" t="n">
-        <v>78249</v>
+        <v>78607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9087,21 +9087,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486365</v>
+        <v>486297</v>
       </c>
       <c r="R84" t="n">
-        <v>6829215</v>
+        <v>6829538</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121468938</v>
+        <v>121469043</v>
       </c>
       <c r="B85" t="n">
-        <v>78638</v>
+        <v>78252</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486329</v>
+        <v>486291</v>
       </c>
       <c r="R85" t="n">
-        <v>6829484</v>
+        <v>6829537</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121468939</v>
+        <v>121469015</v>
       </c>
       <c r="B86" t="n">
-        <v>79193</v>
+        <v>78607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9291,21 +9291,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486265</v>
+        <v>486323</v>
       </c>
       <c r="R86" t="n">
-        <v>6829735</v>
+        <v>6829408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469043</v>
+        <v>121469036</v>
       </c>
       <c r="B87" t="n">
-        <v>78249</v>
+        <v>78252</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486291</v>
+        <v>486261</v>
       </c>
       <c r="R87" t="n">
-        <v>6829537</v>
+        <v>6829744</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,10 +9479,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468995</v>
+        <v>121468938</v>
       </c>
       <c r="B88" t="n">
-        <v>78604</v>
+        <v>78641</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9495,21 +9495,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486256</v>
+        <v>486329</v>
       </c>
       <c r="R88" t="n">
-        <v>6829523</v>
+        <v>6829484</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,10 +9581,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468993</v>
+        <v>121468967</v>
       </c>
       <c r="B89" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486272</v>
+        <v>486329</v>
       </c>
       <c r="R89" t="n">
-        <v>6829527</v>
+        <v>6829590</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121468975</v>
+        <v>121469047</v>
       </c>
       <c r="B90" t="n">
-        <v>78604</v>
+        <v>77539</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9699,21 +9699,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486298</v>
+        <v>486258</v>
       </c>
       <c r="R90" t="n">
-        <v>6829621</v>
+        <v>6829343</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121468919</v>
+        <v>121468973</v>
       </c>
       <c r="B2" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486341</v>
+        <v>486298</v>
       </c>
       <c r="R2" t="n">
-        <v>6829217</v>
+        <v>6829599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468989</v>
+        <v>121468996</v>
       </c>
       <c r="B3" t="n">
         <v>78607</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486302</v>
+        <v>486242</v>
       </c>
       <c r="R3" t="n">
-        <v>6829539</v>
+        <v>6829317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468915</v>
+        <v>121468978</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486223</v>
+        <v>486279</v>
       </c>
       <c r="R4" t="n">
-        <v>6829705</v>
+        <v>6829687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468939</v>
+        <v>121468966</v>
       </c>
       <c r="B5" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486265</v>
+        <v>486335</v>
       </c>
       <c r="R5" t="n">
-        <v>6829735</v>
+        <v>6829590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121469034</v>
+        <v>121468976</v>
       </c>
       <c r="B6" t="n">
-        <v>88034</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486298</v>
+        <v>486293</v>
       </c>
       <c r="R6" t="n">
-        <v>6829599</v>
+        <v>6829631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468958</v>
+        <v>121468985</v>
       </c>
       <c r="B7" t="n">
-        <v>80564</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486278</v>
+        <v>486183</v>
       </c>
       <c r="R7" t="n">
-        <v>6829675</v>
+        <v>6829659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121469012</v>
+        <v>121468983</v>
       </c>
       <c r="B8" t="n">
         <v>78607</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486315</v>
+        <v>486213</v>
       </c>
       <c r="R8" t="n">
-        <v>6829368</v>
+        <v>6829683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469020</v>
+        <v>121468946</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486312</v>
+        <v>486392</v>
       </c>
       <c r="R9" t="n">
-        <v>6829467</v>
+        <v>6829119</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468983</v>
+        <v>121469035</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>78252</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1519,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486213</v>
+        <v>486278</v>
       </c>
       <c r="R10" t="n">
-        <v>6829683</v>
+        <v>6829675</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1605,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468993</v>
+        <v>121468968</v>
       </c>
       <c r="B11" t="n">
         <v>78607</v>
@@ -1633,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486272</v>
+        <v>486325</v>
       </c>
       <c r="R11" t="n">
-        <v>6829527</v>
+        <v>6829578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468969</v>
+        <v>121468914</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1723,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,7 +1809,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121468999</v>
+        <v>121469004</v>
       </c>
       <c r="B13" t="n">
         <v>78607</v>
@@ -1837,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486352</v>
+        <v>486442</v>
       </c>
       <c r="R13" t="n">
-        <v>6829165</v>
+        <v>6829128</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469010</v>
+        <v>121468941</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1927,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486366</v>
+        <v>486174</v>
       </c>
       <c r="R14" t="n">
-        <v>6829228</v>
+        <v>6829641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468917</v>
+        <v>121469008</v>
       </c>
       <c r="B15" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2029,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486305</v>
+        <v>486416</v>
       </c>
       <c r="R15" t="n">
-        <v>6829222</v>
+        <v>6829192</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2115,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468966</v>
+        <v>121468993</v>
       </c>
       <c r="B16" t="n">
         <v>78607</v>
@@ -2143,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486335</v>
+        <v>486272</v>
       </c>
       <c r="R16" t="n">
-        <v>6829590</v>
+        <v>6829527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468914</v>
+        <v>121468971</v>
       </c>
       <c r="B17" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486317</v>
+        <v>486309</v>
       </c>
       <c r="R17" t="n">
-        <v>6829572</v>
+        <v>6829581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2319,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468978</v>
+        <v>121469012</v>
       </c>
       <c r="B18" t="n">
         <v>78607</v>
@@ -2347,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486279</v>
+        <v>486315</v>
       </c>
       <c r="R18" t="n">
-        <v>6829687</v>
+        <v>6829368</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469005</v>
+        <v>121468919</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2437,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486438</v>
+        <v>486341</v>
       </c>
       <c r="R19" t="n">
-        <v>6829156</v>
+        <v>6829217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121468954</v>
+        <v>121469023</v>
       </c>
       <c r="B20" t="n">
-        <v>8435</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,47 +2535,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486213</v>
+        <v>486362</v>
       </c>
       <c r="R20" t="n">
-        <v>6829562</v>
+        <v>6829525</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,7 +2607,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468931</v>
+        <v>121469007</v>
       </c>
       <c r="B21" t="n">
-        <v>78641</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486202</v>
+        <v>486432</v>
       </c>
       <c r="R21" t="n">
-        <v>6829676</v>
+        <v>6829183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468934</v>
+        <v>121468939</v>
       </c>
       <c r="B22" t="n">
-        <v>78641</v>
+        <v>79196</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2743,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486318</v>
+        <v>486265</v>
       </c>
       <c r="R22" t="n">
-        <v>6829376</v>
+        <v>6829735</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2829,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468994</v>
+        <v>121469013</v>
       </c>
       <c r="B23" t="n">
         <v>78607</v>
@@ -2867,10 +2869,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486261</v>
+        <v>486318</v>
       </c>
       <c r="R23" t="n">
-        <v>6829525</v>
+        <v>6829376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2931,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469024</v>
+        <v>121469020</v>
       </c>
       <c r="B24" t="n">
         <v>78607</v>
@@ -2969,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486351</v>
+        <v>486312</v>
       </c>
       <c r="R24" t="n">
-        <v>6829541</v>
+        <v>6829467</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3033,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468976</v>
+        <v>121469044</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>78252</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3049,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3073,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486293</v>
+        <v>486236</v>
       </c>
       <c r="R25" t="n">
-        <v>6829631</v>
+        <v>6829512</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3135,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468940</v>
+        <v>121468999</v>
       </c>
       <c r="B26" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3151,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486207</v>
+        <v>486352</v>
       </c>
       <c r="R26" t="n">
-        <v>6829684</v>
+        <v>6829165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,7 +3237,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121468992</v>
+        <v>121469009</v>
       </c>
       <c r="B27" t="n">
         <v>78607</v>
@@ -3275,10 +3277,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486291</v>
+        <v>486396</v>
       </c>
       <c r="R27" t="n">
-        <v>6829537</v>
+        <v>6829190</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,7 +3339,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121468995</v>
+        <v>121468991</v>
       </c>
       <c r="B28" t="n">
         <v>78607</v>
@@ -3377,10 +3379,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486256</v>
+        <v>486297</v>
       </c>
       <c r="R28" t="n">
-        <v>6829523</v>
+        <v>6829538</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3441,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469007</v>
+        <v>121469036</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>78252</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3457,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3481,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486432</v>
+        <v>486261</v>
       </c>
       <c r="R29" t="n">
-        <v>6829183</v>
+        <v>6829744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3543,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469008</v>
+        <v>121468932</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>78641</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486416</v>
+        <v>486261</v>
       </c>
       <c r="R30" t="n">
-        <v>6829192</v>
+        <v>6829525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,7 +3645,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468985</v>
+        <v>121469010</v>
       </c>
       <c r="B31" t="n">
         <v>78607</v>
@@ -3683,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486183</v>
+        <v>486366</v>
       </c>
       <c r="R31" t="n">
-        <v>6829659</v>
+        <v>6829228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468933</v>
+        <v>121468928</v>
       </c>
       <c r="B32" t="n">
-        <v>78641</v>
+        <v>74713</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3763,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3787,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486317</v>
+        <v>486313</v>
       </c>
       <c r="R32" t="n">
-        <v>6829373</v>
+        <v>6829466</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3849,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468959</v>
+        <v>121468975</v>
       </c>
       <c r="B33" t="n">
-        <v>80564</v>
+        <v>78607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3865,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3889,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486437</v>
+        <v>486298</v>
       </c>
       <c r="R33" t="n">
-        <v>6829174</v>
+        <v>6829621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,7 +3951,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469044</v>
+        <v>121469043</v>
       </c>
       <c r="B34" t="n">
         <v>78252</v>
@@ -3989,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486236</v>
+        <v>486291</v>
       </c>
       <c r="R34" t="n">
-        <v>6829512</v>
+        <v>6829537</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4053,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469046</v>
+        <v>121468931</v>
       </c>
       <c r="B35" t="n">
-        <v>78252</v>
+        <v>78641</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,21 +4069,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4093,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486324</v>
+        <v>486202</v>
       </c>
       <c r="R35" t="n">
-        <v>6829398</v>
+        <v>6829676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4155,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469013</v>
+        <v>121468935</v>
       </c>
       <c r="B36" t="n">
-        <v>78607</v>
+        <v>78641</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,21 +4171,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4195,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486318</v>
+        <v>486323</v>
       </c>
       <c r="R36" t="n">
-        <v>6829376</v>
+        <v>6829408</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4257,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121468927</v>
+        <v>121469027</v>
       </c>
       <c r="B37" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,21 +4273,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486283</v>
+        <v>486370</v>
       </c>
       <c r="R37" t="n">
-        <v>6829532</v>
+        <v>6829559</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,7 +4359,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468982</v>
+        <v>121468977</v>
       </c>
       <c r="B38" t="n">
         <v>78607</v>
@@ -4397,10 +4399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486213</v>
+        <v>486269</v>
       </c>
       <c r="R38" t="n">
-        <v>6829765</v>
+        <v>6829656</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4461,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468918</v>
+        <v>121468998</v>
       </c>
       <c r="B39" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4477,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4501,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486321</v>
+        <v>486366</v>
       </c>
       <c r="R39" t="n">
-        <v>6829248</v>
+        <v>6829176</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4563,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468947</v>
+        <v>121469025</v>
       </c>
       <c r="B40" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4579,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4603,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486213</v>
+        <v>486353</v>
       </c>
       <c r="R40" t="n">
-        <v>6829765</v>
+        <v>6829553</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4665,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469021</v>
+        <v>121468954</v>
       </c>
       <c r="B41" t="n">
-        <v>78607</v>
+        <v>8435</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4675,38 +4677,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486328</v>
+        <v>486213</v>
       </c>
       <c r="R41" t="n">
-        <v>6829486</v>
+        <v>6829562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4747,6 +4758,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4765,7 +4777,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469025</v>
+        <v>121468987</v>
       </c>
       <c r="B42" t="n">
         <v>78607</v>
@@ -4805,10 +4817,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486353</v>
+        <v>486271</v>
       </c>
       <c r="R42" t="n">
-        <v>6829553</v>
+        <v>6829568</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4867,10 +4879,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468955</v>
+        <v>121468969</v>
       </c>
       <c r="B43" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4883,21 +4895,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4919,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486321</v>
+        <v>486317</v>
       </c>
       <c r="R43" t="n">
-        <v>6829248</v>
+        <v>6829572</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,10 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468929</v>
+        <v>121468958</v>
       </c>
       <c r="B44" t="n">
-        <v>78641</v>
+        <v>80564</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4985,21 +4997,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5009,10 +5021,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486309</v>
+        <v>486278</v>
       </c>
       <c r="R44" t="n">
-        <v>6829581</v>
+        <v>6829675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,10 +5083,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468979</v>
+        <v>121468933</v>
       </c>
       <c r="B45" t="n">
-        <v>78607</v>
+        <v>78641</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5087,21 +5099,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5111,10 +5123,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486282</v>
+        <v>486317</v>
       </c>
       <c r="R45" t="n">
-        <v>6829704</v>
+        <v>6829373</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5173,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468932</v>
+        <v>121468947</v>
       </c>
       <c r="B46" t="n">
-        <v>78641</v>
+        <v>57507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5189,21 +5201,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486261</v>
+        <v>486213</v>
       </c>
       <c r="R46" t="n">
-        <v>6829525</v>
+        <v>6829765</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,10 +5287,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469035</v>
+        <v>121468957</v>
       </c>
       <c r="B47" t="n">
-        <v>78252</v>
+        <v>8435</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5287,38 +5299,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486278</v>
+        <v>486210</v>
       </c>
       <c r="R47" t="n">
-        <v>6829675</v>
+        <v>6829556</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,6 +5380,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5377,10 +5399,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469027</v>
+        <v>121468943</v>
       </c>
       <c r="B48" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5393,21 +5415,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5417,10 +5439,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486370</v>
+        <v>486250</v>
       </c>
       <c r="R48" t="n">
-        <v>6829559</v>
+        <v>6829400</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,7 +5501,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468977</v>
+        <v>121469019</v>
       </c>
       <c r="B49" t="n">
         <v>78607</v>
@@ -5519,10 +5541,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486269</v>
+        <v>486309</v>
       </c>
       <c r="R49" t="n">
-        <v>6829656</v>
+        <v>6829468</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5603,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469004</v>
+        <v>121468918</v>
       </c>
       <c r="B50" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5597,21 +5619,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5621,10 +5643,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486442</v>
+        <v>486321</v>
       </c>
       <c r="R50" t="n">
-        <v>6829128</v>
+        <v>6829248</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,10 +5705,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121469006</v>
+        <v>121468937</v>
       </c>
       <c r="B51" t="n">
-        <v>78607</v>
+        <v>78641</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5699,21 +5721,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5723,10 +5745,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486437</v>
+        <v>486310</v>
       </c>
       <c r="R51" t="n">
-        <v>6829175</v>
+        <v>6829463</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5785,10 +5807,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468961</v>
+        <v>121468959</v>
       </c>
       <c r="B52" t="n">
-        <v>78343</v>
+        <v>80564</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5801,21 +5823,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486376</v>
+        <v>486437</v>
       </c>
       <c r="R52" t="n">
-        <v>6829237</v>
+        <v>6829174</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5887,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469018</v>
+        <v>121468922</v>
       </c>
       <c r="B53" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5903,21 +5925,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5949,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486306</v>
+        <v>486376</v>
       </c>
       <c r="R53" t="n">
-        <v>6829450</v>
+        <v>6829237</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5989,10 +6011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469001</v>
+        <v>121468944</v>
       </c>
       <c r="B54" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +6027,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6051,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486374</v>
+        <v>486255</v>
       </c>
       <c r="R54" t="n">
-        <v>6829123</v>
+        <v>6829395</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,7 +6113,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121468970</v>
+        <v>121469028</v>
       </c>
       <c r="B55" t="n">
         <v>78607</v>
@@ -6131,10 +6153,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486315</v>
+        <v>486375</v>
       </c>
       <c r="R55" t="n">
-        <v>6829584</v>
+        <v>6829566</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,10 +6215,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468941</v>
+        <v>121469018</v>
       </c>
       <c r="B56" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6209,21 +6231,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6233,10 +6255,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486174</v>
+        <v>486306</v>
       </c>
       <c r="R56" t="n">
-        <v>6829641</v>
+        <v>6829450</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6317,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469023</v>
+        <v>121469046</v>
       </c>
       <c r="B57" t="n">
-        <v>78607</v>
+        <v>78252</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6311,21 +6333,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6357,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486362</v>
+        <v>486324</v>
       </c>
       <c r="R57" t="n">
-        <v>6829525</v>
+        <v>6829398</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,7 +6419,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468968</v>
+        <v>121468995</v>
       </c>
       <c r="B58" t="n">
         <v>78607</v>
@@ -6437,10 +6459,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486325</v>
+        <v>486256</v>
       </c>
       <c r="R58" t="n">
-        <v>6829578</v>
+        <v>6829523</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6521,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468987</v>
+        <v>121469047</v>
       </c>
       <c r="B59" t="n">
-        <v>78607</v>
+        <v>77539</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6515,21 +6537,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6539,10 +6561,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486271</v>
+        <v>486258</v>
       </c>
       <c r="R59" t="n">
-        <v>6829568</v>
+        <v>6829343</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6703,10 +6725,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468922</v>
+        <v>121468967</v>
       </c>
       <c r="B61" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6719,21 +6741,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6743,10 +6765,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486376</v>
+        <v>486329</v>
       </c>
       <c r="R61" t="n">
-        <v>6829237</v>
+        <v>6829590</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6805,7 +6827,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468975</v>
+        <v>121469024</v>
       </c>
       <c r="B62" t="n">
         <v>78607</v>
@@ -6845,10 +6867,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486298</v>
+        <v>486351</v>
       </c>
       <c r="R62" t="n">
-        <v>6829621</v>
+        <v>6829541</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6929,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468957</v>
+        <v>121468921</v>
       </c>
       <c r="B63" t="n">
-        <v>8435</v>
+        <v>79225</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6919,47 +6941,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486210</v>
+        <v>486365</v>
       </c>
       <c r="R63" t="n">
-        <v>6829556</v>
+        <v>6829163</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7000,7 +7013,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7019,10 +7031,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468946</v>
+        <v>121468915</v>
       </c>
       <c r="B64" t="n">
-        <v>57507</v>
+        <v>79225</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7035,46 +7047,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486392</v>
+        <v>486223</v>
       </c>
       <c r="R64" t="n">
-        <v>6829119</v>
+        <v>6829705</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7133,10 +7133,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468928</v>
+        <v>121468929</v>
       </c>
       <c r="B65" t="n">
-        <v>74713</v>
+        <v>78641</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7149,21 +7149,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486313</v>
+        <v>486309</v>
       </c>
       <c r="R65" t="n">
-        <v>6829466</v>
+        <v>6829581</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7235,10 +7235,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468921</v>
+        <v>121468982</v>
       </c>
       <c r="B66" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486365</v>
+        <v>486213</v>
       </c>
       <c r="R66" t="n">
-        <v>6829163</v>
+        <v>6829765</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468986</v>
+        <v>121468989</v>
       </c>
       <c r="B67" t="n">
         <v>78607</v>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486259</v>
+        <v>486302</v>
       </c>
       <c r="R67" t="n">
-        <v>6829565</v>
+        <v>6829539</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7439,7 +7439,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468984</v>
+        <v>121468986</v>
       </c>
       <c r="B68" t="n">
         <v>78607</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486202</v>
+        <v>486259</v>
       </c>
       <c r="R68" t="n">
-        <v>6829676</v>
+        <v>6829565</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468996</v>
+        <v>121468942</v>
       </c>
       <c r="B69" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486242</v>
+        <v>486165</v>
       </c>
       <c r="R69" t="n">
-        <v>6829317</v>
+        <v>6829633</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7643,10 +7643,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469028</v>
+        <v>121468927</v>
       </c>
       <c r="B70" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7659,21 +7659,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486375</v>
+        <v>486283</v>
       </c>
       <c r="R70" t="n">
-        <v>6829566</v>
+        <v>6829532</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7745,7 +7745,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468971</v>
+        <v>121468992</v>
       </c>
       <c r="B71" t="n">
         <v>78607</v>
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486309</v>
+        <v>486291</v>
       </c>
       <c r="R71" t="n">
-        <v>6829581</v>
+        <v>6829537</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7847,10 +7847,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468943</v>
+        <v>121469021</v>
       </c>
       <c r="B72" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7863,21 +7863,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486250</v>
+        <v>486328</v>
       </c>
       <c r="R72" t="n">
-        <v>6829400</v>
+        <v>6829486</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7949,7 +7949,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469009</v>
+        <v>121469015</v>
       </c>
       <c r="B73" t="n">
         <v>78607</v>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486396</v>
+        <v>486323</v>
       </c>
       <c r="R73" t="n">
-        <v>6829190</v>
+        <v>6829408</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468935</v>
+        <v>121469045</v>
       </c>
       <c r="B74" t="n">
-        <v>78641</v>
+        <v>78252</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486323</v>
+        <v>486365</v>
       </c>
       <c r="R74" t="n">
-        <v>6829408</v>
+        <v>6829215</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469019</v>
+        <v>121468955</v>
       </c>
       <c r="B75" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8169,21 +8169,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486309</v>
+        <v>486321</v>
       </c>
       <c r="R75" t="n">
-        <v>6829468</v>
+        <v>6829248</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8255,10 +8255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468973</v>
+        <v>121468940</v>
       </c>
       <c r="B76" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8271,21 +8271,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486298</v>
+        <v>486207</v>
       </c>
       <c r="R76" t="n">
-        <v>6829599</v>
+        <v>6829684</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8357,10 +8357,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468937</v>
+        <v>121469001</v>
       </c>
       <c r="B77" t="n">
-        <v>78641</v>
+        <v>78607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8373,21 +8373,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486310</v>
+        <v>486374</v>
       </c>
       <c r="R77" t="n">
-        <v>6829463</v>
+        <v>6829123</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8561,10 +8561,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468942</v>
+        <v>121468938</v>
       </c>
       <c r="B79" t="n">
-        <v>79196</v>
+        <v>78641</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8577,21 +8577,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486165</v>
+        <v>486329</v>
       </c>
       <c r="R79" t="n">
-        <v>6829633</v>
+        <v>6829484</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468944</v>
+        <v>121468979</v>
       </c>
       <c r="B80" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486255</v>
+        <v>486282</v>
       </c>
       <c r="R80" t="n">
-        <v>6829395</v>
+        <v>6829704</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121469045</v>
+        <v>121468934</v>
       </c>
       <c r="B81" t="n">
-        <v>78252</v>
+        <v>78641</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486365</v>
+        <v>486318</v>
       </c>
       <c r="R81" t="n">
-        <v>6829215</v>
+        <v>6829376</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,7 +8867,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468998</v>
+        <v>121468984</v>
       </c>
       <c r="B82" t="n">
         <v>78607</v>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486366</v>
+        <v>486202</v>
       </c>
       <c r="R82" t="n">
-        <v>6829176</v>
+        <v>6829676</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,10 +8969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469017</v>
+        <v>121468917</v>
       </c>
       <c r="B83" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8985,21 +8985,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486335</v>
+        <v>486305</v>
       </c>
       <c r="R83" t="n">
-        <v>6829435</v>
+        <v>6829222</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,7 +9071,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468991</v>
+        <v>121468970</v>
       </c>
       <c r="B84" t="n">
         <v>78607</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486297</v>
+        <v>486315</v>
       </c>
       <c r="R84" t="n">
-        <v>6829538</v>
+        <v>6829584</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469043</v>
+        <v>121469034</v>
       </c>
       <c r="B85" t="n">
-        <v>78252</v>
+        <v>88034</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>510</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486291</v>
+        <v>486298</v>
       </c>
       <c r="R85" t="n">
-        <v>6829537</v>
+        <v>6829599</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469015</v>
+        <v>121469005</v>
       </c>
       <c r="B86" t="n">
         <v>78607</v>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486323</v>
+        <v>486438</v>
       </c>
       <c r="R86" t="n">
-        <v>6829408</v>
+        <v>6829156</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469036</v>
+        <v>121468994</v>
       </c>
       <c r="B87" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9393,21 +9393,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9420,7 +9420,7 @@
         <v>486261</v>
       </c>
       <c r="R87" t="n">
-        <v>6829744</v>
+        <v>6829525</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,10 +9479,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468938</v>
+        <v>121468961</v>
       </c>
       <c r="B88" t="n">
-        <v>78641</v>
+        <v>78343</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9495,21 +9495,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486329</v>
+        <v>486376</v>
       </c>
       <c r="R88" t="n">
-        <v>6829484</v>
+        <v>6829237</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,7 +9581,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468967</v>
+        <v>121469006</v>
       </c>
       <c r="B89" t="n">
         <v>78607</v>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486329</v>
+        <v>486437</v>
       </c>
       <c r="R89" t="n">
-        <v>6829590</v>
+        <v>6829175</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469047</v>
+        <v>121469017</v>
       </c>
       <c r="B90" t="n">
-        <v>77539</v>
+        <v>78607</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9699,21 +9699,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486258</v>
+        <v>486335</v>
       </c>
       <c r="R90" t="n">
-        <v>6829343</v>
+        <v>6829435</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -2523,7 +2523,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469023</v>
+        <v>121469013</v>
       </c>
       <c r="B20" t="n">
         <v>78607</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486362</v>
+        <v>486318</v>
       </c>
       <c r="R20" t="n">
-        <v>6829525</v>
+        <v>6829376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469007</v>
+        <v>121469020</v>
       </c>
       <c r="B21" t="n">
         <v>78607</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486432</v>
+        <v>486312</v>
       </c>
       <c r="R21" t="n">
-        <v>6829183</v>
+        <v>6829467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468939</v>
+        <v>121469044</v>
       </c>
       <c r="B22" t="n">
-        <v>79196</v>
+        <v>78252</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486265</v>
+        <v>486236</v>
       </c>
       <c r="R22" t="n">
-        <v>6829735</v>
+        <v>6829512</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469013</v>
+        <v>121469023</v>
       </c>
       <c r="B23" t="n">
         <v>78607</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486318</v>
+        <v>486362</v>
       </c>
       <c r="R23" t="n">
-        <v>6829376</v>
+        <v>6829525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469020</v>
+        <v>121469007</v>
       </c>
       <c r="B24" t="n">
         <v>78607</v>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486312</v>
+        <v>486432</v>
       </c>
       <c r="R24" t="n">
-        <v>6829467</v>
+        <v>6829183</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469044</v>
+        <v>121468939</v>
       </c>
       <c r="B25" t="n">
-        <v>78252</v>
+        <v>79196</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486236</v>
+        <v>486265</v>
       </c>
       <c r="R25" t="n">
-        <v>6829512</v>
+        <v>6829735</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468987</v>
+        <v>121468958</v>
       </c>
       <c r="B42" t="n">
-        <v>78607</v>
+        <v>80564</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,21 +4793,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486271</v>
+        <v>486278</v>
       </c>
       <c r="R42" t="n">
-        <v>6829568</v>
+        <v>6829675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,7 +4879,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468969</v>
+        <v>121468987</v>
       </c>
       <c r="B43" t="n">
         <v>78607</v>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486317</v>
+        <v>486271</v>
       </c>
       <c r="R43" t="n">
-        <v>6829572</v>
+        <v>6829568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468958</v>
+        <v>121468969</v>
       </c>
       <c r="B44" t="n">
-        <v>80564</v>
+        <v>78607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486278</v>
+        <v>486317</v>
       </c>
       <c r="R44" t="n">
-        <v>6829675</v>
+        <v>6829572</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468947</v>
+        <v>121469019</v>
       </c>
       <c r="B46" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486213</v>
+        <v>486309</v>
       </c>
       <c r="R46" t="n">
-        <v>6829765</v>
+        <v>6829468</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468957</v>
+        <v>121468918</v>
       </c>
       <c r="B47" t="n">
-        <v>8435</v>
+        <v>79225</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5299,47 +5299,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486210</v>
+        <v>486321</v>
       </c>
       <c r="R47" t="n">
-        <v>6829556</v>
+        <v>6829248</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,7 +5371,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5399,10 +5389,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468943</v>
+        <v>121468957</v>
       </c>
       <c r="B48" t="n">
-        <v>79196</v>
+        <v>8435</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5411,38 +5401,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486250</v>
+        <v>486210</v>
       </c>
       <c r="R48" t="n">
-        <v>6829400</v>
+        <v>6829556</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,6 +5482,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5501,10 +5501,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469019</v>
+        <v>121468947</v>
       </c>
       <c r="B49" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5517,21 +5517,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486309</v>
+        <v>486213</v>
       </c>
       <c r="R49" t="n">
-        <v>6829468</v>
+        <v>6829765</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5603,10 +5603,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121468918</v>
+        <v>121468943</v>
       </c>
       <c r="B50" t="n">
-        <v>79225</v>
+        <v>79196</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5619,21 +5619,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486321</v>
+        <v>486250</v>
       </c>
       <c r="R50" t="n">
-        <v>6829248</v>
+        <v>6829400</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468959</v>
+        <v>121468944</v>
       </c>
       <c r="B52" t="n">
-        <v>80564</v>
+        <v>79196</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486437</v>
+        <v>486255</v>
       </c>
       <c r="R52" t="n">
-        <v>6829174</v>
+        <v>6829395</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468922</v>
+        <v>121468959</v>
       </c>
       <c r="B53" t="n">
-        <v>79225</v>
+        <v>80564</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5925,21 +5925,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486376</v>
+        <v>486437</v>
       </c>
       <c r="R53" t="n">
-        <v>6829237</v>
+        <v>6829174</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468944</v>
+        <v>121468922</v>
       </c>
       <c r="B54" t="n">
-        <v>79196</v>
+        <v>79225</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6027,21 +6027,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6051,10 +6051,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486255</v>
+        <v>486376</v>
       </c>
       <c r="R54" t="n">
-        <v>6829395</v>
+        <v>6829237</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7133,10 +7133,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468929</v>
+        <v>121468982</v>
       </c>
       <c r="B65" t="n">
-        <v>78641</v>
+        <v>78607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7149,21 +7149,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486309</v>
+        <v>486213</v>
       </c>
       <c r="R65" t="n">
-        <v>6829581</v>
+        <v>6829765</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7235,10 +7235,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468982</v>
+        <v>121468929</v>
       </c>
       <c r="B66" t="n">
-        <v>78607</v>
+        <v>78641</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486213</v>
+        <v>486309</v>
       </c>
       <c r="R66" t="n">
-        <v>6829765</v>
+        <v>6829581</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7337,10 +7337,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468989</v>
+        <v>121468942</v>
       </c>
       <c r="B67" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7353,21 +7353,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486302</v>
+        <v>486165</v>
       </c>
       <c r="R67" t="n">
-        <v>6829539</v>
+        <v>6829633</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7439,7 +7439,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468986</v>
+        <v>121468989</v>
       </c>
       <c r="B68" t="n">
         <v>78607</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486259</v>
+        <v>486302</v>
       </c>
       <c r="R68" t="n">
-        <v>6829565</v>
+        <v>6829539</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468942</v>
+        <v>121468986</v>
       </c>
       <c r="B69" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486165</v>
+        <v>486259</v>
       </c>
       <c r="R69" t="n">
-        <v>6829633</v>
+        <v>6829565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468979</v>
+        <v>121468934</v>
       </c>
       <c r="B80" t="n">
-        <v>78607</v>
+        <v>78641</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486282</v>
+        <v>486318</v>
       </c>
       <c r="R80" t="n">
-        <v>6829704</v>
+        <v>6829376</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468934</v>
+        <v>121468979</v>
       </c>
       <c r="B81" t="n">
-        <v>78641</v>
+        <v>78607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486318</v>
+        <v>486282</v>
       </c>
       <c r="R81" t="n">
-        <v>6829376</v>
+        <v>6829704</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121468973</v>
+        <v>121468977</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486298</v>
+        <v>486269</v>
       </c>
       <c r="R2" t="n">
-        <v>6829599</v>
+        <v>6829656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468996</v>
+        <v>121468983</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486242</v>
+        <v>486213</v>
       </c>
       <c r="R3" t="n">
-        <v>6829317</v>
+        <v>6829683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468978</v>
+        <v>121468989</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486279</v>
+        <v>486302</v>
       </c>
       <c r="R4" t="n">
-        <v>6829687</v>
+        <v>6829539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468966</v>
+        <v>121468937</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486335</v>
+        <v>486310</v>
       </c>
       <c r="R5" t="n">
-        <v>6829590</v>
+        <v>6829463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468976</v>
+        <v>121468961</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486293</v>
+        <v>486376</v>
       </c>
       <c r="R6" t="n">
-        <v>6829631</v>
+        <v>6829237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468985</v>
+        <v>121468921</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486183</v>
+        <v>486365</v>
       </c>
       <c r="R7" t="n">
-        <v>6829659</v>
+        <v>6829163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468983</v>
+        <v>121468995</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486213</v>
+        <v>486256</v>
       </c>
       <c r="R8" t="n">
-        <v>6829683</v>
+        <v>6829523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468946</v>
+        <v>121469019</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,46 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486392</v>
+        <v>486309</v>
       </c>
       <c r="R9" t="n">
-        <v>6829119</v>
+        <v>6829468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469035</v>
+        <v>121468991</v>
       </c>
       <c r="B10" t="n">
-        <v>78252</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486278</v>
+        <v>486297</v>
       </c>
       <c r="R10" t="n">
-        <v>6829675</v>
+        <v>6829538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468968</v>
+        <v>121468946</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>57508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,34 +1609,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486325</v>
+        <v>486392</v>
       </c>
       <c r="R11" t="n">
-        <v>6829578</v>
+        <v>6829119</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468914</v>
+        <v>121468979</v>
       </c>
       <c r="B12" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486317</v>
+        <v>486282</v>
       </c>
       <c r="R12" t="n">
-        <v>6829572</v>
+        <v>6829704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469004</v>
+        <v>121468978</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486442</v>
+        <v>486279</v>
       </c>
       <c r="R13" t="n">
-        <v>6829128</v>
+        <v>6829687</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468941</v>
+        <v>121469005</v>
       </c>
       <c r="B14" t="n">
-        <v>79196</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,21 +1927,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486174</v>
+        <v>486438</v>
       </c>
       <c r="R14" t="n">
-        <v>6829641</v>
+        <v>6829156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469008</v>
+        <v>121468933</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78642</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486416</v>
+        <v>486317</v>
       </c>
       <c r="R15" t="n">
-        <v>6829192</v>
+        <v>6829373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468993</v>
+        <v>121468959</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>80565</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486272</v>
+        <v>486437</v>
       </c>
       <c r="R16" t="n">
-        <v>6829527</v>
+        <v>6829174</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468971</v>
+        <v>121468935</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>78642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486309</v>
+        <v>486323</v>
       </c>
       <c r="R17" t="n">
-        <v>6829581</v>
+        <v>6829408</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121469012</v>
+        <v>121468957</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>8435</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,38 +2331,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486315</v>
+        <v>486210</v>
       </c>
       <c r="R18" t="n">
-        <v>6829368</v>
+        <v>6829556</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,6 +2412,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2421,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468919</v>
+        <v>121468941</v>
       </c>
       <c r="B19" t="n">
-        <v>79225</v>
+        <v>79197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,21 +2447,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486341</v>
+        <v>486174</v>
       </c>
       <c r="R19" t="n">
-        <v>6829217</v>
+        <v>6829641</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469013</v>
+        <v>121469006</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,10 +2573,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486318</v>
+        <v>486437</v>
       </c>
       <c r="R20" t="n">
-        <v>6829376</v>
+        <v>6829175</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469020</v>
+        <v>121469046</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>78253</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,21 +2651,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486312</v>
+        <v>486324</v>
       </c>
       <c r="R21" t="n">
-        <v>6829467</v>
+        <v>6829398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,10 +2737,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469044</v>
+        <v>121469047</v>
       </c>
       <c r="B22" t="n">
-        <v>78252</v>
+        <v>77540</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,21 +2753,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2767,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486236</v>
+        <v>486258</v>
       </c>
       <c r="R22" t="n">
-        <v>6829512</v>
+        <v>6829343</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2839,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469023</v>
+        <v>121469035</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>78253</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2845,21 +2855,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2869,10 +2879,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486362</v>
+        <v>486278</v>
       </c>
       <c r="R23" t="n">
-        <v>6829525</v>
+        <v>6829675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469007</v>
+        <v>121468984</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2971,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486432</v>
+        <v>486202</v>
       </c>
       <c r="R24" t="n">
-        <v>6829183</v>
+        <v>6829676</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,10 +3043,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468939</v>
+        <v>121469015</v>
       </c>
       <c r="B25" t="n">
-        <v>79196</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,21 +3059,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3073,10 +3083,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486265</v>
+        <v>486323</v>
       </c>
       <c r="R25" t="n">
-        <v>6829735</v>
+        <v>6829408</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3135,10 +3145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468999</v>
+        <v>121468975</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3175,10 +3185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486352</v>
+        <v>486298</v>
       </c>
       <c r="R26" t="n">
-        <v>6829165</v>
+        <v>6829621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3237,10 +3247,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469009</v>
+        <v>121469017</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3277,10 +3287,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486396</v>
+        <v>486335</v>
       </c>
       <c r="R27" t="n">
-        <v>6829190</v>
+        <v>6829435</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3339,10 +3349,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121468991</v>
+        <v>121469028</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3379,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486297</v>
+        <v>486375</v>
       </c>
       <c r="R28" t="n">
-        <v>6829538</v>
+        <v>6829566</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,10 +3451,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469036</v>
+        <v>121468936</v>
       </c>
       <c r="B29" t="n">
-        <v>78252</v>
+        <v>78642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3457,21 +3467,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3481,10 +3491,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486261</v>
+        <v>486335</v>
       </c>
       <c r="R29" t="n">
-        <v>6829744</v>
+        <v>6829435</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,10 +3553,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468932</v>
+        <v>121468947</v>
       </c>
       <c r="B30" t="n">
-        <v>78641</v>
+        <v>57508</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3559,21 +3569,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3593,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486261</v>
+        <v>486213</v>
       </c>
       <c r="R30" t="n">
-        <v>6829525</v>
+        <v>6829765</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469010</v>
+        <v>121468993</v>
       </c>
       <c r="B31" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3685,10 +3695,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486366</v>
+        <v>486272</v>
       </c>
       <c r="R31" t="n">
-        <v>6829228</v>
+        <v>6829527</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,10 +3757,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468928</v>
+        <v>121469021</v>
       </c>
       <c r="B32" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,21 +3773,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3787,10 +3797,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486313</v>
+        <v>486328</v>
       </c>
       <c r="R32" t="n">
-        <v>6829466</v>
+        <v>6829486</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3849,10 +3859,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468975</v>
+        <v>121468985</v>
       </c>
       <c r="B33" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3889,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486298</v>
+        <v>486183</v>
       </c>
       <c r="R33" t="n">
-        <v>6829621</v>
+        <v>6829659</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3951,10 +3961,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469043</v>
+        <v>121468919</v>
       </c>
       <c r="B34" t="n">
-        <v>78252</v>
+        <v>79226</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,21 +3977,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +4001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486291</v>
+        <v>486341</v>
       </c>
       <c r="R34" t="n">
-        <v>6829537</v>
+        <v>6829217</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,10 +4063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468931</v>
+        <v>121468966</v>
       </c>
       <c r="B35" t="n">
-        <v>78641</v>
+        <v>78608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,21 +4079,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4093,10 +4103,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486202</v>
+        <v>486335</v>
       </c>
       <c r="R35" t="n">
-        <v>6829676</v>
+        <v>6829590</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468935</v>
+        <v>121468986</v>
       </c>
       <c r="B36" t="n">
-        <v>78641</v>
+        <v>78608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,21 +4181,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4195,10 +4205,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486323</v>
+        <v>486259</v>
       </c>
       <c r="R36" t="n">
-        <v>6829408</v>
+        <v>6829565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4257,10 +4267,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469027</v>
+        <v>121469034</v>
       </c>
       <c r="B37" t="n">
-        <v>78607</v>
+        <v>88038</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,21 +4283,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4307,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486370</v>
+        <v>486298</v>
       </c>
       <c r="R37" t="n">
-        <v>6829559</v>
+        <v>6829599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4359,10 +4369,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468977</v>
+        <v>121468939</v>
       </c>
       <c r="B38" t="n">
-        <v>78607</v>
+        <v>79197</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,21 +4385,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4399,10 +4409,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486269</v>
+        <v>486265</v>
       </c>
       <c r="R38" t="n">
-        <v>6829656</v>
+        <v>6829735</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4461,10 +4471,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468998</v>
+        <v>121469007</v>
       </c>
       <c r="B39" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4501,10 +4511,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486366</v>
+        <v>486432</v>
       </c>
       <c r="R39" t="n">
-        <v>6829176</v>
+        <v>6829183</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,10 +4573,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469025</v>
+        <v>121468928</v>
       </c>
       <c r="B40" t="n">
-        <v>78607</v>
+        <v>74714</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4579,21 +4589,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4603,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486353</v>
+        <v>486313</v>
       </c>
       <c r="R40" t="n">
-        <v>6829553</v>
+        <v>6829466</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4665,10 +4675,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468954</v>
+        <v>121468958</v>
       </c>
       <c r="B41" t="n">
-        <v>8435</v>
+        <v>80565</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4677,47 +4687,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486213</v>
+        <v>486278</v>
       </c>
       <c r="R41" t="n">
-        <v>6829562</v>
+        <v>6829675</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,7 +4759,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468958</v>
+        <v>121468915</v>
       </c>
       <c r="B42" t="n">
-        <v>80564</v>
+        <v>79226</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,21 +4793,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486278</v>
+        <v>486223</v>
       </c>
       <c r="R42" t="n">
-        <v>6829675</v>
+        <v>6829705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,10 +4879,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468987</v>
+        <v>121468929</v>
       </c>
       <c r="B43" t="n">
-        <v>78607</v>
+        <v>78642</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,21 +4895,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486271</v>
+        <v>486309</v>
       </c>
       <c r="R43" t="n">
-        <v>6829568</v>
+        <v>6829581</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468969</v>
+        <v>121468914</v>
       </c>
       <c r="B44" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468933</v>
+        <v>121469004</v>
       </c>
       <c r="B45" t="n">
-        <v>78641</v>
+        <v>78608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5099,21 +5099,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486317</v>
+        <v>486442</v>
       </c>
       <c r="R45" t="n">
-        <v>6829373</v>
+        <v>6829128</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469019</v>
+        <v>121468996</v>
       </c>
       <c r="B46" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486309</v>
+        <v>486242</v>
       </c>
       <c r="R46" t="n">
-        <v>6829468</v>
+        <v>6829317</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468918</v>
+        <v>121469018</v>
       </c>
       <c r="B47" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5303,21 +5303,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5327,10 +5327,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486321</v>
+        <v>486306</v>
       </c>
       <c r="R47" t="n">
-        <v>6829248</v>
+        <v>6829450</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,10 +5389,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468957</v>
+        <v>121469012</v>
       </c>
       <c r="B48" t="n">
-        <v>8435</v>
+        <v>78608</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5401,47 +5401,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486210</v>
+        <v>486315</v>
       </c>
       <c r="R48" t="n">
-        <v>6829556</v>
+        <v>6829368</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,7 +5473,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5501,10 +5491,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468947</v>
+        <v>121469027</v>
       </c>
       <c r="B49" t="n">
-        <v>57507</v>
+        <v>78608</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5517,21 +5507,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5541,10 +5531,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486213</v>
+        <v>486370</v>
       </c>
       <c r="R49" t="n">
-        <v>6829765</v>
+        <v>6829559</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5603,10 +5593,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121468943</v>
+        <v>121469025</v>
       </c>
       <c r="B50" t="n">
-        <v>79196</v>
+        <v>78608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5619,21 +5609,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5643,10 +5633,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486250</v>
+        <v>486353</v>
       </c>
       <c r="R50" t="n">
-        <v>6829400</v>
+        <v>6829553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5705,10 +5695,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468937</v>
+        <v>121468931</v>
       </c>
       <c r="B51" t="n">
-        <v>78641</v>
+        <v>78642</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5745,10 +5735,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486310</v>
+        <v>486202</v>
       </c>
       <c r="R51" t="n">
-        <v>6829463</v>
+        <v>6829676</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5807,10 +5797,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468944</v>
+        <v>121468938</v>
       </c>
       <c r="B52" t="n">
-        <v>79196</v>
+        <v>78642</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5823,21 +5813,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5837,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486255</v>
+        <v>486329</v>
       </c>
       <c r="R52" t="n">
-        <v>6829395</v>
+        <v>6829484</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5909,10 +5899,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468959</v>
+        <v>121468967</v>
       </c>
       <c r="B53" t="n">
-        <v>80564</v>
+        <v>78608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5925,21 +5915,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5949,10 +5939,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486437</v>
+        <v>486329</v>
       </c>
       <c r="R53" t="n">
-        <v>6829174</v>
+        <v>6829590</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6011,10 +6001,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468922</v>
+        <v>121468999</v>
       </c>
       <c r="B54" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6027,21 +6017,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6051,10 +6041,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486376</v>
+        <v>486352</v>
       </c>
       <c r="R54" t="n">
-        <v>6829237</v>
+        <v>6829165</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6113,10 +6103,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469028</v>
+        <v>121469024</v>
       </c>
       <c r="B55" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6153,10 +6143,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486375</v>
+        <v>486351</v>
       </c>
       <c r="R55" t="n">
-        <v>6829566</v>
+        <v>6829541</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6215,10 +6205,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469018</v>
+        <v>121469036</v>
       </c>
       <c r="B56" t="n">
-        <v>78607</v>
+        <v>78253</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6231,21 +6221,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6255,10 +6245,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486306</v>
+        <v>486261</v>
       </c>
       <c r="R56" t="n">
-        <v>6829450</v>
+        <v>6829744</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6317,10 +6307,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469046</v>
+        <v>121468932</v>
       </c>
       <c r="B57" t="n">
-        <v>78252</v>
+        <v>78642</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6333,21 +6323,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6357,10 +6347,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486324</v>
+        <v>486261</v>
       </c>
       <c r="R57" t="n">
-        <v>6829398</v>
+        <v>6829525</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6419,10 +6409,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468995</v>
+        <v>121468976</v>
       </c>
       <c r="B58" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6459,10 +6449,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486256</v>
+        <v>486293</v>
       </c>
       <c r="R58" t="n">
-        <v>6829523</v>
+        <v>6829631</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6521,10 +6511,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469047</v>
+        <v>121468973</v>
       </c>
       <c r="B59" t="n">
-        <v>77539</v>
+        <v>78608</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6537,21 +6527,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6561,10 +6551,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486258</v>
+        <v>486298</v>
       </c>
       <c r="R59" t="n">
-        <v>6829343</v>
+        <v>6829599</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6623,10 +6613,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468974</v>
+        <v>121469008</v>
       </c>
       <c r="B60" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6663,10 +6653,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486301</v>
+        <v>486416</v>
       </c>
       <c r="R60" t="n">
-        <v>6829606</v>
+        <v>6829192</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6725,10 +6715,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468967</v>
+        <v>121468968</v>
       </c>
       <c r="B61" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6765,10 +6755,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486329</v>
+        <v>486325</v>
       </c>
       <c r="R61" t="n">
-        <v>6829590</v>
+        <v>6829578</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6827,10 +6817,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469024</v>
+        <v>121469009</v>
       </c>
       <c r="B62" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6867,10 +6857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486351</v>
+        <v>486396</v>
       </c>
       <c r="R62" t="n">
-        <v>6829541</v>
+        <v>6829190</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6929,10 +6919,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468921</v>
+        <v>121469044</v>
       </c>
       <c r="B63" t="n">
-        <v>79225</v>
+        <v>78253</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6945,21 +6935,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486365</v>
+        <v>486236</v>
       </c>
       <c r="R63" t="n">
-        <v>6829163</v>
+        <v>6829512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7031,10 +7021,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468915</v>
+        <v>121468917</v>
       </c>
       <c r="B64" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486223</v>
+        <v>486305</v>
       </c>
       <c r="R64" t="n">
-        <v>6829705</v>
+        <v>6829222</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7133,10 +7123,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468982</v>
+        <v>121468944</v>
       </c>
       <c r="B65" t="n">
-        <v>78607</v>
+        <v>79197</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7149,21 +7139,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7173,10 +7163,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486213</v>
+        <v>486255</v>
       </c>
       <c r="R65" t="n">
-        <v>6829765</v>
+        <v>6829395</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7235,10 +7225,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468929</v>
+        <v>121468927</v>
       </c>
       <c r="B66" t="n">
-        <v>78641</v>
+        <v>74714</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7251,21 +7241,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7265,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486309</v>
+        <v>486283</v>
       </c>
       <c r="R66" t="n">
-        <v>6829581</v>
+        <v>6829532</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7337,10 +7327,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468942</v>
+        <v>121468940</v>
       </c>
       <c r="B67" t="n">
-        <v>79196</v>
+        <v>79197</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7377,10 +7367,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486165</v>
+        <v>486207</v>
       </c>
       <c r="R67" t="n">
-        <v>6829633</v>
+        <v>6829684</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7439,10 +7429,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468989</v>
+        <v>121468918</v>
       </c>
       <c r="B68" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7455,21 +7445,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7479,10 +7469,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486302</v>
+        <v>486321</v>
       </c>
       <c r="R68" t="n">
-        <v>6829539</v>
+        <v>6829248</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7541,10 +7531,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468986</v>
+        <v>121469020</v>
       </c>
       <c r="B69" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7581,10 +7571,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486259</v>
+        <v>486312</v>
       </c>
       <c r="R69" t="n">
-        <v>6829565</v>
+        <v>6829467</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7643,10 +7633,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468927</v>
+        <v>121468971</v>
       </c>
       <c r="B70" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7659,21 +7649,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7683,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486283</v>
+        <v>486309</v>
       </c>
       <c r="R70" t="n">
-        <v>6829532</v>
+        <v>6829581</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7745,10 +7735,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468992</v>
+        <v>121468982</v>
       </c>
       <c r="B71" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7785,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486291</v>
+        <v>486213</v>
       </c>
       <c r="R71" t="n">
-        <v>6829537</v>
+        <v>6829765</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7847,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469021</v>
+        <v>121468998</v>
       </c>
       <c r="B72" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7887,10 +7877,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486328</v>
+        <v>486366</v>
       </c>
       <c r="R72" t="n">
-        <v>6829486</v>
+        <v>6829176</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7949,10 +7939,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469015</v>
+        <v>121468943</v>
       </c>
       <c r="B73" t="n">
-        <v>78607</v>
+        <v>79197</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7965,21 +7955,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7989,10 +7979,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486323</v>
+        <v>486250</v>
       </c>
       <c r="R73" t="n">
-        <v>6829408</v>
+        <v>6829400</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8051,10 +8041,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469045</v>
+        <v>121468955</v>
       </c>
       <c r="B74" t="n">
-        <v>78252</v>
+        <v>78345</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8067,21 +8057,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8091,10 +8081,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486365</v>
+        <v>486321</v>
       </c>
       <c r="R74" t="n">
-        <v>6829215</v>
+        <v>6829248</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8153,10 +8143,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468955</v>
+        <v>121469010</v>
       </c>
       <c r="B75" t="n">
-        <v>78344</v>
+        <v>78608</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8169,21 +8159,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8193,10 +8183,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486321</v>
+        <v>486366</v>
       </c>
       <c r="R75" t="n">
-        <v>6829248</v>
+        <v>6829228</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8255,10 +8245,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468940</v>
+        <v>121468969</v>
       </c>
       <c r="B76" t="n">
-        <v>79196</v>
+        <v>78608</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8271,21 +8261,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8295,10 +8285,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486207</v>
+        <v>486317</v>
       </c>
       <c r="R76" t="n">
-        <v>6829684</v>
+        <v>6829572</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8357,10 +8347,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469001</v>
+        <v>121468992</v>
       </c>
       <c r="B77" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8397,10 +8387,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486374</v>
+        <v>486291</v>
       </c>
       <c r="R77" t="n">
-        <v>6829123</v>
+        <v>6829537</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8459,10 +8449,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468936</v>
+        <v>121468954</v>
       </c>
       <c r="B78" t="n">
-        <v>78641</v>
+        <v>8435</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8471,38 +8461,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486335</v>
+        <v>486213</v>
       </c>
       <c r="R78" t="n">
-        <v>6829435</v>
+        <v>6829562</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8543,6 +8542,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8561,10 +8561,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468938</v>
+        <v>121468942</v>
       </c>
       <c r="B79" t="n">
-        <v>78641</v>
+        <v>79197</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8577,21 +8577,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486329</v>
+        <v>486165</v>
       </c>
       <c r="R79" t="n">
-        <v>6829484</v>
+        <v>6829633</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468934</v>
+        <v>121468922</v>
       </c>
       <c r="B80" t="n">
-        <v>78641</v>
+        <v>79226</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486318</v>
+        <v>486376</v>
       </c>
       <c r="R80" t="n">
-        <v>6829376</v>
+        <v>6829237</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468979</v>
+        <v>121468994</v>
       </c>
       <c r="B81" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486282</v>
+        <v>486261</v>
       </c>
       <c r="R81" t="n">
-        <v>6829704</v>
+        <v>6829525</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468984</v>
+        <v>121469023</v>
       </c>
       <c r="B82" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486202</v>
+        <v>486362</v>
       </c>
       <c r="R82" t="n">
-        <v>6829676</v>
+        <v>6829525</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,10 +8969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468917</v>
+        <v>121469013</v>
       </c>
       <c r="B83" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8985,21 +8985,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486305</v>
+        <v>486318</v>
       </c>
       <c r="R83" t="n">
-        <v>6829222</v>
+        <v>6829376</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468970</v>
+        <v>121468934</v>
       </c>
       <c r="B84" t="n">
-        <v>78607</v>
+        <v>78642</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9087,21 +9087,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486315</v>
+        <v>486318</v>
       </c>
       <c r="R84" t="n">
-        <v>6829584</v>
+        <v>6829376</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469034</v>
+        <v>121469045</v>
       </c>
       <c r="B85" t="n">
-        <v>88034</v>
+        <v>78253</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486298</v>
+        <v>486365</v>
       </c>
       <c r="R85" t="n">
-        <v>6829599</v>
+        <v>6829215</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469005</v>
+        <v>121468974</v>
       </c>
       <c r="B86" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486438</v>
+        <v>486301</v>
       </c>
       <c r="R86" t="n">
-        <v>6829156</v>
+        <v>6829606</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468994</v>
+        <v>121468987</v>
       </c>
       <c r="B87" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486261</v>
+        <v>486271</v>
       </c>
       <c r="R87" t="n">
-        <v>6829525</v>
+        <v>6829568</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,10 +9479,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468961</v>
+        <v>121469001</v>
       </c>
       <c r="B88" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9495,21 +9495,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486376</v>
+        <v>486374</v>
       </c>
       <c r="R88" t="n">
-        <v>6829237</v>
+        <v>6829123</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,10 +9581,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469006</v>
+        <v>121468970</v>
       </c>
       <c r="B89" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486437</v>
+        <v>486315</v>
       </c>
       <c r="R89" t="n">
-        <v>6829175</v>
+        <v>6829584</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469017</v>
+        <v>121469043</v>
       </c>
       <c r="B90" t="n">
-        <v>78607</v>
+        <v>78253</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9699,21 +9699,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486335</v>
+        <v>486291</v>
       </c>
       <c r="R90" t="n">
-        <v>6829435</v>
+        <v>6829537</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121468977</v>
+        <v>121468937</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486269</v>
+        <v>486310</v>
       </c>
       <c r="R2" t="n">
-        <v>6829656</v>
+        <v>6829463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468983</v>
+        <v>121468977</v>
       </c>
       <c r="B3" t="n">
         <v>78608</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486213</v>
+        <v>486269</v>
       </c>
       <c r="R3" t="n">
-        <v>6829683</v>
+        <v>6829656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468989</v>
+        <v>121468983</v>
       </c>
       <c r="B4" t="n">
         <v>78608</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486302</v>
+        <v>486213</v>
       </c>
       <c r="R4" t="n">
-        <v>6829539</v>
+        <v>6829683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468937</v>
+        <v>121468989</v>
       </c>
       <c r="B5" t="n">
-        <v>78642</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486310</v>
+        <v>486302</v>
       </c>
       <c r="R5" t="n">
-        <v>6829463</v>
+        <v>6829539</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468933</v>
+        <v>121468957</v>
       </c>
       <c r="B15" t="n">
-        <v>78642</v>
+        <v>8435</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,38 +2025,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486317</v>
+        <v>486210</v>
       </c>
       <c r="R15" t="n">
-        <v>6829373</v>
+        <v>6829556</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,6 +2106,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2115,10 +2125,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468959</v>
+        <v>121468941</v>
       </c>
       <c r="B16" t="n">
-        <v>80565</v>
+        <v>79197</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,21 +2141,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2155,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486437</v>
+        <v>486174</v>
       </c>
       <c r="R16" t="n">
-        <v>6829174</v>
+        <v>6829641</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2217,7 +2227,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468935</v>
+        <v>121468933</v>
       </c>
       <c r="B17" t="n">
         <v>78642</v>
@@ -2257,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486323</v>
+        <v>486317</v>
       </c>
       <c r="R17" t="n">
-        <v>6829408</v>
+        <v>6829373</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2319,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468957</v>
+        <v>121468959</v>
       </c>
       <c r="B18" t="n">
-        <v>8435</v>
+        <v>80565</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,47 +2341,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486210</v>
+        <v>486437</v>
       </c>
       <c r="R18" t="n">
-        <v>6829556</v>
+        <v>6829174</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2412,7 +2413,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468941</v>
+        <v>121468935</v>
       </c>
       <c r="B19" t="n">
-        <v>79197</v>
+        <v>78642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486174</v>
+        <v>486323</v>
       </c>
       <c r="R19" t="n">
-        <v>6829641</v>
+        <v>6829408</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468915</v>
+        <v>121468929</v>
       </c>
       <c r="B42" t="n">
-        <v>79226</v>
+        <v>78642</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,21 +4793,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486223</v>
+        <v>486309</v>
       </c>
       <c r="R42" t="n">
-        <v>6829705</v>
+        <v>6829581</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,10 +4879,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468929</v>
+        <v>121468915</v>
       </c>
       <c r="B43" t="n">
-        <v>78642</v>
+        <v>79226</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,21 +4895,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486309</v>
+        <v>486223</v>
       </c>
       <c r="R43" t="n">
-        <v>6829581</v>
+        <v>6829705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468914</v>
+        <v>121469004</v>
       </c>
       <c r="B44" t="n">
-        <v>79226</v>
+        <v>78608</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486317</v>
+        <v>486442</v>
       </c>
       <c r="R44" t="n">
-        <v>6829572</v>
+        <v>6829128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469004</v>
+        <v>121469018</v>
       </c>
       <c r="B45" t="n">
         <v>78608</v>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486442</v>
+        <v>486306</v>
       </c>
       <c r="R45" t="n">
-        <v>6829128</v>
+        <v>6829450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468996</v>
+        <v>121468914</v>
       </c>
       <c r="B46" t="n">
-        <v>78608</v>
+        <v>79226</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486242</v>
+        <v>486317</v>
       </c>
       <c r="R46" t="n">
-        <v>6829317</v>
+        <v>6829572</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469018</v>
+        <v>121468996</v>
       </c>
       <c r="B47" t="n">
         <v>78608</v>
@@ -5327,10 +5327,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486306</v>
+        <v>486242</v>
       </c>
       <c r="R47" t="n">
-        <v>6829450</v>
+        <v>6829317</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468973</v>
+        <v>121469044</v>
       </c>
       <c r="B59" t="n">
-        <v>78608</v>
+        <v>78253</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6527,21 +6527,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486298</v>
+        <v>486236</v>
       </c>
       <c r="R59" t="n">
-        <v>6829599</v>
+        <v>6829512</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469008</v>
+        <v>121468973</v>
       </c>
       <c r="B60" t="n">
         <v>78608</v>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486416</v>
+        <v>486298</v>
       </c>
       <c r="R60" t="n">
-        <v>6829192</v>
+        <v>6829599</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468968</v>
+        <v>121469008</v>
       </c>
       <c r="B61" t="n">
         <v>78608</v>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486325</v>
+        <v>486416</v>
       </c>
       <c r="R61" t="n">
-        <v>6829578</v>
+        <v>6829192</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6817,7 +6817,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469009</v>
+        <v>121468968</v>
       </c>
       <c r="B62" t="n">
         <v>78608</v>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486396</v>
+        <v>486325</v>
       </c>
       <c r="R62" t="n">
-        <v>6829190</v>
+        <v>6829578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469044</v>
+        <v>121469009</v>
       </c>
       <c r="B63" t="n">
-        <v>78253</v>
+        <v>78608</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486236</v>
+        <v>486396</v>
       </c>
       <c r="R63" t="n">
-        <v>6829512</v>
+        <v>6829190</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7123,10 +7123,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468944</v>
+        <v>121468927</v>
       </c>
       <c r="B65" t="n">
-        <v>79197</v>
+        <v>74714</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486255</v>
+        <v>486283</v>
       </c>
       <c r="R65" t="n">
-        <v>6829395</v>
+        <v>6829532</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7225,10 +7225,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468927</v>
+        <v>121468944</v>
       </c>
       <c r="B66" t="n">
-        <v>74714</v>
+        <v>79197</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7241,21 +7241,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486283</v>
+        <v>486255</v>
       </c>
       <c r="R66" t="n">
-        <v>6829532</v>
+        <v>6829395</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8449,10 +8449,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468954</v>
+        <v>121468942</v>
       </c>
       <c r="B78" t="n">
-        <v>8435</v>
+        <v>79197</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8461,47 +8461,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486213</v>
+        <v>486165</v>
       </c>
       <c r="R78" t="n">
-        <v>6829562</v>
+        <v>6829633</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8542,7 +8533,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8561,10 +8551,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468942</v>
+        <v>121468954</v>
       </c>
       <c r="B79" t="n">
-        <v>79197</v>
+        <v>8435</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8573,38 +8563,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486165</v>
+        <v>486213</v>
       </c>
       <c r="R79" t="n">
-        <v>6829633</v>
+        <v>6829562</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,6 +8644,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468922</v>
+        <v>121469045</v>
       </c>
       <c r="B80" t="n">
-        <v>79226</v>
+        <v>78253</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486376</v>
+        <v>486365</v>
       </c>
       <c r="R80" t="n">
-        <v>6829237</v>
+        <v>6829215</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468994</v>
+        <v>121468922</v>
       </c>
       <c r="B81" t="n">
-        <v>78608</v>
+        <v>79226</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486261</v>
+        <v>486376</v>
       </c>
       <c r="R81" t="n">
-        <v>6829525</v>
+        <v>6829237</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,7 +8867,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469023</v>
+        <v>121468994</v>
       </c>
       <c r="B82" t="n">
         <v>78608</v>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486362</v>
+        <v>486261</v>
       </c>
       <c r="R82" t="n">
         <v>6829525</v>
@@ -8969,7 +8969,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469013</v>
+        <v>121469023</v>
       </c>
       <c r="B83" t="n">
         <v>78608</v>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486318</v>
+        <v>486362</v>
       </c>
       <c r="R83" t="n">
-        <v>6829376</v>
+        <v>6829525</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468934</v>
+        <v>121469013</v>
       </c>
       <c r="B84" t="n">
-        <v>78642</v>
+        <v>78608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9087,21 +9087,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469045</v>
+        <v>121468934</v>
       </c>
       <c r="B85" t="n">
-        <v>78253</v>
+        <v>78642</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486365</v>
+        <v>486318</v>
       </c>
       <c r="R85" t="n">
-        <v>6829215</v>
+        <v>6829376</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121468937</v>
+        <v>121469004</v>
       </c>
       <c r="B2" t="n">
-        <v>78642</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486310</v>
+        <v>486442</v>
       </c>
       <c r="R2" t="n">
-        <v>6829463</v>
+        <v>6829128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468977</v>
+        <v>121469005</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486269</v>
+        <v>486438</v>
       </c>
       <c r="R3" t="n">
-        <v>6829656</v>
+        <v>6829156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468983</v>
+        <v>121468947</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>486213</v>
       </c>
       <c r="R4" t="n">
-        <v>6829683</v>
+        <v>6829765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468989</v>
+        <v>121469028</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486302</v>
+        <v>486375</v>
       </c>
       <c r="R5" t="n">
-        <v>6829539</v>
+        <v>6829566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468961</v>
+        <v>121468955</v>
       </c>
       <c r="B6" t="n">
-        <v>78344</v>
+        <v>78346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486376</v>
+        <v>486321</v>
       </c>
       <c r="R6" t="n">
-        <v>6829237</v>
+        <v>6829248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468921</v>
+        <v>121468931</v>
       </c>
       <c r="B7" t="n">
-        <v>79226</v>
+        <v>78643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486365</v>
+        <v>486202</v>
       </c>
       <c r="R7" t="n">
-        <v>6829163</v>
+        <v>6829676</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468995</v>
+        <v>121468937</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486256</v>
+        <v>486310</v>
       </c>
       <c r="R8" t="n">
-        <v>6829523</v>
+        <v>6829463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469019</v>
+        <v>121468942</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>79198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486309</v>
+        <v>486165</v>
       </c>
       <c r="R9" t="n">
-        <v>6829468</v>
+        <v>6829633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468991</v>
+        <v>121469043</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486297</v>
+        <v>486291</v>
       </c>
       <c r="R10" t="n">
-        <v>6829538</v>
+        <v>6829537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468946</v>
+        <v>121468978</v>
       </c>
       <c r="B11" t="n">
-        <v>57508</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,46 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486392</v>
+        <v>486279</v>
       </c>
       <c r="R11" t="n">
-        <v>6829119</v>
+        <v>6829687</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468979</v>
+        <v>121468933</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486282</v>
+        <v>486317</v>
       </c>
       <c r="R12" t="n">
-        <v>6829704</v>
+        <v>6829373</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121468978</v>
+        <v>121469036</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1849,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486279</v>
+        <v>486261</v>
       </c>
       <c r="R13" t="n">
-        <v>6829687</v>
+        <v>6829744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469005</v>
+        <v>121469027</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486438</v>
+        <v>486370</v>
       </c>
       <c r="R14" t="n">
-        <v>6829156</v>
+        <v>6829559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468957</v>
+        <v>121468915</v>
       </c>
       <c r="B15" t="n">
-        <v>8435</v>
+        <v>79227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,47 +2013,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486210</v>
+        <v>486223</v>
       </c>
       <c r="R15" t="n">
-        <v>6829556</v>
+        <v>6829705</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,7 +2085,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2125,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468941</v>
+        <v>121468979</v>
       </c>
       <c r="B16" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2141,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486174</v>
+        <v>486282</v>
       </c>
       <c r="R16" t="n">
-        <v>6829641</v>
+        <v>6829704</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2227,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468933</v>
+        <v>121469013</v>
       </c>
       <c r="B17" t="n">
-        <v>78642</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2243,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2267,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486317</v>
+        <v>486318</v>
       </c>
       <c r="R17" t="n">
-        <v>6829373</v>
+        <v>6829376</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2329,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468959</v>
+        <v>121468984</v>
       </c>
       <c r="B18" t="n">
-        <v>80565</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2345,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2369,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486437</v>
+        <v>486202</v>
       </c>
       <c r="R18" t="n">
-        <v>6829174</v>
+        <v>6829676</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2431,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468935</v>
+        <v>121468943</v>
       </c>
       <c r="B19" t="n">
-        <v>78642</v>
+        <v>79198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2471,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486323</v>
+        <v>486250</v>
       </c>
       <c r="R19" t="n">
-        <v>6829408</v>
+        <v>6829400</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469006</v>
+        <v>121468935</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2549,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2573,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486437</v>
+        <v>486323</v>
       </c>
       <c r="R20" t="n">
-        <v>6829175</v>
+        <v>6829408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469046</v>
+        <v>121469023</v>
       </c>
       <c r="B21" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486324</v>
+        <v>486362</v>
       </c>
       <c r="R21" t="n">
-        <v>6829398</v>
+        <v>6829525</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2737,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469047</v>
+        <v>121468999</v>
       </c>
       <c r="B22" t="n">
-        <v>77540</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2753,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2777,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486258</v>
+        <v>486352</v>
       </c>
       <c r="R22" t="n">
-        <v>6829343</v>
+        <v>6829165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2839,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469035</v>
+        <v>121468917</v>
       </c>
       <c r="B23" t="n">
-        <v>78253</v>
+        <v>79227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2855,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2879,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486278</v>
+        <v>486305</v>
       </c>
       <c r="R23" t="n">
-        <v>6829675</v>
+        <v>6829222</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468984</v>
+        <v>121468968</v>
       </c>
       <c r="B24" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2981,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486202</v>
+        <v>486325</v>
       </c>
       <c r="R24" t="n">
-        <v>6829676</v>
+        <v>6829578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3043,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469015</v>
+        <v>121469007</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486323</v>
+        <v>486432</v>
       </c>
       <c r="R25" t="n">
-        <v>6829408</v>
+        <v>6829183</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468975</v>
+        <v>121468944</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>79198</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3161,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3185,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486298</v>
+        <v>486255</v>
       </c>
       <c r="R26" t="n">
-        <v>6829621</v>
+        <v>6829395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469017</v>
+        <v>121468936</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3263,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3349,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469028</v>
+        <v>121468966</v>
       </c>
       <c r="B28" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3389,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486375</v>
+        <v>486335</v>
       </c>
       <c r="R28" t="n">
-        <v>6829566</v>
+        <v>6829590</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121468936</v>
+        <v>121468941</v>
       </c>
       <c r="B29" t="n">
-        <v>78642</v>
+        <v>79198</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3467,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3491,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486335</v>
+        <v>486174</v>
       </c>
       <c r="R29" t="n">
-        <v>6829435</v>
+        <v>6829641</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468947</v>
+        <v>121469001</v>
       </c>
       <c r="B30" t="n">
-        <v>57508</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3569,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3593,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486213</v>
+        <v>486374</v>
       </c>
       <c r="R30" t="n">
-        <v>6829765</v>
+        <v>6829123</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468993</v>
+        <v>121469009</v>
       </c>
       <c r="B31" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3695,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486272</v>
+        <v>486396</v>
       </c>
       <c r="R31" t="n">
-        <v>6829527</v>
+        <v>6829190</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3757,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469021</v>
+        <v>121469045</v>
       </c>
       <c r="B32" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3773,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3797,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486328</v>
+        <v>486365</v>
       </c>
       <c r="R32" t="n">
-        <v>6829486</v>
+        <v>6829215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468985</v>
+        <v>121468940</v>
       </c>
       <c r="B33" t="n">
-        <v>78608</v>
+        <v>79198</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3875,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486183</v>
+        <v>486207</v>
       </c>
       <c r="R33" t="n">
-        <v>6829659</v>
+        <v>6829684</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3961,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468919</v>
+        <v>121468961</v>
       </c>
       <c r="B34" t="n">
-        <v>79226</v>
+        <v>78345</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3977,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4001,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486341</v>
+        <v>486376</v>
       </c>
       <c r="R34" t="n">
-        <v>6829217</v>
+        <v>6829237</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4063,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468966</v>
+        <v>121468914</v>
       </c>
       <c r="B35" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4079,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4103,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486335</v>
+        <v>486317</v>
       </c>
       <c r="R35" t="n">
-        <v>6829590</v>
+        <v>6829572</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468986</v>
+        <v>121469035</v>
       </c>
       <c r="B36" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4181,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4205,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486259</v>
+        <v>486278</v>
       </c>
       <c r="R36" t="n">
-        <v>6829565</v>
+        <v>6829675</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4267,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469034</v>
+        <v>121469047</v>
       </c>
       <c r="B37" t="n">
-        <v>88038</v>
+        <v>77541</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4283,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4307,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486298</v>
+        <v>486258</v>
       </c>
       <c r="R37" t="n">
-        <v>6829599</v>
+        <v>6829343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468939</v>
+        <v>121468967</v>
       </c>
       <c r="B38" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4385,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4409,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486265</v>
+        <v>486329</v>
       </c>
       <c r="R38" t="n">
-        <v>6829735</v>
+        <v>6829590</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121469007</v>
+        <v>121468957</v>
       </c>
       <c r="B39" t="n">
-        <v>78608</v>
+        <v>8435</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4483,38 +4461,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486432</v>
+        <v>486210</v>
       </c>
       <c r="R39" t="n">
-        <v>6829183</v>
+        <v>6829556</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4555,6 +4542,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4573,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468928</v>
+        <v>121468969</v>
       </c>
       <c r="B40" t="n">
-        <v>74714</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4589,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4613,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486313</v>
+        <v>486317</v>
       </c>
       <c r="R40" t="n">
-        <v>6829466</v>
+        <v>6829572</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4675,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468958</v>
+        <v>121469024</v>
       </c>
       <c r="B41" t="n">
-        <v>80565</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4691,21 +4679,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4715,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486278</v>
+        <v>486351</v>
       </c>
       <c r="R41" t="n">
-        <v>6829675</v>
+        <v>6829541</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4777,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468929</v>
+        <v>121468989</v>
       </c>
       <c r="B42" t="n">
-        <v>78642</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4817,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486309</v>
+        <v>486302</v>
       </c>
       <c r="R42" t="n">
-        <v>6829581</v>
+        <v>6829539</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468915</v>
+        <v>121468922</v>
       </c>
       <c r="B43" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4919,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486223</v>
+        <v>486376</v>
       </c>
       <c r="R43" t="n">
-        <v>6829705</v>
+        <v>6829237</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4981,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469004</v>
+        <v>121469025</v>
       </c>
       <c r="B44" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486442</v>
+        <v>486353</v>
       </c>
       <c r="R44" t="n">
-        <v>6829128</v>
+        <v>6829553</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5083,10 +5071,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469018</v>
+        <v>121468975</v>
       </c>
       <c r="B45" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5123,10 +5111,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486306</v>
+        <v>486298</v>
       </c>
       <c r="R45" t="n">
-        <v>6829450</v>
+        <v>6829621</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5185,10 +5173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468914</v>
+        <v>121468982</v>
       </c>
       <c r="B46" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5201,21 +5189,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5225,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486317</v>
+        <v>486213</v>
       </c>
       <c r="R46" t="n">
-        <v>6829572</v>
+        <v>6829765</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,10 +5275,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468996</v>
+        <v>121468939</v>
       </c>
       <c r="B47" t="n">
-        <v>78608</v>
+        <v>79198</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5303,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5327,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486242</v>
+        <v>486265</v>
       </c>
       <c r="R47" t="n">
-        <v>6829317</v>
+        <v>6829735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469012</v>
+        <v>121468994</v>
       </c>
       <c r="B48" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5429,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486315</v>
+        <v>486261</v>
       </c>
       <c r="R48" t="n">
-        <v>6829368</v>
+        <v>6829525</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,10 +5479,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469027</v>
+        <v>121468996</v>
       </c>
       <c r="B49" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5531,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486370</v>
+        <v>486242</v>
       </c>
       <c r="R49" t="n">
-        <v>6829559</v>
+        <v>6829317</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5593,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469025</v>
+        <v>121469017</v>
       </c>
       <c r="B50" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5633,10 +5621,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486353</v>
+        <v>486335</v>
       </c>
       <c r="R50" t="n">
-        <v>6829553</v>
+        <v>6829435</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,10 +5683,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468931</v>
+        <v>121468959</v>
       </c>
       <c r="B51" t="n">
-        <v>78642</v>
+        <v>80566</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5711,21 +5699,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5735,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486202</v>
+        <v>486437</v>
       </c>
       <c r="R51" t="n">
-        <v>6829676</v>
+        <v>6829174</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5797,10 +5785,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468938</v>
+        <v>121468958</v>
       </c>
       <c r="B52" t="n">
-        <v>78642</v>
+        <v>80566</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5813,21 +5801,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5837,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486329</v>
+        <v>486278</v>
       </c>
       <c r="R52" t="n">
-        <v>6829484</v>
+        <v>6829675</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5899,10 +5887,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468967</v>
+        <v>121469008</v>
       </c>
       <c r="B53" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5939,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486329</v>
+        <v>486416</v>
       </c>
       <c r="R53" t="n">
-        <v>6829590</v>
+        <v>6829192</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6001,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468999</v>
+        <v>121469044</v>
       </c>
       <c r="B54" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6017,21 +6005,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6041,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486352</v>
+        <v>486236</v>
       </c>
       <c r="R54" t="n">
-        <v>6829165</v>
+        <v>6829512</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6103,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469024</v>
+        <v>121468929</v>
       </c>
       <c r="B55" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6119,21 +6107,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6143,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486351</v>
+        <v>486309</v>
       </c>
       <c r="R55" t="n">
-        <v>6829541</v>
+        <v>6829581</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6205,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469036</v>
+        <v>121469018</v>
       </c>
       <c r="B56" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6221,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6245,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486261</v>
+        <v>486306</v>
       </c>
       <c r="R56" t="n">
-        <v>6829744</v>
+        <v>6829450</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6307,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468932</v>
+        <v>121468983</v>
       </c>
       <c r="B57" t="n">
-        <v>78642</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6323,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6347,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486261</v>
+        <v>486213</v>
       </c>
       <c r="R57" t="n">
-        <v>6829525</v>
+        <v>6829683</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6409,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468976</v>
+        <v>121469015</v>
       </c>
       <c r="B58" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6449,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486293</v>
+        <v>486323</v>
       </c>
       <c r="R58" t="n">
-        <v>6829631</v>
+        <v>6829408</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6511,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469044</v>
+        <v>121469006</v>
       </c>
       <c r="B59" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6527,21 +6515,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6551,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486236</v>
+        <v>486437</v>
       </c>
       <c r="R59" t="n">
-        <v>6829512</v>
+        <v>6829175</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6613,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468973</v>
+        <v>121468946</v>
       </c>
       <c r="B60" t="n">
-        <v>78608</v>
+        <v>57509</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6629,34 +6617,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486298</v>
+        <v>486392</v>
       </c>
       <c r="R60" t="n">
-        <v>6829599</v>
+        <v>6829119</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469008</v>
+        <v>121469034</v>
       </c>
       <c r="B61" t="n">
-        <v>78608</v>
+        <v>88039</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6731,21 +6731,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486416</v>
+        <v>486298</v>
       </c>
       <c r="R61" t="n">
-        <v>6829192</v>
+        <v>6829599</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468968</v>
+        <v>121469021</v>
       </c>
       <c r="B62" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486325</v>
+        <v>486328</v>
       </c>
       <c r="R62" t="n">
-        <v>6829578</v>
+        <v>6829486</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121469009</v>
+        <v>121468976</v>
       </c>
       <c r="B63" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486396</v>
+        <v>486293</v>
       </c>
       <c r="R63" t="n">
-        <v>6829190</v>
+        <v>6829631</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7021,10 +7021,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468917</v>
+        <v>121469046</v>
       </c>
       <c r="B64" t="n">
-        <v>79226</v>
+        <v>78254</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7037,21 +7037,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486305</v>
+        <v>486324</v>
       </c>
       <c r="R64" t="n">
-        <v>6829222</v>
+        <v>6829398</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7123,10 +7123,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468927</v>
+        <v>121468934</v>
       </c>
       <c r="B65" t="n">
-        <v>74714</v>
+        <v>78643</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486283</v>
+        <v>486318</v>
       </c>
       <c r="R65" t="n">
-        <v>6829532</v>
+        <v>6829376</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7225,10 +7225,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468944</v>
+        <v>121469012</v>
       </c>
       <c r="B66" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7241,21 +7241,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486255</v>
+        <v>486315</v>
       </c>
       <c r="R66" t="n">
-        <v>6829395</v>
+        <v>6829368</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7327,10 +7327,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468940</v>
+        <v>121468973</v>
       </c>
       <c r="B67" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7343,21 +7343,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486207</v>
+        <v>486298</v>
       </c>
       <c r="R67" t="n">
-        <v>6829684</v>
+        <v>6829599</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7429,10 +7429,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468918</v>
+        <v>121468987</v>
       </c>
       <c r="B68" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7445,21 +7445,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486321</v>
+        <v>486271</v>
       </c>
       <c r="R68" t="n">
-        <v>6829248</v>
+        <v>6829568</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121469020</v>
+        <v>121468993</v>
       </c>
       <c r="B69" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486312</v>
+        <v>486272</v>
       </c>
       <c r="R69" t="n">
-        <v>6829467</v>
+        <v>6829527</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7633,10 +7633,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468971</v>
+        <v>121468992</v>
       </c>
       <c r="B70" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486309</v>
+        <v>486291</v>
       </c>
       <c r="R70" t="n">
-        <v>6829581</v>
+        <v>6829537</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7735,10 +7735,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468982</v>
+        <v>121468921</v>
       </c>
       <c r="B71" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7751,21 +7751,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486213</v>
+        <v>486365</v>
       </c>
       <c r="R71" t="n">
-        <v>6829765</v>
+        <v>6829163</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468998</v>
+        <v>121468985</v>
       </c>
       <c r="B72" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486366</v>
+        <v>486183</v>
       </c>
       <c r="R72" t="n">
-        <v>6829176</v>
+        <v>6829659</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468943</v>
+        <v>121468954</v>
       </c>
       <c r="B73" t="n">
-        <v>79197</v>
+        <v>8435</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7951,38 +7951,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486250</v>
+        <v>486213</v>
       </c>
       <c r="R73" t="n">
-        <v>6829400</v>
+        <v>6829562</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,6 +8032,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8041,10 +8051,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468955</v>
+        <v>121469010</v>
       </c>
       <c r="B74" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8057,21 +8067,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8081,10 +8091,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486321</v>
+        <v>486366</v>
       </c>
       <c r="R74" t="n">
-        <v>6829248</v>
+        <v>6829228</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8143,10 +8153,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469010</v>
+        <v>121468970</v>
       </c>
       <c r="B75" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8183,10 +8193,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486366</v>
+        <v>486315</v>
       </c>
       <c r="R75" t="n">
-        <v>6829228</v>
+        <v>6829584</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8245,10 +8255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468969</v>
+        <v>121468986</v>
       </c>
       <c r="B76" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8285,10 +8295,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486317</v>
+        <v>486259</v>
       </c>
       <c r="R76" t="n">
-        <v>6829572</v>
+        <v>6829565</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8347,10 +8357,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468992</v>
+        <v>121468927</v>
       </c>
       <c r="B77" t="n">
-        <v>78608</v>
+        <v>74715</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8363,21 +8373,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8387,10 +8397,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486291</v>
+        <v>486283</v>
       </c>
       <c r="R77" t="n">
-        <v>6829537</v>
+        <v>6829532</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8449,10 +8459,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468942</v>
+        <v>121468998</v>
       </c>
       <c r="B78" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8465,21 +8475,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8489,10 +8499,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486165</v>
+        <v>486366</v>
       </c>
       <c r="R78" t="n">
-        <v>6829633</v>
+        <v>6829176</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8551,10 +8561,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468954</v>
+        <v>121468977</v>
       </c>
       <c r="B79" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8563,47 +8573,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486213</v>
+        <v>486269</v>
       </c>
       <c r="R79" t="n">
-        <v>6829562</v>
+        <v>6829656</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8644,7 +8645,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469045</v>
+        <v>121468918</v>
       </c>
       <c r="B80" t="n">
-        <v>78253</v>
+        <v>79227</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486365</v>
+        <v>486321</v>
       </c>
       <c r="R80" t="n">
-        <v>6829215</v>
+        <v>6829248</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468922</v>
+        <v>121468932</v>
       </c>
       <c r="B81" t="n">
-        <v>79226</v>
+        <v>78643</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486376</v>
+        <v>486261</v>
       </c>
       <c r="R81" t="n">
-        <v>6829237</v>
+        <v>6829525</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468994</v>
+        <v>121468938</v>
       </c>
       <c r="B82" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8883,21 +8883,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486261</v>
+        <v>486329</v>
       </c>
       <c r="R82" t="n">
-        <v>6829525</v>
+        <v>6829484</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,10 +8969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469023</v>
+        <v>121468974</v>
       </c>
       <c r="B83" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486362</v>
+        <v>486301</v>
       </c>
       <c r="R83" t="n">
-        <v>6829525</v>
+        <v>6829606</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469013</v>
+        <v>121469019</v>
       </c>
       <c r="B84" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486318</v>
+        <v>486309</v>
       </c>
       <c r="R84" t="n">
-        <v>6829376</v>
+        <v>6829468</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121468934</v>
+        <v>121468995</v>
       </c>
       <c r="B85" t="n">
-        <v>78642</v>
+        <v>78609</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9189,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486318</v>
+        <v>486256</v>
       </c>
       <c r="R85" t="n">
-        <v>6829376</v>
+        <v>6829523</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121468974</v>
+        <v>121469020</v>
       </c>
       <c r="B86" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486301</v>
+        <v>486312</v>
       </c>
       <c r="R86" t="n">
-        <v>6829606</v>
+        <v>6829467</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468987</v>
+        <v>121468919</v>
       </c>
       <c r="B87" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9393,21 +9393,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486271</v>
+        <v>486341</v>
       </c>
       <c r="R87" t="n">
-        <v>6829568</v>
+        <v>6829217</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,10 +9479,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469001</v>
+        <v>121468971</v>
       </c>
       <c r="B88" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486374</v>
+        <v>486309</v>
       </c>
       <c r="R88" t="n">
-        <v>6829123</v>
+        <v>6829581</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,10 +9581,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468970</v>
+        <v>121468991</v>
       </c>
       <c r="B89" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486315</v>
+        <v>486297</v>
       </c>
       <c r="R89" t="n">
-        <v>6829584</v>
+        <v>6829538</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469043</v>
+        <v>121468928</v>
       </c>
       <c r="B90" t="n">
-        <v>78253</v>
+        <v>74715</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9699,21 +9699,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486291</v>
+        <v>486313</v>
       </c>
       <c r="R90" t="n">
-        <v>6829537</v>
+        <v>6829466</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121469004</v>
+        <v>121469017</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486442</v>
+        <v>486335</v>
       </c>
       <c r="R2" t="n">
-        <v>6829128</v>
+        <v>6829435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121469005</v>
+        <v>121469028</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486438</v>
+        <v>486375</v>
       </c>
       <c r="R3" t="n">
-        <v>6829156</v>
+        <v>6829566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468947</v>
+        <v>121468936</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>78643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486213</v>
+        <v>486335</v>
       </c>
       <c r="R4" t="n">
-        <v>6829765</v>
+        <v>6829435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121469028</v>
+        <v>121468921</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486375</v>
+        <v>486365</v>
       </c>
       <c r="R5" t="n">
-        <v>6829566</v>
+        <v>6829163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468955</v>
+        <v>121468985</v>
       </c>
       <c r="B6" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486321</v>
+        <v>486183</v>
       </c>
       <c r="R6" t="n">
-        <v>6829248</v>
+        <v>6829659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468931</v>
+        <v>121468971</v>
       </c>
       <c r="B7" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486202</v>
+        <v>486309</v>
       </c>
       <c r="R7" t="n">
-        <v>6829676</v>
+        <v>6829581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468937</v>
+        <v>121469010</v>
       </c>
       <c r="B8" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486310</v>
+        <v>486366</v>
       </c>
       <c r="R8" t="n">
-        <v>6829463</v>
+        <v>6829228</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468942</v>
+        <v>121468984</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486165</v>
+        <v>486202</v>
       </c>
       <c r="R9" t="n">
-        <v>6829633</v>
+        <v>6829676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469043</v>
+        <v>121468987</v>
       </c>
       <c r="B10" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486291</v>
+        <v>486271</v>
       </c>
       <c r="R10" t="n">
-        <v>6829537</v>
+        <v>6829568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468978</v>
+        <v>121468967</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486279</v>
+        <v>486329</v>
       </c>
       <c r="R11" t="n">
-        <v>6829687</v>
+        <v>6829590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468933</v>
+        <v>121468932</v>
       </c>
       <c r="B12" t="n">
         <v>78643</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486317</v>
+        <v>486261</v>
       </c>
       <c r="R12" t="n">
-        <v>6829373</v>
+        <v>6829525</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469036</v>
+        <v>121468976</v>
       </c>
       <c r="B13" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486261</v>
+        <v>486293</v>
       </c>
       <c r="R13" t="n">
-        <v>6829744</v>
+        <v>6829631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469027</v>
+        <v>121468941</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486370</v>
+        <v>486174</v>
       </c>
       <c r="R14" t="n">
-        <v>6829559</v>
+        <v>6829641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468915</v>
+        <v>121469036</v>
       </c>
       <c r="B15" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486223</v>
+        <v>486261</v>
       </c>
       <c r="R15" t="n">
-        <v>6829705</v>
+        <v>6829744</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468979</v>
+        <v>121468944</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486282</v>
+        <v>486255</v>
       </c>
       <c r="R16" t="n">
-        <v>6829704</v>
+        <v>6829395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469013</v>
+        <v>121468927</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486318</v>
+        <v>486283</v>
       </c>
       <c r="R17" t="n">
-        <v>6829376</v>
+        <v>6829532</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468984</v>
+        <v>121468957</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,38 +2319,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486202</v>
+        <v>486210</v>
       </c>
       <c r="R18" t="n">
-        <v>6829676</v>
+        <v>6829556</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,6 +2400,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2409,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468943</v>
+        <v>121469047</v>
       </c>
       <c r="B19" t="n">
-        <v>79198</v>
+        <v>77541</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486250</v>
+        <v>486258</v>
       </c>
       <c r="R19" t="n">
-        <v>6829400</v>
+        <v>6829343</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121468935</v>
+        <v>121469035</v>
       </c>
       <c r="B20" t="n">
-        <v>78643</v>
+        <v>78254</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486323</v>
+        <v>486278</v>
       </c>
       <c r="R20" t="n">
-        <v>6829408</v>
+        <v>6829675</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469023</v>
+        <v>121468917</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486362</v>
+        <v>486305</v>
       </c>
       <c r="R21" t="n">
-        <v>6829525</v>
+        <v>6829222</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468999</v>
+        <v>121468966</v>
       </c>
       <c r="B22" t="n">
         <v>78609</v>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486352</v>
+        <v>486335</v>
       </c>
       <c r="R22" t="n">
-        <v>6829165</v>
+        <v>6829590</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468917</v>
+        <v>121468978</v>
       </c>
       <c r="B23" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486305</v>
+        <v>486279</v>
       </c>
       <c r="R23" t="n">
-        <v>6829222</v>
+        <v>6829687</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468968</v>
+        <v>121468935</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486325</v>
+        <v>486323</v>
       </c>
       <c r="R24" t="n">
-        <v>6829578</v>
+        <v>6829408</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469007</v>
+        <v>121468919</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486432</v>
+        <v>486341</v>
       </c>
       <c r="R25" t="n">
-        <v>6829183</v>
+        <v>6829217</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468944</v>
+        <v>121469024</v>
       </c>
       <c r="B26" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486255</v>
+        <v>486351</v>
       </c>
       <c r="R26" t="n">
-        <v>6829395</v>
+        <v>6829541</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121468936</v>
+        <v>121468977</v>
       </c>
       <c r="B27" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486335</v>
+        <v>486269</v>
       </c>
       <c r="R27" t="n">
-        <v>6829435</v>
+        <v>6829656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121468966</v>
+        <v>121469009</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -3367,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486335</v>
+        <v>486396</v>
       </c>
       <c r="R28" t="n">
-        <v>6829590</v>
+        <v>6829190</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121468941</v>
+        <v>121468969</v>
       </c>
       <c r="B29" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486174</v>
+        <v>486317</v>
       </c>
       <c r="R29" t="n">
-        <v>6829641</v>
+        <v>6829572</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469001</v>
+        <v>121469006</v>
       </c>
       <c r="B30" t="n">
         <v>78609</v>
@@ -3571,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486374</v>
+        <v>486437</v>
       </c>
       <c r="R30" t="n">
-        <v>6829123</v>
+        <v>6829175</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3643,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469009</v>
+        <v>121469007</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3673,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486396</v>
+        <v>486432</v>
       </c>
       <c r="R31" t="n">
-        <v>6829190</v>
+        <v>6829183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469045</v>
+        <v>121469015</v>
       </c>
       <c r="B32" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486365</v>
+        <v>486323</v>
       </c>
       <c r="R32" t="n">
-        <v>6829215</v>
+        <v>6829408</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468940</v>
+        <v>121468994</v>
       </c>
       <c r="B33" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486207</v>
+        <v>486261</v>
       </c>
       <c r="R33" t="n">
-        <v>6829684</v>
+        <v>6829525</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468961</v>
+        <v>121468918</v>
       </c>
       <c r="B34" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486376</v>
+        <v>486321</v>
       </c>
       <c r="R34" t="n">
-        <v>6829237</v>
+        <v>6829248</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468914</v>
+        <v>121468937</v>
       </c>
       <c r="B35" t="n">
-        <v>79227</v>
+        <v>78643</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4067,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486317</v>
+        <v>486310</v>
       </c>
       <c r="R35" t="n">
-        <v>6829572</v>
+        <v>6829463</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469035</v>
+        <v>121468961</v>
       </c>
       <c r="B36" t="n">
-        <v>78254</v>
+        <v>78345</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4169,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486278</v>
+        <v>486376</v>
       </c>
       <c r="R36" t="n">
-        <v>6829675</v>
+        <v>6829237</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469047</v>
+        <v>121468993</v>
       </c>
       <c r="B37" t="n">
-        <v>77541</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4271,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486258</v>
+        <v>486272</v>
       </c>
       <c r="R37" t="n">
-        <v>6829343</v>
+        <v>6829527</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468967</v>
+        <v>121469044</v>
       </c>
       <c r="B38" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4373,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486329</v>
+        <v>486236</v>
       </c>
       <c r="R38" t="n">
-        <v>6829590</v>
+        <v>6829512</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468957</v>
+        <v>121468992</v>
       </c>
       <c r="B39" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,47 +4471,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486210</v>
+        <v>486291</v>
       </c>
       <c r="R39" t="n">
-        <v>6829556</v>
+        <v>6829537</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4542,7 +4543,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468969</v>
+        <v>121468983</v>
       </c>
       <c r="B40" t="n">
         <v>78609</v>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486317</v>
+        <v>486213</v>
       </c>
       <c r="R40" t="n">
-        <v>6829572</v>
+        <v>6829683</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469024</v>
+        <v>121468939</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486351</v>
+        <v>486265</v>
       </c>
       <c r="R41" t="n">
-        <v>6829541</v>
+        <v>6829735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468989</v>
+        <v>121468943</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486302</v>
+        <v>486250</v>
       </c>
       <c r="R42" t="n">
-        <v>6829539</v>
+        <v>6829400</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468922</v>
+        <v>121469046</v>
       </c>
       <c r="B43" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4883,21 +4883,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486376</v>
+        <v>486324</v>
       </c>
       <c r="R43" t="n">
-        <v>6829237</v>
+        <v>6829398</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,7 +4969,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469025</v>
+        <v>121469019</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486353</v>
+        <v>486309</v>
       </c>
       <c r="R44" t="n">
-        <v>6829553</v>
+        <v>6829468</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468975</v>
+        <v>121468915</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5087,21 +5087,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486298</v>
+        <v>486223</v>
       </c>
       <c r="R45" t="n">
-        <v>6829621</v>
+        <v>6829705</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5173,7 +5173,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468982</v>
+        <v>121468970</v>
       </c>
       <c r="B46" t="n">
         <v>78609</v>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486213</v>
+        <v>486315</v>
       </c>
       <c r="R46" t="n">
-        <v>6829765</v>
+        <v>6829584</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468939</v>
+        <v>121469045</v>
       </c>
       <c r="B47" t="n">
-        <v>79198</v>
+        <v>78254</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486265</v>
+        <v>486365</v>
       </c>
       <c r="R47" t="n">
-        <v>6829735</v>
+        <v>6829215</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468994</v>
+        <v>121469021</v>
       </c>
       <c r="B48" t="n">
         <v>78609</v>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486261</v>
+        <v>486328</v>
       </c>
       <c r="R48" t="n">
-        <v>6829525</v>
+        <v>6829486</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,10 +5479,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468996</v>
+        <v>121468954</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5491,38 +5491,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486242</v>
+        <v>486213</v>
       </c>
       <c r="R49" t="n">
-        <v>6829317</v>
+        <v>6829562</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5563,6 +5572,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5581,7 +5591,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469017</v>
+        <v>121468998</v>
       </c>
       <c r="B50" t="n">
         <v>78609</v>
@@ -5621,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486335</v>
+        <v>486366</v>
       </c>
       <c r="R50" t="n">
-        <v>6829435</v>
+        <v>6829176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468959</v>
+        <v>121468934</v>
       </c>
       <c r="B51" t="n">
-        <v>80566</v>
+        <v>78643</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5699,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5723,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486437</v>
+        <v>486318</v>
       </c>
       <c r="R51" t="n">
-        <v>6829174</v>
+        <v>6829376</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5785,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468958</v>
+        <v>121468999</v>
       </c>
       <c r="B52" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5801,21 +5811,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486278</v>
+        <v>486352</v>
       </c>
       <c r="R52" t="n">
-        <v>6829675</v>
+        <v>6829165</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5887,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469008</v>
+        <v>121468938</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5903,21 +5913,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486416</v>
+        <v>486329</v>
       </c>
       <c r="R53" t="n">
-        <v>6829192</v>
+        <v>6829484</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5989,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469044</v>
+        <v>121468973</v>
       </c>
       <c r="B54" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +6015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486236</v>
+        <v>486298</v>
       </c>
       <c r="R54" t="n">
-        <v>6829512</v>
+        <v>6829599</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121468929</v>
+        <v>121469013</v>
       </c>
       <c r="B55" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6107,21 +6117,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486309</v>
+        <v>486318</v>
       </c>
       <c r="R55" t="n">
-        <v>6829581</v>
+        <v>6829376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,10 +6203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469018</v>
+        <v>121468933</v>
       </c>
       <c r="B56" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6209,21 +6219,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6233,10 +6243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486306</v>
+        <v>486317</v>
       </c>
       <c r="R56" t="n">
-        <v>6829450</v>
+        <v>6829373</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468983</v>
+        <v>121468958</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6311,21 +6321,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6345,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486213</v>
+        <v>486278</v>
       </c>
       <c r="R57" t="n">
-        <v>6829683</v>
+        <v>6829675</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,7 +6407,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469015</v>
+        <v>121469005</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6437,10 +6447,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486323</v>
+        <v>486438</v>
       </c>
       <c r="R58" t="n">
-        <v>6829408</v>
+        <v>6829156</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469006</v>
+        <v>121468942</v>
       </c>
       <c r="B59" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6515,21 +6525,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6539,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486437</v>
+        <v>486165</v>
       </c>
       <c r="R59" t="n">
-        <v>6829175</v>
+        <v>6829633</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468946</v>
+        <v>121468986</v>
       </c>
       <c r="B60" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,46 +6627,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486392</v>
+        <v>486259</v>
       </c>
       <c r="R60" t="n">
-        <v>6829119</v>
+        <v>6829565</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6715,10 +6713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469034</v>
+        <v>121468996</v>
       </c>
       <c r="B61" t="n">
-        <v>88039</v>
+        <v>78609</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6731,21 +6729,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6755,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486298</v>
+        <v>486242</v>
       </c>
       <c r="R61" t="n">
-        <v>6829599</v>
+        <v>6829317</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6817,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469021</v>
+        <v>121468914</v>
       </c>
       <c r="B62" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6833,21 +6831,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6857,10 +6855,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486328</v>
+        <v>486317</v>
       </c>
       <c r="R62" t="n">
-        <v>6829486</v>
+        <v>6829572</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6919,10 +6917,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468976</v>
+        <v>121468931</v>
       </c>
       <c r="B63" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6935,21 +6933,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6959,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486293</v>
+        <v>486202</v>
       </c>
       <c r="R63" t="n">
-        <v>6829631</v>
+        <v>6829676</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7021,10 +7019,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469046</v>
+        <v>121468929</v>
       </c>
       <c r="B64" t="n">
-        <v>78254</v>
+        <v>78643</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7037,21 +7035,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7061,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486324</v>
+        <v>486309</v>
       </c>
       <c r="R64" t="n">
-        <v>6829398</v>
+        <v>6829581</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7123,10 +7121,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468934</v>
+        <v>121469025</v>
       </c>
       <c r="B65" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7139,21 +7137,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7163,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486318</v>
+        <v>486353</v>
       </c>
       <c r="R65" t="n">
-        <v>6829376</v>
+        <v>6829553</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7225,7 +7223,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469012</v>
+        <v>121468991</v>
       </c>
       <c r="B66" t="n">
         <v>78609</v>
@@ -7265,10 +7263,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486315</v>
+        <v>486297</v>
       </c>
       <c r="R66" t="n">
-        <v>6829368</v>
+        <v>6829538</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7327,7 +7325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468973</v>
+        <v>121469012</v>
       </c>
       <c r="B67" t="n">
         <v>78609</v>
@@ -7367,10 +7365,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486298</v>
+        <v>486315</v>
       </c>
       <c r="R67" t="n">
-        <v>6829599</v>
+        <v>6829368</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7429,7 +7427,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468987</v>
+        <v>121469018</v>
       </c>
       <c r="B68" t="n">
         <v>78609</v>
@@ -7469,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486271</v>
+        <v>486306</v>
       </c>
       <c r="R68" t="n">
-        <v>6829568</v>
+        <v>6829450</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7531,10 +7529,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468993</v>
+        <v>121468928</v>
       </c>
       <c r="B69" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7547,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7571,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486272</v>
+        <v>486313</v>
       </c>
       <c r="R69" t="n">
-        <v>6829527</v>
+        <v>6829466</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7633,7 +7631,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468992</v>
+        <v>121469001</v>
       </c>
       <c r="B70" t="n">
         <v>78609</v>
@@ -7673,10 +7671,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486291</v>
+        <v>486374</v>
       </c>
       <c r="R70" t="n">
-        <v>6829537</v>
+        <v>6829123</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7735,10 +7733,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468921</v>
+        <v>121468974</v>
       </c>
       <c r="B71" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7751,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486365</v>
+        <v>486301</v>
       </c>
       <c r="R71" t="n">
-        <v>6829163</v>
+        <v>6829606</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7837,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468985</v>
+        <v>121469034</v>
       </c>
       <c r="B72" t="n">
-        <v>78609</v>
+        <v>88039</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7853,21 +7851,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7877,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486183</v>
+        <v>486298</v>
       </c>
       <c r="R72" t="n">
-        <v>6829659</v>
+        <v>6829599</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7939,10 +7937,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468954</v>
+        <v>121468959</v>
       </c>
       <c r="B73" t="n">
-        <v>8435</v>
+        <v>80566</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7951,47 +7949,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486213</v>
+        <v>486437</v>
       </c>
       <c r="R73" t="n">
-        <v>6829562</v>
+        <v>6829174</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8032,7 +8021,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8051,7 +8039,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469010</v>
+        <v>121468968</v>
       </c>
       <c r="B74" t="n">
         <v>78609</v>
@@ -8091,10 +8079,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486366</v>
+        <v>486325</v>
       </c>
       <c r="R74" t="n">
-        <v>6829228</v>
+        <v>6829578</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8153,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468970</v>
+        <v>121468955</v>
       </c>
       <c r="B75" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8169,21 +8157,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8193,10 +8181,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486315</v>
+        <v>486321</v>
       </c>
       <c r="R75" t="n">
-        <v>6829584</v>
+        <v>6829248</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8255,7 +8243,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468986</v>
+        <v>121469008</v>
       </c>
       <c r="B76" t="n">
         <v>78609</v>
@@ -8295,10 +8283,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486259</v>
+        <v>486416</v>
       </c>
       <c r="R76" t="n">
-        <v>6829565</v>
+        <v>6829192</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8357,10 +8345,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468927</v>
+        <v>121469020</v>
       </c>
       <c r="B77" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8373,21 +8361,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8397,10 +8385,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486283</v>
+        <v>486312</v>
       </c>
       <c r="R77" t="n">
-        <v>6829532</v>
+        <v>6829467</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8459,10 +8447,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468998</v>
+        <v>121469043</v>
       </c>
       <c r="B78" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8475,21 +8463,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8499,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486366</v>
+        <v>486291</v>
       </c>
       <c r="R78" t="n">
-        <v>6829176</v>
+        <v>6829537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8561,7 +8549,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468977</v>
+        <v>121468989</v>
       </c>
       <c r="B79" t="n">
         <v>78609</v>
@@ -8601,10 +8589,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486269</v>
+        <v>486302</v>
       </c>
       <c r="R79" t="n">
-        <v>6829656</v>
+        <v>6829539</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8663,10 +8651,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468918</v>
+        <v>121468940</v>
       </c>
       <c r="B80" t="n">
-        <v>79227</v>
+        <v>79198</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8667,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8691,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486321</v>
+        <v>486207</v>
       </c>
       <c r="R80" t="n">
-        <v>6829248</v>
+        <v>6829684</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,10 +8753,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468932</v>
+        <v>121468922</v>
       </c>
       <c r="B81" t="n">
-        <v>78643</v>
+        <v>79227</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,21 +8769,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486261</v>
+        <v>486376</v>
       </c>
       <c r="R81" t="n">
-        <v>6829525</v>
+        <v>6829237</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,10 +8855,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468938</v>
+        <v>121468979</v>
       </c>
       <c r="B82" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8883,21 +8871,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8907,10 +8895,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486329</v>
+        <v>486282</v>
       </c>
       <c r="R82" t="n">
-        <v>6829484</v>
+        <v>6829704</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,7 +8957,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468974</v>
+        <v>121469023</v>
       </c>
       <c r="B83" t="n">
         <v>78609</v>
@@ -9009,10 +8997,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486301</v>
+        <v>486362</v>
       </c>
       <c r="R83" t="n">
-        <v>6829606</v>
+        <v>6829525</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,7 +9059,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469019</v>
+        <v>121469004</v>
       </c>
       <c r="B84" t="n">
         <v>78609</v>
@@ -9111,10 +9099,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486309</v>
+        <v>486442</v>
       </c>
       <c r="R84" t="n">
-        <v>6829468</v>
+        <v>6829128</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9275,7 +9263,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469020</v>
+        <v>121468975</v>
       </c>
       <c r="B86" t="n">
         <v>78609</v>
@@ -9315,10 +9303,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486312</v>
+        <v>486298</v>
       </c>
       <c r="R86" t="n">
-        <v>6829467</v>
+        <v>6829621</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9365,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468919</v>
+        <v>121469027</v>
       </c>
       <c r="B87" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9393,21 +9381,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9417,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486341</v>
+        <v>486370</v>
       </c>
       <c r="R87" t="n">
-        <v>6829217</v>
+        <v>6829559</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,7 +9467,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468971</v>
+        <v>121468982</v>
       </c>
       <c r="B88" t="n">
         <v>78609</v>
@@ -9519,10 +9507,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486309</v>
+        <v>486213</v>
       </c>
       <c r="R88" t="n">
-        <v>6829581</v>
+        <v>6829765</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,10 +9569,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468991</v>
+        <v>121468947</v>
       </c>
       <c r="B89" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9597,21 +9585,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9621,10 +9609,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486297</v>
+        <v>486213</v>
       </c>
       <c r="R89" t="n">
-        <v>6829538</v>
+        <v>6829765</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,10 +9671,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121468928</v>
+        <v>121468946</v>
       </c>
       <c r="B90" t="n">
-        <v>74715</v>
+        <v>57509</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9699,34 +9687,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486313</v>
+        <v>486392</v>
       </c>
       <c r="R90" t="n">
-        <v>6829466</v>
+        <v>6829119</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121469017</v>
+        <v>121469001</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486335</v>
+        <v>486374</v>
       </c>
       <c r="R2" t="n">
-        <v>6829435</v>
+        <v>6829123</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121469028</v>
+        <v>121468940</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486375</v>
+        <v>486207</v>
       </c>
       <c r="R3" t="n">
-        <v>6829566</v>
+        <v>6829684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468936</v>
+        <v>121468914</v>
       </c>
       <c r="B4" t="n">
-        <v>78643</v>
+        <v>79227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486335</v>
+        <v>486317</v>
       </c>
       <c r="R4" t="n">
-        <v>6829435</v>
+        <v>6829572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468921</v>
+        <v>121468976</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486365</v>
+        <v>486293</v>
       </c>
       <c r="R5" t="n">
-        <v>6829163</v>
+        <v>6829631</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468985</v>
+        <v>121469010</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486183</v>
+        <v>486366</v>
       </c>
       <c r="R6" t="n">
-        <v>6829659</v>
+        <v>6829228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468971</v>
+        <v>121469005</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486309</v>
+        <v>486438</v>
       </c>
       <c r="R7" t="n">
-        <v>6829581</v>
+        <v>6829156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121469010</v>
+        <v>121469035</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486366</v>
+        <v>486278</v>
       </c>
       <c r="R8" t="n">
-        <v>6829228</v>
+        <v>6829675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468984</v>
+        <v>121469046</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486202</v>
+        <v>486324</v>
       </c>
       <c r="R9" t="n">
-        <v>6829676</v>
+        <v>6829398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468987</v>
+        <v>121468979</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486271</v>
+        <v>486282</v>
       </c>
       <c r="R10" t="n">
-        <v>6829568</v>
+        <v>6829704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468967</v>
+        <v>121468968</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486329</v>
+        <v>486325</v>
       </c>
       <c r="R11" t="n">
-        <v>6829590</v>
+        <v>6829578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468932</v>
+        <v>121468939</v>
       </c>
       <c r="B12" t="n">
-        <v>78643</v>
+        <v>79198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486261</v>
+        <v>486265</v>
       </c>
       <c r="R12" t="n">
-        <v>6829525</v>
+        <v>6829735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121468976</v>
+        <v>121469013</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486293</v>
+        <v>486318</v>
       </c>
       <c r="R13" t="n">
-        <v>6829631</v>
+        <v>6829376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468941</v>
+        <v>121468975</v>
       </c>
       <c r="B14" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486174</v>
+        <v>486298</v>
       </c>
       <c r="R14" t="n">
-        <v>6829641</v>
+        <v>6829621</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469036</v>
+        <v>121468973</v>
       </c>
       <c r="B15" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486261</v>
+        <v>486298</v>
       </c>
       <c r="R15" t="n">
-        <v>6829744</v>
+        <v>6829599</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468944</v>
+        <v>121468998</v>
       </c>
       <c r="B16" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486255</v>
+        <v>486366</v>
       </c>
       <c r="R16" t="n">
-        <v>6829395</v>
+        <v>6829176</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468927</v>
+        <v>121468971</v>
       </c>
       <c r="B17" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486283</v>
+        <v>486309</v>
       </c>
       <c r="R17" t="n">
-        <v>6829532</v>
+        <v>6829581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468957</v>
+        <v>121468982</v>
       </c>
       <c r="B18" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,47 +2319,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486210</v>
+        <v>486213</v>
       </c>
       <c r="R18" t="n">
-        <v>6829556</v>
+        <v>6829765</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2391,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469047</v>
+        <v>121469006</v>
       </c>
       <c r="B19" t="n">
-        <v>77541</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486258</v>
+        <v>486437</v>
       </c>
       <c r="R19" t="n">
-        <v>6829343</v>
+        <v>6829175</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469035</v>
+        <v>121469034</v>
       </c>
       <c r="B20" t="n">
-        <v>78254</v>
+        <v>88039</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486278</v>
+        <v>486298</v>
       </c>
       <c r="R20" t="n">
-        <v>6829675</v>
+        <v>6829599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468917</v>
+        <v>121469024</v>
       </c>
       <c r="B21" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486305</v>
+        <v>486351</v>
       </c>
       <c r="R21" t="n">
-        <v>6829222</v>
+        <v>6829541</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468966</v>
+        <v>121468943</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486335</v>
+        <v>486250</v>
       </c>
       <c r="R22" t="n">
-        <v>6829590</v>
+        <v>6829400</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468978</v>
+        <v>121468977</v>
       </c>
       <c r="B23" t="n">
         <v>78609</v>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486279</v>
+        <v>486269</v>
       </c>
       <c r="R23" t="n">
-        <v>6829687</v>
+        <v>6829656</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468935</v>
+        <v>121469028</v>
       </c>
       <c r="B24" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486323</v>
+        <v>486375</v>
       </c>
       <c r="R24" t="n">
-        <v>6829408</v>
+        <v>6829566</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468919</v>
+        <v>121468978</v>
       </c>
       <c r="B25" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486341</v>
+        <v>486279</v>
       </c>
       <c r="R25" t="n">
-        <v>6829217</v>
+        <v>6829687</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469024</v>
+        <v>121469036</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486351</v>
+        <v>486261</v>
       </c>
       <c r="R26" t="n">
-        <v>6829541</v>
+        <v>6829744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121468977</v>
+        <v>121468993</v>
       </c>
       <c r="B27" t="n">
         <v>78609</v>
@@ -3275,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486269</v>
+        <v>486272</v>
       </c>
       <c r="R27" t="n">
-        <v>6829656</v>
+        <v>6829527</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469009</v>
+        <v>121468922</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486396</v>
+        <v>486376</v>
       </c>
       <c r="R28" t="n">
-        <v>6829190</v>
+        <v>6829237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121468969</v>
+        <v>121468927</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486317</v>
+        <v>486283</v>
       </c>
       <c r="R29" t="n">
-        <v>6829572</v>
+        <v>6829532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469006</v>
+        <v>121468915</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486437</v>
+        <v>486223</v>
       </c>
       <c r="R30" t="n">
-        <v>6829175</v>
+        <v>6829705</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,7 +3633,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469007</v>
+        <v>121468999</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3683,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486432</v>
+        <v>486352</v>
       </c>
       <c r="R31" t="n">
-        <v>6829183</v>
+        <v>6829165</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469015</v>
+        <v>121468996</v>
       </c>
       <c r="B32" t="n">
         <v>78609</v>
@@ -3785,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486323</v>
+        <v>486242</v>
       </c>
       <c r="R32" t="n">
-        <v>6829408</v>
+        <v>6829317</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468994</v>
+        <v>121468983</v>
       </c>
       <c r="B33" t="n">
         <v>78609</v>
@@ -3887,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486261</v>
+        <v>486213</v>
       </c>
       <c r="R33" t="n">
-        <v>6829525</v>
+        <v>6829683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468918</v>
+        <v>121469025</v>
       </c>
       <c r="B34" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486321</v>
+        <v>486353</v>
       </c>
       <c r="R34" t="n">
-        <v>6829248</v>
+        <v>6829553</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468937</v>
+        <v>121469019</v>
       </c>
       <c r="B35" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486310</v>
+        <v>486309</v>
       </c>
       <c r="R35" t="n">
-        <v>6829463</v>
+        <v>6829468</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468961</v>
+        <v>121468928</v>
       </c>
       <c r="B36" t="n">
-        <v>78345</v>
+        <v>74715</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486376</v>
+        <v>486313</v>
       </c>
       <c r="R36" t="n">
-        <v>6829237</v>
+        <v>6829466</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121468993</v>
+        <v>121468932</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486272</v>
+        <v>486261</v>
       </c>
       <c r="R37" t="n">
-        <v>6829527</v>
+        <v>6829525</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469044</v>
+        <v>121468931</v>
       </c>
       <c r="B38" t="n">
-        <v>78254</v>
+        <v>78643</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486236</v>
+        <v>486202</v>
       </c>
       <c r="R38" t="n">
-        <v>6829512</v>
+        <v>6829676</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468992</v>
+        <v>121468919</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486291</v>
+        <v>486341</v>
       </c>
       <c r="R39" t="n">
-        <v>6829537</v>
+        <v>6829217</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468983</v>
+        <v>121469044</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486213</v>
+        <v>486236</v>
       </c>
       <c r="R40" t="n">
-        <v>6829683</v>
+        <v>6829512</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468939</v>
+        <v>121468935</v>
       </c>
       <c r="B41" t="n">
-        <v>79198</v>
+        <v>78643</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486265</v>
+        <v>486323</v>
       </c>
       <c r="R41" t="n">
-        <v>6829735</v>
+        <v>6829408</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468943</v>
+        <v>121468995</v>
       </c>
       <c r="B42" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486250</v>
+        <v>486256</v>
       </c>
       <c r="R42" t="n">
-        <v>6829400</v>
+        <v>6829523</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4867,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469046</v>
+        <v>121469008</v>
       </c>
       <c r="B43" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4883,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486324</v>
+        <v>486416</v>
       </c>
       <c r="R43" t="n">
-        <v>6829398</v>
+        <v>6829192</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469019</v>
+        <v>121469004</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5009,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486309</v>
+        <v>486442</v>
       </c>
       <c r="R44" t="n">
-        <v>6829468</v>
+        <v>6829128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468915</v>
+        <v>121469018</v>
       </c>
       <c r="B45" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5087,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5111,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486223</v>
+        <v>486306</v>
       </c>
       <c r="R45" t="n">
-        <v>6829705</v>
+        <v>6829450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5173,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468970</v>
+        <v>121468961</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5189,21 +5179,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486315</v>
+        <v>486376</v>
       </c>
       <c r="R46" t="n">
-        <v>6829584</v>
+        <v>6829237</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469045</v>
+        <v>121469007</v>
       </c>
       <c r="B47" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,21 +5281,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486365</v>
+        <v>486432</v>
       </c>
       <c r="R47" t="n">
-        <v>6829215</v>
+        <v>6829183</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469021</v>
+        <v>121468974</v>
       </c>
       <c r="B48" t="n">
         <v>78609</v>
@@ -5417,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486328</v>
+        <v>486301</v>
       </c>
       <c r="R48" t="n">
-        <v>6829486</v>
+        <v>6829606</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468954</v>
+        <v>121469020</v>
       </c>
       <c r="B49" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5491,47 +5481,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486213</v>
+        <v>486312</v>
       </c>
       <c r="R49" t="n">
-        <v>6829562</v>
+        <v>6829467</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5572,7 +5553,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5591,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121468998</v>
+        <v>121469015</v>
       </c>
       <c r="B50" t="n">
         <v>78609</v>
@@ -5631,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486366</v>
+        <v>486323</v>
       </c>
       <c r="R50" t="n">
-        <v>6829176</v>
+        <v>6829408</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,7 +5673,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468934</v>
+        <v>121468929</v>
       </c>
       <c r="B51" t="n">
         <v>78643</v>
@@ -5733,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486318</v>
+        <v>486309</v>
       </c>
       <c r="R51" t="n">
-        <v>6829376</v>
+        <v>6829581</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468999</v>
+        <v>121468958</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486352</v>
+        <v>486278</v>
       </c>
       <c r="R52" t="n">
-        <v>6829165</v>
+        <v>6829675</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468938</v>
+        <v>121468941</v>
       </c>
       <c r="B53" t="n">
-        <v>78643</v>
+        <v>79198</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,21 +5893,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5917,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486329</v>
+        <v>486174</v>
       </c>
       <c r="R53" t="n">
-        <v>6829484</v>
+        <v>6829641</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +5979,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468973</v>
+        <v>121468944</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,21 +5995,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6019,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486298</v>
+        <v>486255</v>
       </c>
       <c r="R54" t="n">
-        <v>6829599</v>
+        <v>6829395</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6081,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469013</v>
+        <v>121469043</v>
       </c>
       <c r="B55" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6117,21 +6097,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6141,10 +6121,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486318</v>
+        <v>486291</v>
       </c>
       <c r="R55" t="n">
-        <v>6829376</v>
+        <v>6829537</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,7 +6183,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468933</v>
+        <v>121468937</v>
       </c>
       <c r="B56" t="n">
         <v>78643</v>
@@ -6243,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486317</v>
+        <v>486310</v>
       </c>
       <c r="R56" t="n">
-        <v>6829373</v>
+        <v>6829463</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6305,10 +6285,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468958</v>
+        <v>121468994</v>
       </c>
       <c r="B57" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,21 +6301,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6345,10 +6325,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486278</v>
+        <v>486261</v>
       </c>
       <c r="R57" t="n">
-        <v>6829675</v>
+        <v>6829525</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6407,7 +6387,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469005</v>
+        <v>121468992</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6447,10 +6427,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486438</v>
+        <v>486291</v>
       </c>
       <c r="R58" t="n">
-        <v>6829156</v>
+        <v>6829537</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,10 +6489,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468942</v>
+        <v>121468918</v>
       </c>
       <c r="B59" t="n">
-        <v>79198</v>
+        <v>79227</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6525,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6549,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486165</v>
+        <v>486321</v>
       </c>
       <c r="R59" t="n">
-        <v>6829633</v>
+        <v>6829248</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,7 +6591,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468986</v>
+        <v>121468987</v>
       </c>
       <c r="B60" t="n">
         <v>78609</v>
@@ -6651,10 +6631,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486259</v>
+        <v>486271</v>
       </c>
       <c r="R60" t="n">
-        <v>6829565</v>
+        <v>6829568</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,10 +6693,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468996</v>
+        <v>121468936</v>
       </c>
       <c r="B61" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6729,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6753,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486242</v>
+        <v>486335</v>
       </c>
       <c r="R61" t="n">
-        <v>6829317</v>
+        <v>6829435</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6795,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468914</v>
+        <v>121468986</v>
       </c>
       <c r="B62" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6831,21 +6811,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,10 +6835,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486317</v>
+        <v>486259</v>
       </c>
       <c r="R62" t="n">
-        <v>6829572</v>
+        <v>6829565</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,10 +6897,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468931</v>
+        <v>121468917</v>
       </c>
       <c r="B63" t="n">
-        <v>78643</v>
+        <v>79227</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6933,21 +6913,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6957,10 +6937,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486202</v>
+        <v>486305</v>
       </c>
       <c r="R63" t="n">
-        <v>6829676</v>
+        <v>6829222</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,10 +6999,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468929</v>
+        <v>121468989</v>
       </c>
       <c r="B64" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7035,21 +7015,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,10 +7039,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486309</v>
+        <v>486302</v>
       </c>
       <c r="R64" t="n">
-        <v>6829581</v>
+        <v>6829539</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7121,10 +7101,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469025</v>
+        <v>121468934</v>
       </c>
       <c r="B65" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7137,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7161,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486353</v>
+        <v>486318</v>
       </c>
       <c r="R65" t="n">
-        <v>6829553</v>
+        <v>6829376</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,7 +7203,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468991</v>
+        <v>121468969</v>
       </c>
       <c r="B66" t="n">
         <v>78609</v>
@@ -7263,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486297</v>
+        <v>486317</v>
       </c>
       <c r="R66" t="n">
-        <v>6829538</v>
+        <v>6829572</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7325,7 +7305,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469012</v>
+        <v>121469009</v>
       </c>
       <c r="B67" t="n">
         <v>78609</v>
@@ -7365,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486315</v>
+        <v>486396</v>
       </c>
       <c r="R67" t="n">
-        <v>6829368</v>
+        <v>6829190</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,7 +7407,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469018</v>
+        <v>121469023</v>
       </c>
       <c r="B68" t="n">
         <v>78609</v>
@@ -7467,10 +7447,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486306</v>
+        <v>486362</v>
       </c>
       <c r="R68" t="n">
-        <v>6829450</v>
+        <v>6829525</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468928</v>
+        <v>121468966</v>
       </c>
       <c r="B69" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7545,21 +7525,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7549,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486313</v>
+        <v>486335</v>
       </c>
       <c r="R69" t="n">
-        <v>6829466</v>
+        <v>6829590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7631,7 +7611,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469001</v>
+        <v>121469021</v>
       </c>
       <c r="B70" t="n">
         <v>78609</v>
@@ -7671,10 +7651,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486374</v>
+        <v>486328</v>
       </c>
       <c r="R70" t="n">
-        <v>6829123</v>
+        <v>6829486</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7733,10 +7713,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468974</v>
+        <v>121468921</v>
       </c>
       <c r="B71" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7749,21 +7729,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7753,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486301</v>
+        <v>486365</v>
       </c>
       <c r="R71" t="n">
-        <v>6829606</v>
+        <v>6829163</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7815,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469034</v>
+        <v>121468970</v>
       </c>
       <c r="B72" t="n">
-        <v>88039</v>
+        <v>78609</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7851,21 +7831,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7855,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486298</v>
+        <v>486315</v>
       </c>
       <c r="R72" t="n">
-        <v>6829599</v>
+        <v>6829584</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7937,10 +7917,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468959</v>
+        <v>121469027</v>
       </c>
       <c r="B73" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7953,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486437</v>
+        <v>486370</v>
       </c>
       <c r="R73" t="n">
-        <v>6829174</v>
+        <v>6829559</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468968</v>
+        <v>121469045</v>
       </c>
       <c r="B74" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8055,21 +8035,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8079,10 +8059,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486325</v>
+        <v>486365</v>
       </c>
       <c r="R74" t="n">
-        <v>6829578</v>
+        <v>6829215</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8141,10 +8121,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468955</v>
+        <v>121468959</v>
       </c>
       <c r="B75" t="n">
-        <v>78346</v>
+        <v>80566</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8157,21 +8137,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8181,10 +8161,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486321</v>
+        <v>486437</v>
       </c>
       <c r="R75" t="n">
-        <v>6829248</v>
+        <v>6829174</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8243,10 +8223,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469008</v>
+        <v>121468954</v>
       </c>
       <c r="B76" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8255,38 +8235,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486416</v>
+        <v>486213</v>
       </c>
       <c r="R76" t="n">
-        <v>6829192</v>
+        <v>6829562</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8327,6 +8316,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8345,10 +8335,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469020</v>
+        <v>121468957</v>
       </c>
       <c r="B77" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8357,38 +8347,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486312</v>
+        <v>486210</v>
       </c>
       <c r="R77" t="n">
-        <v>6829467</v>
+        <v>6829556</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8429,6 +8428,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469043</v>
+        <v>121468938</v>
       </c>
       <c r="B78" t="n">
-        <v>78254</v>
+        <v>78643</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8463,21 +8463,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486291</v>
+        <v>486329</v>
       </c>
       <c r="R78" t="n">
-        <v>6829537</v>
+        <v>6829484</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8549,10 +8549,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468989</v>
+        <v>121468942</v>
       </c>
       <c r="B79" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8565,21 +8565,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486302</v>
+        <v>486165</v>
       </c>
       <c r="R79" t="n">
-        <v>6829539</v>
+        <v>6829633</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8651,10 +8651,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468940</v>
+        <v>121469012</v>
       </c>
       <c r="B80" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8667,21 +8667,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486207</v>
+        <v>486315</v>
       </c>
       <c r="R80" t="n">
-        <v>6829684</v>
+        <v>6829368</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8753,10 +8753,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468922</v>
+        <v>121468984</v>
       </c>
       <c r="B81" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8769,21 +8769,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486376</v>
+        <v>486202</v>
       </c>
       <c r="R81" t="n">
-        <v>6829237</v>
+        <v>6829676</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8855,7 +8855,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468979</v>
+        <v>121468967</v>
       </c>
       <c r="B82" t="n">
         <v>78609</v>
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486282</v>
+        <v>486329</v>
       </c>
       <c r="R82" t="n">
-        <v>6829704</v>
+        <v>6829590</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8957,7 +8957,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469023</v>
+        <v>121468991</v>
       </c>
       <c r="B83" t="n">
         <v>78609</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486362</v>
+        <v>486297</v>
       </c>
       <c r="R83" t="n">
-        <v>6829525</v>
+        <v>6829538</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9059,7 +9059,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469004</v>
+        <v>121469017</v>
       </c>
       <c r="B84" t="n">
         <v>78609</v>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486442</v>
+        <v>486335</v>
       </c>
       <c r="R84" t="n">
-        <v>6829128</v>
+        <v>6829435</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9161,10 +9161,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121468995</v>
+        <v>121468933</v>
       </c>
       <c r="B85" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9177,21 +9177,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486256</v>
+        <v>486317</v>
       </c>
       <c r="R85" t="n">
-        <v>6829523</v>
+        <v>6829373</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9263,7 +9263,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121468975</v>
+        <v>121468985</v>
       </c>
       <c r="B86" t="n">
         <v>78609</v>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486298</v>
+        <v>486183</v>
       </c>
       <c r="R86" t="n">
-        <v>6829621</v>
+        <v>6829659</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469027</v>
+        <v>121468947</v>
       </c>
       <c r="B87" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9381,21 +9381,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486370</v>
+        <v>486213</v>
       </c>
       <c r="R87" t="n">
-        <v>6829559</v>
+        <v>6829765</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9467,10 +9467,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468982</v>
+        <v>121469047</v>
       </c>
       <c r="B88" t="n">
-        <v>78609</v>
+        <v>77541</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9483,21 +9483,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486213</v>
+        <v>486258</v>
       </c>
       <c r="R88" t="n">
-        <v>6829765</v>
+        <v>6829343</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468947</v>
+        <v>121468955</v>
       </c>
       <c r="B89" t="n">
-        <v>57509</v>
+        <v>78346</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486213</v>
+        <v>486321</v>
       </c>
       <c r="R89" t="n">
-        <v>6829765</v>
+        <v>6829248</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121469001</v>
+        <v>121469012</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486374</v>
+        <v>486315</v>
       </c>
       <c r="R2" t="n">
-        <v>6829123</v>
+        <v>6829368</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468940</v>
+        <v>121469027</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486207</v>
+        <v>486370</v>
       </c>
       <c r="R3" t="n">
-        <v>6829684</v>
+        <v>6829559</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468914</v>
+        <v>121469023</v>
       </c>
       <c r="B4" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486317</v>
+        <v>486362</v>
       </c>
       <c r="R4" t="n">
-        <v>6829572</v>
+        <v>6829525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468976</v>
+        <v>121468933</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486293</v>
+        <v>486317</v>
       </c>
       <c r="R5" t="n">
-        <v>6829631</v>
+        <v>6829373</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121469010</v>
+        <v>121468932</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486366</v>
+        <v>486261</v>
       </c>
       <c r="R6" t="n">
-        <v>6829228</v>
+        <v>6829525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121469005</v>
+        <v>121468947</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486438</v>
+        <v>486213</v>
       </c>
       <c r="R7" t="n">
-        <v>6829156</v>
+        <v>6829765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121469035</v>
+        <v>121468959</v>
       </c>
       <c r="B8" t="n">
-        <v>78254</v>
+        <v>80566</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486278</v>
+        <v>486437</v>
       </c>
       <c r="R8" t="n">
-        <v>6829675</v>
+        <v>6829174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469046</v>
+        <v>121469020</v>
       </c>
       <c r="B9" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486324</v>
+        <v>486312</v>
       </c>
       <c r="R9" t="n">
-        <v>6829398</v>
+        <v>6829467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468979</v>
+        <v>121469008</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486282</v>
+        <v>486416</v>
       </c>
       <c r="R10" t="n">
-        <v>6829704</v>
+        <v>6829192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468968</v>
+        <v>121469028</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486325</v>
+        <v>486375</v>
       </c>
       <c r="R11" t="n">
-        <v>6829578</v>
+        <v>6829566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468939</v>
+        <v>121468976</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486265</v>
+        <v>486293</v>
       </c>
       <c r="R12" t="n">
-        <v>6829735</v>
+        <v>6829631</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469013</v>
+        <v>121469010</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486318</v>
+        <v>486366</v>
       </c>
       <c r="R13" t="n">
-        <v>6829376</v>
+        <v>6829228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468975</v>
+        <v>121469044</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486298</v>
+        <v>486236</v>
       </c>
       <c r="R14" t="n">
-        <v>6829621</v>
+        <v>6829512</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468973</v>
+        <v>121468982</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486298</v>
+        <v>486213</v>
       </c>
       <c r="R15" t="n">
-        <v>6829599</v>
+        <v>6829765</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468998</v>
+        <v>121468984</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486366</v>
+        <v>486202</v>
       </c>
       <c r="R16" t="n">
-        <v>6829176</v>
+        <v>6829676</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468971</v>
+        <v>121468970</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486309</v>
+        <v>486315</v>
       </c>
       <c r="R17" t="n">
-        <v>6829581</v>
+        <v>6829584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468982</v>
+        <v>121468979</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486213</v>
+        <v>486282</v>
       </c>
       <c r="R18" t="n">
-        <v>6829765</v>
+        <v>6829704</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469006</v>
+        <v>121469018</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486437</v>
+        <v>486306</v>
       </c>
       <c r="R19" t="n">
-        <v>6829175</v>
+        <v>6829450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469034</v>
+        <v>121469006</v>
       </c>
       <c r="B20" t="n">
-        <v>88039</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486298</v>
+        <v>486437</v>
       </c>
       <c r="R20" t="n">
-        <v>6829599</v>
+        <v>6829175</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469024</v>
+        <v>121468922</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486351</v>
+        <v>486376</v>
       </c>
       <c r="R21" t="n">
-        <v>6829541</v>
+        <v>6829237</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468943</v>
+        <v>121468917</v>
       </c>
       <c r="B22" t="n">
-        <v>79198</v>
+        <v>79227</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486250</v>
+        <v>486305</v>
       </c>
       <c r="R22" t="n">
-        <v>6829400</v>
+        <v>6829222</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468977</v>
+        <v>121469019</v>
       </c>
       <c r="B23" t="n">
         <v>78609</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486269</v>
+        <v>486309</v>
       </c>
       <c r="R23" t="n">
-        <v>6829656</v>
+        <v>6829468</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469028</v>
+        <v>121469009</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486375</v>
+        <v>486396</v>
       </c>
       <c r="R24" t="n">
-        <v>6829566</v>
+        <v>6829190</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468978</v>
+        <v>121468938</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486279</v>
+        <v>486329</v>
       </c>
       <c r="R25" t="n">
-        <v>6829687</v>
+        <v>6829484</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469036</v>
+        <v>121468994</v>
       </c>
       <c r="B26" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,7 +3166,7 @@
         <v>486261</v>
       </c>
       <c r="R26" t="n">
-        <v>6829744</v>
+        <v>6829525</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121468922</v>
+        <v>121468929</v>
       </c>
       <c r="B28" t="n">
-        <v>79227</v>
+        <v>78643</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486376</v>
+        <v>486309</v>
       </c>
       <c r="R28" t="n">
-        <v>6829237</v>
+        <v>6829581</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121468927</v>
+        <v>121469021</v>
       </c>
       <c r="B29" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486283</v>
+        <v>486328</v>
       </c>
       <c r="R29" t="n">
-        <v>6829532</v>
+        <v>6829486</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468915</v>
+        <v>121468941</v>
       </c>
       <c r="B30" t="n">
-        <v>79227</v>
+        <v>79198</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486223</v>
+        <v>486174</v>
       </c>
       <c r="R30" t="n">
-        <v>6829705</v>
+        <v>6829641</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468999</v>
+        <v>121468968</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486352</v>
+        <v>486325</v>
       </c>
       <c r="R31" t="n">
-        <v>6829165</v>
+        <v>6829578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468996</v>
+        <v>121468936</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486242</v>
+        <v>486335</v>
       </c>
       <c r="R32" t="n">
-        <v>6829317</v>
+        <v>6829435</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468983</v>
+        <v>121469046</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486213</v>
+        <v>486324</v>
       </c>
       <c r="R33" t="n">
-        <v>6829683</v>
+        <v>6829398</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121469025</v>
+        <v>121468919</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486353</v>
+        <v>486341</v>
       </c>
       <c r="R34" t="n">
-        <v>6829553</v>
+        <v>6829217</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469019</v>
+        <v>121469047</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>77541</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486309</v>
+        <v>486258</v>
       </c>
       <c r="R35" t="n">
-        <v>6829468</v>
+        <v>6829343</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468928</v>
+        <v>121468955</v>
       </c>
       <c r="B36" t="n">
-        <v>74715</v>
+        <v>78346</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486313</v>
+        <v>486321</v>
       </c>
       <c r="R36" t="n">
-        <v>6829466</v>
+        <v>6829248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121468932</v>
+        <v>121469005</v>
       </c>
       <c r="B37" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486261</v>
+        <v>486438</v>
       </c>
       <c r="R37" t="n">
-        <v>6829525</v>
+        <v>6829156</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468931</v>
+        <v>121468940</v>
       </c>
       <c r="B38" t="n">
-        <v>78643</v>
+        <v>79198</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486202</v>
+        <v>486207</v>
       </c>
       <c r="R38" t="n">
-        <v>6829676</v>
+        <v>6829684</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468919</v>
+        <v>121468974</v>
       </c>
       <c r="B39" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486341</v>
+        <v>486301</v>
       </c>
       <c r="R39" t="n">
-        <v>6829217</v>
+        <v>6829606</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121469044</v>
+        <v>121468967</v>
       </c>
       <c r="B40" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486236</v>
+        <v>486329</v>
       </c>
       <c r="R40" t="n">
-        <v>6829512</v>
+        <v>6829590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468935</v>
+        <v>121469001</v>
       </c>
       <c r="B41" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486323</v>
+        <v>486374</v>
       </c>
       <c r="R41" t="n">
-        <v>6829408</v>
+        <v>6829123</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468995</v>
+        <v>121469036</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486256</v>
+        <v>486261</v>
       </c>
       <c r="R42" t="n">
-        <v>6829523</v>
+        <v>6829744</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469008</v>
+        <v>121468934</v>
       </c>
       <c r="B43" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486416</v>
+        <v>486318</v>
       </c>
       <c r="R43" t="n">
-        <v>6829192</v>
+        <v>6829376</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469004</v>
+        <v>121468966</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486442</v>
+        <v>486335</v>
       </c>
       <c r="R44" t="n">
-        <v>6829128</v>
+        <v>6829590</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469018</v>
+        <v>121468944</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486306</v>
+        <v>486255</v>
       </c>
       <c r="R45" t="n">
-        <v>6829450</v>
+        <v>6829395</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468961</v>
+        <v>121469034</v>
       </c>
       <c r="B46" t="n">
-        <v>78345</v>
+        <v>88039</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486376</v>
+        <v>486298</v>
       </c>
       <c r="R46" t="n">
-        <v>6829237</v>
+        <v>6829599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469007</v>
+        <v>121468931</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5281,21 +5281,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486432</v>
+        <v>486202</v>
       </c>
       <c r="R47" t="n">
-        <v>6829183</v>
+        <v>6829676</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468974</v>
+        <v>121468915</v>
       </c>
       <c r="B48" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5383,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486301</v>
+        <v>486223</v>
       </c>
       <c r="R48" t="n">
-        <v>6829606</v>
+        <v>6829705</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469020</v>
+        <v>121468921</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486312</v>
+        <v>486365</v>
       </c>
       <c r="R49" t="n">
-        <v>6829467</v>
+        <v>6829163</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469015</v>
+        <v>121468999</v>
       </c>
       <c r="B50" t="n">
         <v>78609</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486323</v>
+        <v>486352</v>
       </c>
       <c r="R50" t="n">
-        <v>6829408</v>
+        <v>6829165</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468929</v>
+        <v>121468971</v>
       </c>
       <c r="B51" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468958</v>
+        <v>121468986</v>
       </c>
       <c r="B52" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486278</v>
+        <v>486259</v>
       </c>
       <c r="R52" t="n">
-        <v>6829675</v>
+        <v>6829565</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5877,7 +5877,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468941</v>
+        <v>121468939</v>
       </c>
       <c r="B53" t="n">
         <v>79198</v>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486174</v>
+        <v>486265</v>
       </c>
       <c r="R53" t="n">
-        <v>6829641</v>
+        <v>6829735</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468944</v>
+        <v>121468954</v>
       </c>
       <c r="B54" t="n">
-        <v>79198</v>
+        <v>8435</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5991,38 +5991,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486255</v>
+        <v>486213</v>
       </c>
       <c r="R54" t="n">
-        <v>6829395</v>
+        <v>6829562</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6063,6 +6072,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6081,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469043</v>
+        <v>121468943</v>
       </c>
       <c r="B55" t="n">
-        <v>78254</v>
+        <v>79198</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6097,21 +6107,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6121,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486291</v>
+        <v>486250</v>
       </c>
       <c r="R55" t="n">
-        <v>6829537</v>
+        <v>6829400</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6183,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468937</v>
+        <v>121468961</v>
       </c>
       <c r="B56" t="n">
-        <v>78643</v>
+        <v>78345</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6199,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486310</v>
+        <v>486376</v>
       </c>
       <c r="R56" t="n">
-        <v>6829463</v>
+        <v>6829237</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,7 +6295,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468994</v>
+        <v>121468989</v>
       </c>
       <c r="B57" t="n">
         <v>78609</v>
@@ -6325,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486261</v>
+        <v>486302</v>
       </c>
       <c r="R57" t="n">
-        <v>6829525</v>
+        <v>6829539</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6387,7 +6397,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468992</v>
+        <v>121468987</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6427,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486291</v>
+        <v>486271</v>
       </c>
       <c r="R58" t="n">
-        <v>6829537</v>
+        <v>6829568</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6489,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468918</v>
+        <v>121468978</v>
       </c>
       <c r="B59" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6505,21 +6515,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486321</v>
+        <v>486279</v>
       </c>
       <c r="R59" t="n">
-        <v>6829248</v>
+        <v>6829687</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6591,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468987</v>
+        <v>121468928</v>
       </c>
       <c r="B60" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6607,21 +6617,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6631,10 +6641,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486271</v>
+        <v>486313</v>
       </c>
       <c r="R60" t="n">
-        <v>6829568</v>
+        <v>6829466</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6693,10 +6703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468936</v>
+        <v>121469045</v>
       </c>
       <c r="B61" t="n">
-        <v>78643</v>
+        <v>78254</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6709,21 +6719,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6743,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486335</v>
+        <v>486365</v>
       </c>
       <c r="R61" t="n">
-        <v>6829435</v>
+        <v>6829215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,10 +6805,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468986</v>
+        <v>121468918</v>
       </c>
       <c r="B62" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6811,21 +6821,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6835,10 +6845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486259</v>
+        <v>486321</v>
       </c>
       <c r="R62" t="n">
-        <v>6829565</v>
+        <v>6829248</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6897,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468917</v>
+        <v>121468942</v>
       </c>
       <c r="B63" t="n">
-        <v>79227</v>
+        <v>79198</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6913,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6937,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486305</v>
+        <v>486165</v>
       </c>
       <c r="R63" t="n">
-        <v>6829222</v>
+        <v>6829633</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6999,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468989</v>
+        <v>121468958</v>
       </c>
       <c r="B64" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7015,21 +7025,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7039,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486302</v>
+        <v>486278</v>
       </c>
       <c r="R64" t="n">
-        <v>6829539</v>
+        <v>6829675</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7101,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468934</v>
+        <v>121468983</v>
       </c>
       <c r="B65" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7117,21 +7127,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7141,10 +7151,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486318</v>
+        <v>486213</v>
       </c>
       <c r="R65" t="n">
-        <v>6829376</v>
+        <v>6829683</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,7 +7213,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468969</v>
+        <v>121468977</v>
       </c>
       <c r="B66" t="n">
         <v>78609</v>
@@ -7243,10 +7253,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486317</v>
+        <v>486269</v>
       </c>
       <c r="R66" t="n">
-        <v>6829572</v>
+        <v>6829656</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7305,7 +7315,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469009</v>
+        <v>121469007</v>
       </c>
       <c r="B67" t="n">
         <v>78609</v>
@@ -7345,10 +7355,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486396</v>
+        <v>486432</v>
       </c>
       <c r="R67" t="n">
-        <v>6829190</v>
+        <v>6829183</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7407,10 +7417,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469023</v>
+        <v>121468935</v>
       </c>
       <c r="B68" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7423,21 +7433,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7447,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486362</v>
+        <v>486323</v>
       </c>
       <c r="R68" t="n">
-        <v>6829525</v>
+        <v>6829408</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7509,7 +7519,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468966</v>
+        <v>121468991</v>
       </c>
       <c r="B69" t="n">
         <v>78609</v>
@@ -7549,10 +7559,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486335</v>
+        <v>486297</v>
       </c>
       <c r="R69" t="n">
-        <v>6829590</v>
+        <v>6829538</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7611,10 +7621,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469021</v>
+        <v>121468937</v>
       </c>
       <c r="B70" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7627,21 +7637,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7651,10 +7661,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486328</v>
+        <v>486310</v>
       </c>
       <c r="R70" t="n">
-        <v>6829486</v>
+        <v>6829463</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,10 +7723,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468921</v>
+        <v>121469025</v>
       </c>
       <c r="B71" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7729,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7753,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486365</v>
+        <v>486353</v>
       </c>
       <c r="R71" t="n">
-        <v>6829163</v>
+        <v>6829553</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7815,7 +7825,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468970</v>
+        <v>121468996</v>
       </c>
       <c r="B72" t="n">
         <v>78609</v>
@@ -7855,10 +7865,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486315</v>
+        <v>486242</v>
       </c>
       <c r="R72" t="n">
-        <v>6829584</v>
+        <v>6829317</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7917,7 +7927,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469027</v>
+        <v>121468998</v>
       </c>
       <c r="B73" t="n">
         <v>78609</v>
@@ -7957,10 +7967,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486370</v>
+        <v>486366</v>
       </c>
       <c r="R73" t="n">
-        <v>6829559</v>
+        <v>6829176</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8029,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121469045</v>
+        <v>121468957</v>
       </c>
       <c r="B74" t="n">
-        <v>78254</v>
+        <v>8435</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8031,38 +8041,47 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486365</v>
+        <v>486210</v>
       </c>
       <c r="R74" t="n">
-        <v>6829215</v>
+        <v>6829556</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8103,6 +8122,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8121,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468959</v>
+        <v>121469017</v>
       </c>
       <c r="B75" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8137,21 +8157,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8181,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486437</v>
+        <v>486335</v>
       </c>
       <c r="R75" t="n">
-        <v>6829174</v>
+        <v>6829435</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8223,10 +8243,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468954</v>
+        <v>121468973</v>
       </c>
       <c r="B76" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8235,47 +8255,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486213</v>
+        <v>486298</v>
       </c>
       <c r="R76" t="n">
-        <v>6829562</v>
+        <v>6829599</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8316,7 +8327,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8335,10 +8345,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468957</v>
+        <v>121469004</v>
       </c>
       <c r="B77" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8347,47 +8357,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486210</v>
+        <v>486442</v>
       </c>
       <c r="R77" t="n">
-        <v>6829556</v>
+        <v>6829128</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8428,7 +8429,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468938</v>
+        <v>121468927</v>
       </c>
       <c r="B78" t="n">
-        <v>78643</v>
+        <v>74715</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8463,21 +8463,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486329</v>
+        <v>486283</v>
       </c>
       <c r="R78" t="n">
-        <v>6829484</v>
+        <v>6829532</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8549,10 +8549,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468942</v>
+        <v>121468992</v>
       </c>
       <c r="B79" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8565,21 +8565,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486165</v>
+        <v>486291</v>
       </c>
       <c r="R79" t="n">
-        <v>6829633</v>
+        <v>6829537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8651,10 +8651,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469012</v>
+        <v>121469035</v>
       </c>
       <c r="B80" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8667,21 +8667,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486315</v>
+        <v>486278</v>
       </c>
       <c r="R80" t="n">
-        <v>6829368</v>
+        <v>6829675</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8753,7 +8753,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468984</v>
+        <v>121468969</v>
       </c>
       <c r="B81" t="n">
         <v>78609</v>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486202</v>
+        <v>486317</v>
       </c>
       <c r="R81" t="n">
-        <v>6829676</v>
+        <v>6829572</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8855,7 +8855,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468967</v>
+        <v>121469024</v>
       </c>
       <c r="B82" t="n">
         <v>78609</v>
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486329</v>
+        <v>486351</v>
       </c>
       <c r="R82" t="n">
-        <v>6829590</v>
+        <v>6829541</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8957,7 +8957,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468991</v>
+        <v>121468985</v>
       </c>
       <c r="B83" t="n">
         <v>78609</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486297</v>
+        <v>486183</v>
       </c>
       <c r="R83" t="n">
-        <v>6829538</v>
+        <v>6829659</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9059,7 +9059,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469017</v>
+        <v>121468995</v>
       </c>
       <c r="B84" t="n">
         <v>78609</v>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486335</v>
+        <v>486256</v>
       </c>
       <c r="R84" t="n">
-        <v>6829435</v>
+        <v>6829523</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9161,10 +9161,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121468933</v>
+        <v>121469013</v>
       </c>
       <c r="B85" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9177,21 +9177,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486317</v>
+        <v>486318</v>
       </c>
       <c r="R85" t="n">
-        <v>6829373</v>
+        <v>6829376</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9263,10 +9263,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121468985</v>
+        <v>121469043</v>
       </c>
       <c r="B86" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9279,21 +9279,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486183</v>
+        <v>486291</v>
       </c>
       <c r="R86" t="n">
-        <v>6829659</v>
+        <v>6829537</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468947</v>
+        <v>121469015</v>
       </c>
       <c r="B87" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9381,21 +9381,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486213</v>
+        <v>486323</v>
       </c>
       <c r="R87" t="n">
-        <v>6829765</v>
+        <v>6829408</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9467,10 +9467,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469047</v>
+        <v>121468975</v>
       </c>
       <c r="B88" t="n">
-        <v>77541</v>
+        <v>78609</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9483,21 +9483,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486258</v>
+        <v>486298</v>
       </c>
       <c r="R88" t="n">
-        <v>6829343</v>
+        <v>6829621</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468955</v>
+        <v>121468914</v>
       </c>
       <c r="B89" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486321</v>
+        <v>486317</v>
       </c>
       <c r="R89" t="n">
-        <v>6829248</v>
+        <v>6829572</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468947</v>
+        <v>121469020</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486213</v>
+        <v>486312</v>
       </c>
       <c r="R7" t="n">
-        <v>6829765</v>
+        <v>6829467</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468959</v>
+        <v>121469008</v>
       </c>
       <c r="B8" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486437</v>
+        <v>486416</v>
       </c>
       <c r="R8" t="n">
-        <v>6829174</v>
+        <v>6829192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469020</v>
+        <v>121469028</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486312</v>
+        <v>486375</v>
       </c>
       <c r="R9" t="n">
-        <v>6829467</v>
+        <v>6829566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469008</v>
+        <v>121468976</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486416</v>
+        <v>486293</v>
       </c>
       <c r="R10" t="n">
-        <v>6829192</v>
+        <v>6829631</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469028</v>
+        <v>121468959</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486375</v>
+        <v>486437</v>
       </c>
       <c r="R11" t="n">
-        <v>6829566</v>
+        <v>6829174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468976</v>
+        <v>121469010</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486293</v>
+        <v>486366</v>
       </c>
       <c r="R12" t="n">
-        <v>6829631</v>
+        <v>6829228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469010</v>
+        <v>121468947</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486366</v>
+        <v>486213</v>
       </c>
       <c r="R13" t="n">
-        <v>6829228</v>
+        <v>6829765</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469044</v>
+        <v>121468984</v>
       </c>
       <c r="B14" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486236</v>
+        <v>486202</v>
       </c>
       <c r="R14" t="n">
-        <v>6829512</v>
+        <v>6829676</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468982</v>
+        <v>121469044</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486213</v>
+        <v>486236</v>
       </c>
       <c r="R15" t="n">
-        <v>6829765</v>
+        <v>6829512</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468984</v>
+        <v>121468970</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486202</v>
+        <v>486315</v>
       </c>
       <c r="R16" t="n">
-        <v>6829676</v>
+        <v>6829584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468970</v>
+        <v>121468982</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486315</v>
+        <v>486213</v>
       </c>
       <c r="R17" t="n">
-        <v>6829584</v>
+        <v>6829765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468966</v>
+        <v>121468944</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486335</v>
+        <v>486255</v>
       </c>
       <c r="R44" t="n">
-        <v>6829590</v>
+        <v>6829395</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468944</v>
+        <v>121468966</v>
       </c>
       <c r="B45" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486255</v>
+        <v>486335</v>
       </c>
       <c r="R45" t="n">
-        <v>6829395</v>
+        <v>6829590</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469034</v>
+        <v>121468954</v>
       </c>
       <c r="B46" t="n">
-        <v>88039</v>
+        <v>8435</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5175,38 +5175,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>510</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486298</v>
+        <v>486213</v>
       </c>
       <c r="R46" t="n">
-        <v>6829599</v>
+        <v>6829562</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,6 +5256,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5265,10 +5275,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468931</v>
+        <v>121468939</v>
       </c>
       <c r="B47" t="n">
-        <v>78643</v>
+        <v>79198</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5281,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486202</v>
+        <v>486265</v>
       </c>
       <c r="R47" t="n">
-        <v>6829676</v>
+        <v>6829735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468915</v>
+        <v>121469034</v>
       </c>
       <c r="B48" t="n">
-        <v>79227</v>
+        <v>88039</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5393,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486223</v>
+        <v>486298</v>
       </c>
       <c r="R48" t="n">
-        <v>6829705</v>
+        <v>6829599</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5479,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468921</v>
+        <v>121468931</v>
       </c>
       <c r="B49" t="n">
-        <v>79227</v>
+        <v>78643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5495,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486365</v>
+        <v>486202</v>
       </c>
       <c r="R49" t="n">
-        <v>6829163</v>
+        <v>6829676</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5877,10 +5887,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468939</v>
+        <v>121468915</v>
       </c>
       <c r="B53" t="n">
-        <v>79198</v>
+        <v>79227</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5893,21 +5903,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5917,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486265</v>
+        <v>486223</v>
       </c>
       <c r="R53" t="n">
-        <v>6829735</v>
+        <v>6829705</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5979,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468954</v>
+        <v>121468921</v>
       </c>
       <c r="B54" t="n">
-        <v>8435</v>
+        <v>79227</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5991,47 +6001,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486213</v>
+        <v>486365</v>
       </c>
       <c r="R54" t="n">
-        <v>6829562</v>
+        <v>6829163</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6072,7 +6073,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7417,7 +7417,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468935</v>
+        <v>121468937</v>
       </c>
       <c r="B68" t="n">
         <v>78643</v>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486323</v>
+        <v>486310</v>
       </c>
       <c r="R68" t="n">
-        <v>6829408</v>
+        <v>6829463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7519,10 +7519,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468991</v>
+        <v>121468935</v>
       </c>
       <c r="B69" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7535,21 +7535,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486297</v>
+        <v>486323</v>
       </c>
       <c r="R69" t="n">
-        <v>6829538</v>
+        <v>6829408</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7621,10 +7621,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468937</v>
+        <v>121468991</v>
       </c>
       <c r="B70" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7637,21 +7637,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486310</v>
+        <v>486297</v>
       </c>
       <c r="R70" t="n">
-        <v>6829463</v>
+        <v>6829538</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7723,10 +7723,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469025</v>
+        <v>121468957</v>
       </c>
       <c r="B71" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7735,38 +7735,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486353</v>
+        <v>486210</v>
       </c>
       <c r="R71" t="n">
-        <v>6829553</v>
+        <v>6829556</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7807,6 +7816,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7825,7 +7835,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468996</v>
+        <v>121469025</v>
       </c>
       <c r="B72" t="n">
         <v>78609</v>
@@ -7865,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486242</v>
+        <v>486353</v>
       </c>
       <c r="R72" t="n">
-        <v>6829317</v>
+        <v>6829553</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7927,7 +7937,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468998</v>
+        <v>121468996</v>
       </c>
       <c r="B73" t="n">
         <v>78609</v>
@@ -7967,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486366</v>
+        <v>486242</v>
       </c>
       <c r="R73" t="n">
-        <v>6829176</v>
+        <v>6829317</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8029,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468957</v>
+        <v>121468998</v>
       </c>
       <c r="B74" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8041,47 +8051,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486210</v>
+        <v>486366</v>
       </c>
       <c r="R74" t="n">
-        <v>6829556</v>
+        <v>6829176</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8122,7 +8123,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -6091,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121468943</v>
+        <v>121468961</v>
       </c>
       <c r="B55" t="n">
-        <v>79198</v>
+        <v>78345</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486250</v>
+        <v>486376</v>
       </c>
       <c r="R55" t="n">
-        <v>6829400</v>
+        <v>6829237</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468961</v>
+        <v>121468989</v>
       </c>
       <c r="B56" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486376</v>
+        <v>486302</v>
       </c>
       <c r="R56" t="n">
-        <v>6829237</v>
+        <v>6829539</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468989</v>
+        <v>121468987</v>
       </c>
       <c r="B57" t="n">
         <v>78609</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486302</v>
+        <v>486271</v>
       </c>
       <c r="R57" t="n">
-        <v>6829539</v>
+        <v>6829568</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468987</v>
+        <v>121468943</v>
       </c>
       <c r="B58" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486271</v>
+        <v>486250</v>
       </c>
       <c r="R58" t="n">
-        <v>6829568</v>
+        <v>6829400</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7723,10 +7723,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468957</v>
+        <v>121469025</v>
       </c>
       <c r="B71" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7735,47 +7735,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486210</v>
+        <v>486353</v>
       </c>
       <c r="R71" t="n">
-        <v>6829556</v>
+        <v>6829553</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7816,7 +7807,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7835,7 +7825,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469025</v>
+        <v>121468996</v>
       </c>
       <c r="B72" t="n">
         <v>78609</v>
@@ -7875,10 +7865,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486353</v>
+        <v>486242</v>
       </c>
       <c r="R72" t="n">
-        <v>6829553</v>
+        <v>6829317</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7937,7 +7927,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468996</v>
+        <v>121468998</v>
       </c>
       <c r="B73" t="n">
         <v>78609</v>
@@ -7977,10 +7967,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486242</v>
+        <v>486366</v>
       </c>
       <c r="R73" t="n">
-        <v>6829317</v>
+        <v>6829176</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8029,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468998</v>
+        <v>121468957</v>
       </c>
       <c r="B74" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8051,38 +8041,47 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486366</v>
+        <v>486210</v>
       </c>
       <c r="R74" t="n">
-        <v>6829176</v>
+        <v>6829556</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8123,6 +8122,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9263,10 +9263,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469043</v>
+        <v>121469015</v>
       </c>
       <c r="B86" t="n">
-        <v>78254</v>
+        <v>78609</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9279,21 +9279,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486291</v>
+        <v>486323</v>
       </c>
       <c r="R86" t="n">
-        <v>6829537</v>
+        <v>6829408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9365,7 +9365,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121469015</v>
+        <v>121468975</v>
       </c>
       <c r="B87" t="n">
         <v>78609</v>
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486323</v>
+        <v>486298</v>
       </c>
       <c r="R87" t="n">
-        <v>6829408</v>
+        <v>6829621</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9467,10 +9467,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468975</v>
+        <v>121469043</v>
       </c>
       <c r="B88" t="n">
-        <v>78609</v>
+        <v>78254</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9483,21 +9483,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486298</v>
+        <v>486291</v>
       </c>
       <c r="R88" t="n">
-        <v>6829621</v>
+        <v>6829537</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121469012</v>
+        <v>121469021</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486315</v>
+        <v>486328</v>
       </c>
       <c r="R2" t="n">
-        <v>6829368</v>
+        <v>6829486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121469027</v>
+        <v>121468937</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78650</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486370</v>
+        <v>486310</v>
       </c>
       <c r="R3" t="n">
-        <v>6829559</v>
+        <v>6829463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121469023</v>
+        <v>121468914</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486362</v>
+        <v>486317</v>
       </c>
       <c r="R4" t="n">
-        <v>6829525</v>
+        <v>6829572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468933</v>
+        <v>121468967</v>
       </c>
       <c r="B5" t="n">
-        <v>78643</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486317</v>
+        <v>486329</v>
       </c>
       <c r="R5" t="n">
-        <v>6829373</v>
+        <v>6829590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468932</v>
+        <v>121468999</v>
       </c>
       <c r="B6" t="n">
-        <v>78643</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486261</v>
+        <v>486352</v>
       </c>
       <c r="R6" t="n">
-        <v>6829525</v>
+        <v>6829165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121469020</v>
+        <v>121468982</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486312</v>
+        <v>486213</v>
       </c>
       <c r="R7" t="n">
-        <v>6829467</v>
+        <v>6829765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121469008</v>
+        <v>121468938</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486416</v>
+        <v>486329</v>
       </c>
       <c r="R8" t="n">
-        <v>6829192</v>
+        <v>6829484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469028</v>
+        <v>121468917</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486375</v>
+        <v>486305</v>
       </c>
       <c r="R9" t="n">
-        <v>6829566</v>
+        <v>6829222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468976</v>
+        <v>121468961</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486293</v>
+        <v>486376</v>
       </c>
       <c r="R10" t="n">
-        <v>6829631</v>
+        <v>6829237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468959</v>
+        <v>121469024</v>
       </c>
       <c r="B11" t="n">
-        <v>80566</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486437</v>
+        <v>486351</v>
       </c>
       <c r="R11" t="n">
-        <v>6829174</v>
+        <v>6829541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469010</v>
+        <v>121468993</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486366</v>
+        <v>486272</v>
       </c>
       <c r="R12" t="n">
-        <v>6829228</v>
+        <v>6829527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121468947</v>
+        <v>121469025</v>
       </c>
       <c r="B13" t="n">
-        <v>57509</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486213</v>
+        <v>486353</v>
       </c>
       <c r="R13" t="n">
-        <v>6829765</v>
+        <v>6829553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468984</v>
+        <v>121469004</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486202</v>
+        <v>486442</v>
       </c>
       <c r="R14" t="n">
-        <v>6829676</v>
+        <v>6829128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469044</v>
+        <v>121468983</v>
       </c>
       <c r="B15" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486236</v>
+        <v>486213</v>
       </c>
       <c r="R15" t="n">
-        <v>6829512</v>
+        <v>6829683</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468970</v>
+        <v>121468957</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>8436</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,38 +2115,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486315</v>
+        <v>486210</v>
       </c>
       <c r="R16" t="n">
-        <v>6829584</v>
+        <v>6829556</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,6 +2196,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468982</v>
+        <v>121468940</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>79205</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486213</v>
+        <v>486207</v>
       </c>
       <c r="R17" t="n">
-        <v>6829765</v>
+        <v>6829684</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468979</v>
+        <v>121468922</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486282</v>
+        <v>486376</v>
       </c>
       <c r="R18" t="n">
-        <v>6829704</v>
+        <v>6829237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121469018</v>
+        <v>121469005</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486306</v>
+        <v>486438</v>
       </c>
       <c r="R19" t="n">
-        <v>6829450</v>
+        <v>6829156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469006</v>
+        <v>121468941</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>79205</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486437</v>
+        <v>486174</v>
       </c>
       <c r="R20" t="n">
-        <v>6829175</v>
+        <v>6829641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468922</v>
+        <v>121469007</v>
       </c>
       <c r="B21" t="n">
-        <v>79227</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486376</v>
+        <v>486432</v>
       </c>
       <c r="R21" t="n">
-        <v>6829237</v>
+        <v>6829183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468917</v>
+        <v>121469046</v>
       </c>
       <c r="B22" t="n">
-        <v>79227</v>
+        <v>78261</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486305</v>
+        <v>486324</v>
       </c>
       <c r="R22" t="n">
-        <v>6829222</v>
+        <v>6829398</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469019</v>
+        <v>121469017</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486309</v>
+        <v>486335</v>
       </c>
       <c r="R23" t="n">
-        <v>6829468</v>
+        <v>6829435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469009</v>
+        <v>121469008</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486396</v>
+        <v>486416</v>
       </c>
       <c r="R24" t="n">
-        <v>6829190</v>
+        <v>6829192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468938</v>
+        <v>121468975</v>
       </c>
       <c r="B25" t="n">
-        <v>78643</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486329</v>
+        <v>486298</v>
       </c>
       <c r="R25" t="n">
-        <v>6829484</v>
+        <v>6829621</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468994</v>
+        <v>121468955</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486261</v>
+        <v>486321</v>
       </c>
       <c r="R26" t="n">
-        <v>6829525</v>
+        <v>6829248</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121468993</v>
+        <v>121468954</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>8436</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,38 +3247,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486272</v>
+        <v>486213</v>
       </c>
       <c r="R27" t="n">
-        <v>6829527</v>
+        <v>6829562</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,6 +3328,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3327,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121468929</v>
+        <v>121469043</v>
       </c>
       <c r="B28" t="n">
-        <v>78643</v>
+        <v>78261</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3363,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486309</v>
+        <v>486291</v>
       </c>
       <c r="R28" t="n">
-        <v>6829581</v>
+        <v>6829537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469021</v>
+        <v>121468934</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>78650</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486328</v>
+        <v>486318</v>
       </c>
       <c r="R29" t="n">
-        <v>6829486</v>
+        <v>6829376</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468941</v>
+        <v>121468932</v>
       </c>
       <c r="B30" t="n">
-        <v>79198</v>
+        <v>78650</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486174</v>
+        <v>486261</v>
       </c>
       <c r="R30" t="n">
-        <v>6829641</v>
+        <v>6829525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468968</v>
+        <v>121469013</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486325</v>
+        <v>486318</v>
       </c>
       <c r="R31" t="n">
-        <v>6829578</v>
+        <v>6829376</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468936</v>
+        <v>121469028</v>
       </c>
       <c r="B32" t="n">
-        <v>78643</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486335</v>
+        <v>486375</v>
       </c>
       <c r="R32" t="n">
-        <v>6829435</v>
+        <v>6829566</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469046</v>
+        <v>121469010</v>
       </c>
       <c r="B33" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486324</v>
+        <v>486366</v>
       </c>
       <c r="R33" t="n">
-        <v>6829398</v>
+        <v>6829228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468919</v>
+        <v>121468966</v>
       </c>
       <c r="B34" t="n">
-        <v>79227</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486341</v>
+        <v>486335</v>
       </c>
       <c r="R34" t="n">
-        <v>6829217</v>
+        <v>6829590</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469047</v>
+        <v>121468970</v>
       </c>
       <c r="B35" t="n">
-        <v>77541</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486258</v>
+        <v>486315</v>
       </c>
       <c r="R35" t="n">
-        <v>6829343</v>
+        <v>6829584</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468955</v>
+        <v>121468915</v>
       </c>
       <c r="B36" t="n">
-        <v>78346</v>
+        <v>79234</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486321</v>
+        <v>486223</v>
       </c>
       <c r="R36" t="n">
-        <v>6829248</v>
+        <v>6829705</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469005</v>
+        <v>121469001</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486438</v>
+        <v>486374</v>
       </c>
       <c r="R37" t="n">
-        <v>6829156</v>
+        <v>6829123</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468940</v>
+        <v>121469044</v>
       </c>
       <c r="B38" t="n">
-        <v>79198</v>
+        <v>78261</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486207</v>
+        <v>486236</v>
       </c>
       <c r="R38" t="n">
-        <v>6829684</v>
+        <v>6829512</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468974</v>
+        <v>121469023</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486301</v>
+        <v>486362</v>
       </c>
       <c r="R39" t="n">
-        <v>6829606</v>
+        <v>6829525</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468967</v>
+        <v>121468927</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>74722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486329</v>
+        <v>486283</v>
       </c>
       <c r="R40" t="n">
-        <v>6829590</v>
+        <v>6829532</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469001</v>
+        <v>121468987</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4693,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486374</v>
+        <v>486271</v>
       </c>
       <c r="R41" t="n">
-        <v>6829123</v>
+        <v>6829568</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469036</v>
+        <v>121468939</v>
       </c>
       <c r="B42" t="n">
-        <v>78254</v>
+        <v>79205</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4791,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486261</v>
+        <v>486265</v>
       </c>
       <c r="R42" t="n">
-        <v>6829744</v>
+        <v>6829735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468934</v>
+        <v>121468958</v>
       </c>
       <c r="B43" t="n">
-        <v>78643</v>
+        <v>80573</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4893,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486318</v>
+        <v>486278</v>
       </c>
       <c r="R43" t="n">
-        <v>6829376</v>
+        <v>6829675</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468944</v>
+        <v>121469009</v>
       </c>
       <c r="B44" t="n">
-        <v>79198</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4995,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486255</v>
+        <v>486396</v>
       </c>
       <c r="R44" t="n">
-        <v>6829395</v>
+        <v>6829190</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468966</v>
+        <v>121468935</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>78650</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5097,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486335</v>
+        <v>486323</v>
       </c>
       <c r="R45" t="n">
-        <v>6829590</v>
+        <v>6829408</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468954</v>
+        <v>121468947</v>
       </c>
       <c r="B46" t="n">
-        <v>8435</v>
+        <v>57510</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5175,37 +5195,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
@@ -5215,7 +5226,7 @@
         <v>486213</v>
       </c>
       <c r="R46" t="n">
-        <v>6829562</v>
+        <v>6829765</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5256,7 +5267,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5275,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468939</v>
+        <v>121468995</v>
       </c>
       <c r="B47" t="n">
-        <v>79198</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,21 +5301,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486265</v>
+        <v>486256</v>
       </c>
       <c r="R47" t="n">
-        <v>6829735</v>
+        <v>6829523</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469034</v>
+        <v>121468968</v>
       </c>
       <c r="B48" t="n">
-        <v>88039</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5393,21 +5403,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5417,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486298</v>
+        <v>486325</v>
       </c>
       <c r="R48" t="n">
-        <v>6829599</v>
+        <v>6829578</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468931</v>
+        <v>121468996</v>
       </c>
       <c r="B49" t="n">
-        <v>78643</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5495,21 +5505,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5519,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486202</v>
+        <v>486242</v>
       </c>
       <c r="R49" t="n">
-        <v>6829676</v>
+        <v>6829317</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121468999</v>
+        <v>121468976</v>
       </c>
       <c r="B50" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5621,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486352</v>
+        <v>486293</v>
       </c>
       <c r="R50" t="n">
-        <v>6829165</v>
+        <v>6829631</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468971</v>
+        <v>121468918</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5699,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5723,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486309</v>
+        <v>486321</v>
       </c>
       <c r="R51" t="n">
-        <v>6829581</v>
+        <v>6829248</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5788,7 +5798,7 @@
         <v>121468986</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5887,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468915</v>
+        <v>121468977</v>
       </c>
       <c r="B53" t="n">
-        <v>79227</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5903,21 +5913,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486223</v>
+        <v>486269</v>
       </c>
       <c r="R53" t="n">
-        <v>6829705</v>
+        <v>6829656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5989,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468921</v>
+        <v>121468943</v>
       </c>
       <c r="B54" t="n">
-        <v>79227</v>
+        <v>79205</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +6015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486365</v>
+        <v>486250</v>
       </c>
       <c r="R54" t="n">
-        <v>6829163</v>
+        <v>6829400</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121468961</v>
+        <v>121468942</v>
       </c>
       <c r="B55" t="n">
-        <v>78345</v>
+        <v>79205</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6107,21 +6117,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486376</v>
+        <v>486165</v>
       </c>
       <c r="R55" t="n">
-        <v>6829237</v>
+        <v>6829633</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,10 +6203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468989</v>
+        <v>121469020</v>
       </c>
       <c r="B56" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6233,10 +6243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486302</v>
+        <v>486312</v>
       </c>
       <c r="R56" t="n">
-        <v>6829539</v>
+        <v>6829467</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468987</v>
+        <v>121468933</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>78650</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6311,21 +6321,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6345,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486271</v>
+        <v>486317</v>
       </c>
       <c r="R57" t="n">
-        <v>6829568</v>
+        <v>6829373</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6407,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468943</v>
+        <v>121468974</v>
       </c>
       <c r="B58" t="n">
-        <v>79198</v>
+        <v>78616</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6413,21 +6423,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6437,10 +6447,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486250</v>
+        <v>486301</v>
       </c>
       <c r="R58" t="n">
-        <v>6829400</v>
+        <v>6829606</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468978</v>
+        <v>121468991</v>
       </c>
       <c r="B59" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6539,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486279</v>
+        <v>486297</v>
       </c>
       <c r="R59" t="n">
-        <v>6829687</v>
+        <v>6829538</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468928</v>
+        <v>121469036</v>
       </c>
       <c r="B60" t="n">
-        <v>74715</v>
+        <v>78261</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,21 +6627,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6641,10 +6651,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486313</v>
+        <v>486261</v>
       </c>
       <c r="R60" t="n">
-        <v>6829466</v>
+        <v>6829744</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6703,10 +6713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469045</v>
+        <v>121468929</v>
       </c>
       <c r="B61" t="n">
-        <v>78254</v>
+        <v>78650</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6719,21 +6729,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6743,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486365</v>
+        <v>486309</v>
       </c>
       <c r="R61" t="n">
-        <v>6829215</v>
+        <v>6829581</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6805,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468918</v>
+        <v>121468919</v>
       </c>
       <c r="B62" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6845,10 +6855,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486321</v>
+        <v>486341</v>
       </c>
       <c r="R62" t="n">
-        <v>6829248</v>
+        <v>6829217</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6917,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468942</v>
+        <v>121468921</v>
       </c>
       <c r="B63" t="n">
-        <v>79198</v>
+        <v>79234</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6923,21 +6933,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486165</v>
+        <v>486365</v>
       </c>
       <c r="R63" t="n">
-        <v>6829633</v>
+        <v>6829163</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7019,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468958</v>
+        <v>121469012</v>
       </c>
       <c r="B64" t="n">
-        <v>80566</v>
+        <v>78616</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7025,21 +7035,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486278</v>
+        <v>486315</v>
       </c>
       <c r="R64" t="n">
-        <v>6829675</v>
+        <v>6829368</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,10 +7121,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468983</v>
+        <v>121468978</v>
       </c>
       <c r="B65" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7151,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486213</v>
+        <v>486279</v>
       </c>
       <c r="R65" t="n">
-        <v>6829683</v>
+        <v>6829687</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7213,10 +7223,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468977</v>
+        <v>121468946</v>
       </c>
       <c r="B66" t="n">
-        <v>78609</v>
+        <v>57510</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7229,34 +7239,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486269</v>
+        <v>486392</v>
       </c>
       <c r="R66" t="n">
-        <v>6829656</v>
+        <v>6829119</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7315,10 +7337,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121469007</v>
+        <v>121469019</v>
       </c>
       <c r="B67" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7355,10 +7377,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486432</v>
+        <v>486309</v>
       </c>
       <c r="R67" t="n">
-        <v>6829183</v>
+        <v>6829468</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7417,10 +7439,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468937</v>
+        <v>121469047</v>
       </c>
       <c r="B68" t="n">
-        <v>78643</v>
+        <v>77548</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7433,21 +7455,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7457,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486310</v>
+        <v>486258</v>
       </c>
       <c r="R68" t="n">
-        <v>6829463</v>
+        <v>6829343</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7519,10 +7541,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468935</v>
+        <v>121468984</v>
       </c>
       <c r="B69" t="n">
-        <v>78643</v>
+        <v>78616</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7535,21 +7557,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7559,10 +7581,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486323</v>
+        <v>486202</v>
       </c>
       <c r="R69" t="n">
-        <v>6829408</v>
+        <v>6829676</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7621,10 +7643,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468991</v>
+        <v>121468985</v>
       </c>
       <c r="B70" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7661,10 +7683,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486297</v>
+        <v>486183</v>
       </c>
       <c r="R70" t="n">
-        <v>6829538</v>
+        <v>6829659</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7723,10 +7745,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469025</v>
+        <v>121468998</v>
       </c>
       <c r="B71" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7763,10 +7785,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486353</v>
+        <v>486366</v>
       </c>
       <c r="R71" t="n">
-        <v>6829553</v>
+        <v>6829176</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,10 +7847,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468996</v>
+        <v>121468944</v>
       </c>
       <c r="B72" t="n">
-        <v>78609</v>
+        <v>79205</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7841,21 +7863,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7865,10 +7887,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486242</v>
+        <v>486255</v>
       </c>
       <c r="R72" t="n">
-        <v>6829317</v>
+        <v>6829395</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7927,10 +7949,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468998</v>
+        <v>121469015</v>
       </c>
       <c r="B73" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7967,10 +7989,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486366</v>
+        <v>486323</v>
       </c>
       <c r="R73" t="n">
-        <v>6829176</v>
+        <v>6829408</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8029,10 +8051,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468957</v>
+        <v>121468931</v>
       </c>
       <c r="B74" t="n">
-        <v>8435</v>
+        <v>78650</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8041,47 +8063,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486210</v>
+        <v>486202</v>
       </c>
       <c r="R74" t="n">
-        <v>6829556</v>
+        <v>6829676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8122,7 +8135,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8141,10 +8153,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469017</v>
+        <v>121468973</v>
       </c>
       <c r="B75" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8181,10 +8193,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486335</v>
+        <v>486298</v>
       </c>
       <c r="R75" t="n">
-        <v>6829435</v>
+        <v>6829599</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8243,10 +8255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468973</v>
+        <v>121468928</v>
       </c>
       <c r="B76" t="n">
-        <v>78609</v>
+        <v>74722</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8259,21 +8271,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8283,10 +8295,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486298</v>
+        <v>486313</v>
       </c>
       <c r="R76" t="n">
-        <v>6829599</v>
+        <v>6829466</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8345,10 +8357,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469004</v>
+        <v>121468959</v>
       </c>
       <c r="B77" t="n">
-        <v>78609</v>
+        <v>80573</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8361,21 +8373,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8385,10 +8397,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486442</v>
+        <v>486437</v>
       </c>
       <c r="R77" t="n">
-        <v>6829128</v>
+        <v>6829174</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8447,10 +8459,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468927</v>
+        <v>121469018</v>
       </c>
       <c r="B78" t="n">
-        <v>74715</v>
+        <v>78616</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8463,21 +8475,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8487,10 +8499,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486283</v>
+        <v>486306</v>
       </c>
       <c r="R78" t="n">
-        <v>6829532</v>
+        <v>6829450</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8549,10 +8561,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468992</v>
+        <v>121469045</v>
       </c>
       <c r="B79" t="n">
-        <v>78609</v>
+        <v>78261</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8565,21 +8577,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8589,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486291</v>
+        <v>486365</v>
       </c>
       <c r="R79" t="n">
-        <v>6829537</v>
+        <v>6829215</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8654,7 +8666,7 @@
         <v>121469035</v>
       </c>
       <c r="B80" t="n">
-        <v>78254</v>
+        <v>78261</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8753,10 +8765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468969</v>
+        <v>121468971</v>
       </c>
       <c r="B81" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8793,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486317</v>
+        <v>486309</v>
       </c>
       <c r="R81" t="n">
-        <v>6829572</v>
+        <v>6829581</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8855,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121469024</v>
+        <v>121468994</v>
       </c>
       <c r="B82" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8895,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486351</v>
+        <v>486261</v>
       </c>
       <c r="R82" t="n">
-        <v>6829541</v>
+        <v>6829525</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8957,10 +8969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468985</v>
+        <v>121468969</v>
       </c>
       <c r="B83" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8997,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486183</v>
+        <v>486317</v>
       </c>
       <c r="R83" t="n">
-        <v>6829659</v>
+        <v>6829572</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9059,10 +9071,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468995</v>
+        <v>121468979</v>
       </c>
       <c r="B84" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9099,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486256</v>
+        <v>486282</v>
       </c>
       <c r="R84" t="n">
-        <v>6829523</v>
+        <v>6829704</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9161,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469013</v>
+        <v>121469006</v>
       </c>
       <c r="B85" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9201,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486318</v>
+        <v>486437</v>
       </c>
       <c r="R85" t="n">
-        <v>6829376</v>
+        <v>6829175</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9263,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469015</v>
+        <v>121469027</v>
       </c>
       <c r="B86" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9303,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486323</v>
+        <v>486370</v>
       </c>
       <c r="R86" t="n">
-        <v>6829408</v>
+        <v>6829559</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9365,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468975</v>
+        <v>121468992</v>
       </c>
       <c r="B87" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9405,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486298</v>
+        <v>486291</v>
       </c>
       <c r="R87" t="n">
-        <v>6829621</v>
+        <v>6829537</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9467,10 +9479,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469043</v>
+        <v>121468989</v>
       </c>
       <c r="B88" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9483,21 +9495,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9507,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486291</v>
+        <v>486302</v>
       </c>
       <c r="R88" t="n">
-        <v>6829537</v>
+        <v>6829539</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9569,10 +9581,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468914</v>
+        <v>121469034</v>
       </c>
       <c r="B89" t="n">
-        <v>79227</v>
+        <v>88046</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9585,21 +9597,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9609,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486317</v>
+        <v>486298</v>
       </c>
       <c r="R89" t="n">
-        <v>6829572</v>
+        <v>6829599</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9671,10 +9683,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121468946</v>
+        <v>121468936</v>
       </c>
       <c r="B90" t="n">
-        <v>57509</v>
+        <v>78650</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9687,46 +9699,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486392</v>
+        <v>486335</v>
       </c>
       <c r="R90" t="n">
-        <v>6829119</v>
+        <v>6829435</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469046</v>
+        <v>121469017</v>
       </c>
       <c r="B22" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486324</v>
+        <v>486335</v>
       </c>
       <c r="R22" t="n">
-        <v>6829398</v>
+        <v>6829435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469017</v>
+        <v>121469008</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486335</v>
+        <v>486416</v>
       </c>
       <c r="R23" t="n">
-        <v>6829435</v>
+        <v>6829192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121469008</v>
+        <v>121468975</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486416</v>
+        <v>486298</v>
       </c>
       <c r="R24" t="n">
-        <v>6829192</v>
+        <v>6829621</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468975</v>
+        <v>121469046</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486298</v>
+        <v>486324</v>
       </c>
       <c r="R25" t="n">
-        <v>6829621</v>
+        <v>6829398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469013</v>
+        <v>121469010</v>
       </c>
       <c r="B31" t="n">
         <v>78616</v>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486318</v>
+        <v>486366</v>
       </c>
       <c r="R31" t="n">
-        <v>6829376</v>
+        <v>6829228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469028</v>
+        <v>121469013</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486375</v>
+        <v>486318</v>
       </c>
       <c r="R32" t="n">
-        <v>6829566</v>
+        <v>6829376</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469010</v>
+        <v>121469028</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486366</v>
+        <v>486375</v>
       </c>
       <c r="R33" t="n">
-        <v>6829228</v>
+        <v>6829566</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468966</v>
+        <v>121468915</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486335</v>
+        <v>486223</v>
       </c>
       <c r="R34" t="n">
-        <v>6829590</v>
+        <v>6829705</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468970</v>
+        <v>121469001</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486315</v>
+        <v>486374</v>
       </c>
       <c r="R35" t="n">
-        <v>6829584</v>
+        <v>6829123</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468915</v>
+        <v>121468966</v>
       </c>
       <c r="B36" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486223</v>
+        <v>486335</v>
       </c>
       <c r="R36" t="n">
-        <v>6829705</v>
+        <v>6829590</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469001</v>
+        <v>121468970</v>
       </c>
       <c r="B37" t="n">
         <v>78616</v>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486374</v>
+        <v>486315</v>
       </c>
       <c r="R37" t="n">
-        <v>6829123</v>
+        <v>6829584</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468958</v>
+        <v>121468947</v>
       </c>
       <c r="B43" t="n">
-        <v>80573</v>
+        <v>57510</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,21 +4893,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486278</v>
+        <v>486213</v>
       </c>
       <c r="R43" t="n">
-        <v>6829675</v>
+        <v>6829765</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469009</v>
+        <v>121468958</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>80573</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,21 +4995,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486396</v>
+        <v>486278</v>
       </c>
       <c r="R44" t="n">
-        <v>6829190</v>
+        <v>6829675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468935</v>
+        <v>121469009</v>
       </c>
       <c r="B45" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,21 +5097,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486323</v>
+        <v>486396</v>
       </c>
       <c r="R45" t="n">
-        <v>6829408</v>
+        <v>6829190</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468947</v>
+        <v>121468935</v>
       </c>
       <c r="B46" t="n">
-        <v>57510</v>
+        <v>78650</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,21 +5199,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486213</v>
+        <v>486323</v>
       </c>
       <c r="R46" t="n">
-        <v>6829765</v>
+        <v>6829408</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468991</v>
+        <v>121469036</v>
       </c>
       <c r="B59" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486297</v>
+        <v>486261</v>
       </c>
       <c r="R59" t="n">
-        <v>6829538</v>
+        <v>6829744</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469036</v>
+        <v>121468929</v>
       </c>
       <c r="B60" t="n">
-        <v>78261</v>
+        <v>78650</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486261</v>
+        <v>486309</v>
       </c>
       <c r="R60" t="n">
-        <v>6829744</v>
+        <v>6829581</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468929</v>
+        <v>121469012</v>
       </c>
       <c r="B61" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486309</v>
+        <v>486315</v>
       </c>
       <c r="R61" t="n">
-        <v>6829581</v>
+        <v>6829368</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468919</v>
+        <v>121468978</v>
       </c>
       <c r="B62" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6831,21 +6831,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486341</v>
+        <v>486279</v>
       </c>
       <c r="R62" t="n">
-        <v>6829217</v>
+        <v>6829687</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468921</v>
+        <v>121468991</v>
       </c>
       <c r="B63" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6933,21 +6933,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486365</v>
+        <v>486297</v>
       </c>
       <c r="R63" t="n">
-        <v>6829163</v>
+        <v>6829538</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121469012</v>
+        <v>121468919</v>
       </c>
       <c r="B64" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486315</v>
+        <v>486341</v>
       </c>
       <c r="R64" t="n">
-        <v>6829368</v>
+        <v>6829217</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468978</v>
+        <v>121468921</v>
       </c>
       <c r="B65" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486279</v>
+        <v>486365</v>
       </c>
       <c r="R65" t="n">
-        <v>6829687</v>
+        <v>6829163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8867,7 +8867,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468994</v>
+        <v>121469027</v>
       </c>
       <c r="B82" t="n">
         <v>78616</v>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486261</v>
+        <v>486370</v>
       </c>
       <c r="R82" t="n">
-        <v>6829525</v>
+        <v>6829559</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,7 +8969,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468969</v>
+        <v>121468992</v>
       </c>
       <c r="B83" t="n">
         <v>78616</v>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486317</v>
+        <v>486291</v>
       </c>
       <c r="R83" t="n">
-        <v>6829572</v>
+        <v>6829537</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,7 +9071,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468979</v>
+        <v>121468989</v>
       </c>
       <c r="B84" t="n">
         <v>78616</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486282</v>
+        <v>486302</v>
       </c>
       <c r="R84" t="n">
-        <v>6829704</v>
+        <v>6829539</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469006</v>
+        <v>121468994</v>
       </c>
       <c r="B85" t="n">
         <v>78616</v>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486437</v>
+        <v>486261</v>
       </c>
       <c r="R85" t="n">
-        <v>6829175</v>
+        <v>6829525</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469027</v>
+        <v>121468969</v>
       </c>
       <c r="B86" t="n">
         <v>78616</v>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486370</v>
+        <v>486317</v>
       </c>
       <c r="R86" t="n">
-        <v>6829559</v>
+        <v>6829572</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,7 +9377,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468992</v>
+        <v>121468979</v>
       </c>
       <c r="B87" t="n">
         <v>78616</v>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486291</v>
+        <v>486282</v>
       </c>
       <c r="R87" t="n">
-        <v>6829537</v>
+        <v>6829704</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,7 +9479,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468989</v>
+        <v>121469006</v>
       </c>
       <c r="B88" t="n">
         <v>78616</v>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486302</v>
+        <v>486437</v>
       </c>
       <c r="R88" t="n">
-        <v>6829539</v>
+        <v>6829175</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468938</v>
+        <v>121468917</v>
       </c>
       <c r="B8" t="n">
-        <v>78650</v>
+        <v>79234</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486329</v>
+        <v>486305</v>
       </c>
       <c r="R8" t="n">
-        <v>6829484</v>
+        <v>6829222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468917</v>
+        <v>121468961</v>
       </c>
       <c r="B9" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486305</v>
+        <v>486376</v>
       </c>
       <c r="R9" t="n">
-        <v>6829222</v>
+        <v>6829237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468961</v>
+        <v>121468938</v>
       </c>
       <c r="B10" t="n">
-        <v>78352</v>
+        <v>78650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486376</v>
+        <v>486329</v>
       </c>
       <c r="R10" t="n">
-        <v>6829237</v>
+        <v>6829484</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121469017</v>
+        <v>121469046</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486335</v>
+        <v>486324</v>
       </c>
       <c r="R22" t="n">
-        <v>6829435</v>
+        <v>6829398</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121469008</v>
+        <v>121469017</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486416</v>
+        <v>486335</v>
       </c>
       <c r="R23" t="n">
-        <v>6829192</v>
+        <v>6829435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468975</v>
+        <v>121469008</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486298</v>
+        <v>486416</v>
       </c>
       <c r="R24" t="n">
-        <v>6829621</v>
+        <v>6829192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469046</v>
+        <v>121468975</v>
       </c>
       <c r="B25" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486324</v>
+        <v>486298</v>
       </c>
       <c r="R25" t="n">
-        <v>6829398</v>
+        <v>6829621</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468986</v>
+        <v>121468977</v>
       </c>
       <c r="B52" t="n">
         <v>78616</v>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486259</v>
+        <v>486269</v>
       </c>
       <c r="R52" t="n">
-        <v>6829565</v>
+        <v>6829656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468977</v>
+        <v>121468986</v>
       </c>
       <c r="B53" t="n">
         <v>78616</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486269</v>
+        <v>486259</v>
       </c>
       <c r="R53" t="n">
-        <v>6829656</v>
+        <v>6829565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469036</v>
+        <v>121468991</v>
       </c>
       <c r="B59" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486261</v>
+        <v>486297</v>
       </c>
       <c r="R59" t="n">
-        <v>6829744</v>
+        <v>6829538</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468929</v>
+        <v>121469036</v>
       </c>
       <c r="B60" t="n">
-        <v>78650</v>
+        <v>78261</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486309</v>
+        <v>486261</v>
       </c>
       <c r="R60" t="n">
-        <v>6829581</v>
+        <v>6829744</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469012</v>
+        <v>121468929</v>
       </c>
       <c r="B61" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486315</v>
+        <v>486309</v>
       </c>
       <c r="R61" t="n">
-        <v>6829368</v>
+        <v>6829581</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468978</v>
+        <v>121468919</v>
       </c>
       <c r="B62" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6831,21 +6831,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486279</v>
+        <v>486341</v>
       </c>
       <c r="R62" t="n">
-        <v>6829687</v>
+        <v>6829217</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468991</v>
+        <v>121468921</v>
       </c>
       <c r="B63" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6933,21 +6933,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486297</v>
+        <v>486365</v>
       </c>
       <c r="R63" t="n">
-        <v>6829538</v>
+        <v>6829163</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468919</v>
+        <v>121469012</v>
       </c>
       <c r="B64" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486341</v>
+        <v>486315</v>
       </c>
       <c r="R64" t="n">
-        <v>6829217</v>
+        <v>6829368</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468921</v>
+        <v>121468978</v>
       </c>
       <c r="B65" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486365</v>
+        <v>486279</v>
       </c>
       <c r="R65" t="n">
-        <v>6829163</v>
+        <v>6829687</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121468922</v>
+        <v>121469024</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486376</v>
+        <v>486351</v>
       </c>
       <c r="R2" t="n">
-        <v>6829237</v>
+        <v>6829541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468961</v>
+        <v>121468927</v>
       </c>
       <c r="B3" t="n">
-        <v>78352</v>
+        <v>74722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486376</v>
+        <v>486283</v>
       </c>
       <c r="R3" t="n">
-        <v>6829237</v>
+        <v>6829532</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121469027</v>
+        <v>121468961</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486370</v>
+        <v>486376</v>
       </c>
       <c r="R4" t="n">
-        <v>6829559</v>
+        <v>6829237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468970</v>
+        <v>121469001</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486315</v>
+        <v>486374</v>
       </c>
       <c r="R5" t="n">
-        <v>6829584</v>
+        <v>6829123</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121469005</v>
+        <v>121468993</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486438</v>
+        <v>486272</v>
       </c>
       <c r="R6" t="n">
-        <v>6829156</v>
+        <v>6829527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468986</v>
+        <v>121468975</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486259</v>
+        <v>486298</v>
       </c>
       <c r="R7" t="n">
-        <v>6829565</v>
+        <v>6829621</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121468957</v>
+        <v>121469006</v>
       </c>
       <c r="B8" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,47 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486210</v>
+        <v>486437</v>
       </c>
       <c r="R8" t="n">
-        <v>6829556</v>
+        <v>6829175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,7 +1371,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121468936</v>
+        <v>121469012</v>
       </c>
       <c r="B9" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486335</v>
+        <v>486315</v>
       </c>
       <c r="R9" t="n">
-        <v>6829435</v>
+        <v>6829368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469025</v>
+        <v>121468977</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486353</v>
+        <v>486269</v>
       </c>
       <c r="R10" t="n">
-        <v>6829553</v>
+        <v>6829656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468918</v>
+        <v>121469019</v>
       </c>
       <c r="B11" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486321</v>
+        <v>486309</v>
       </c>
       <c r="R11" t="n">
-        <v>6829248</v>
+        <v>6829468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468937</v>
+        <v>121468970</v>
       </c>
       <c r="B12" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486310</v>
+        <v>486315</v>
       </c>
       <c r="R12" t="n">
-        <v>6829463</v>
+        <v>6829584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121468994</v>
+        <v>121469043</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486261</v>
+        <v>486291</v>
       </c>
       <c r="R13" t="n">
-        <v>6829525</v>
+        <v>6829537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468978</v>
+        <v>121469045</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486279</v>
+        <v>486365</v>
       </c>
       <c r="R14" t="n">
-        <v>6829687</v>
+        <v>6829215</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121469019</v>
+        <v>121468933</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486309</v>
+        <v>486317</v>
       </c>
       <c r="R15" t="n">
-        <v>6829468</v>
+        <v>6829373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468959</v>
+        <v>121468935</v>
       </c>
       <c r="B16" t="n">
-        <v>80573</v>
+        <v>78650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486437</v>
+        <v>486323</v>
       </c>
       <c r="R16" t="n">
-        <v>6829174</v>
+        <v>6829408</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468954</v>
+        <v>121468982</v>
       </c>
       <c r="B17" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,37 +2217,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
@@ -2267,7 +2248,7 @@
         <v>486213</v>
       </c>
       <c r="R17" t="n">
-        <v>6829562</v>
+        <v>6829765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,7 +2289,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2327,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468940</v>
+        <v>121468942</v>
       </c>
       <c r="B18" t="n">
         <v>79205</v>
@@ -2367,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486207</v>
+        <v>486165</v>
       </c>
       <c r="R18" t="n">
-        <v>6829684</v>
+        <v>6829633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468999</v>
+        <v>121468940</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486352</v>
+        <v>486207</v>
       </c>
       <c r="R19" t="n">
-        <v>6829165</v>
+        <v>6829684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121468942</v>
+        <v>121468986</v>
       </c>
       <c r="B20" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486165</v>
+        <v>486259</v>
       </c>
       <c r="R20" t="n">
-        <v>6829633</v>
+        <v>6829565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468955</v>
+        <v>121468937</v>
       </c>
       <c r="B21" t="n">
-        <v>78353</v>
+        <v>78650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486321</v>
+        <v>486310</v>
       </c>
       <c r="R21" t="n">
-        <v>6829248</v>
+        <v>6829463</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468944</v>
+        <v>121468974</v>
       </c>
       <c r="B22" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486255</v>
+        <v>486301</v>
       </c>
       <c r="R22" t="n">
-        <v>6829395</v>
+        <v>6829606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468914</v>
+        <v>121468928</v>
       </c>
       <c r="B23" t="n">
-        <v>79234</v>
+        <v>74722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486317</v>
+        <v>486313</v>
       </c>
       <c r="R23" t="n">
-        <v>6829572</v>
+        <v>6829466</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468971</v>
+        <v>121468954</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,38 +2931,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486309</v>
+        <v>486213</v>
       </c>
       <c r="R24" t="n">
-        <v>6829581</v>
+        <v>6829562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,6 +3012,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3041,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468928</v>
+        <v>121469010</v>
       </c>
       <c r="B25" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486313</v>
+        <v>486366</v>
       </c>
       <c r="R25" t="n">
-        <v>6829466</v>
+        <v>6829228</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468941</v>
+        <v>121469017</v>
       </c>
       <c r="B26" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486174</v>
+        <v>486335</v>
       </c>
       <c r="R26" t="n">
-        <v>6829641</v>
+        <v>6829435</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121468992</v>
+        <v>121469028</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3285,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486291</v>
+        <v>486375</v>
       </c>
       <c r="R27" t="n">
-        <v>6829537</v>
+        <v>6829566</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121468947</v>
+        <v>121469020</v>
       </c>
       <c r="B28" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486213</v>
+        <v>486312</v>
       </c>
       <c r="R28" t="n">
-        <v>6829765</v>
+        <v>6829467</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121469024</v>
+        <v>121468921</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486351</v>
+        <v>486365</v>
       </c>
       <c r="R29" t="n">
-        <v>6829541</v>
+        <v>6829163</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468985</v>
+        <v>121469023</v>
       </c>
       <c r="B30" t="n">
         <v>78616</v>
@@ -3591,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486183</v>
+        <v>486362</v>
       </c>
       <c r="R30" t="n">
-        <v>6829659</v>
+        <v>6829525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468998</v>
+        <v>121468959</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>80573</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486366</v>
+        <v>486437</v>
       </c>
       <c r="R31" t="n">
-        <v>6829176</v>
+        <v>6829174</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121469047</v>
+        <v>121468929</v>
       </c>
       <c r="B32" t="n">
-        <v>77548</v>
+        <v>78650</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486258</v>
+        <v>486309</v>
       </c>
       <c r="R32" t="n">
-        <v>6829343</v>
+        <v>6829581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468921</v>
+        <v>121468978</v>
       </c>
       <c r="B33" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486365</v>
+        <v>486279</v>
       </c>
       <c r="R33" t="n">
-        <v>6829163</v>
+        <v>6829687</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,7 +3949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468938</v>
+        <v>121468932</v>
       </c>
       <c r="B34" t="n">
         <v>78650</v>
@@ -3999,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486329</v>
+        <v>486261</v>
       </c>
       <c r="R34" t="n">
-        <v>6829484</v>
+        <v>6829525</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468975</v>
+        <v>121468931</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,21 +4067,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486298</v>
+        <v>486202</v>
       </c>
       <c r="R35" t="n">
-        <v>6829621</v>
+        <v>6829676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,7 +4153,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468974</v>
+        <v>121469007</v>
       </c>
       <c r="B36" t="n">
         <v>78616</v>
@@ -4203,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486301</v>
+        <v>486432</v>
       </c>
       <c r="R36" t="n">
-        <v>6829606</v>
+        <v>6829183</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,7 +4255,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121469013</v>
+        <v>121468966</v>
       </c>
       <c r="B37" t="n">
         <v>78616</v>
@@ -4305,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486318</v>
+        <v>486335</v>
       </c>
       <c r="R37" t="n">
-        <v>6829376</v>
+        <v>6829590</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,7 +4357,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121469017</v>
+        <v>121468971</v>
       </c>
       <c r="B38" t="n">
         <v>78616</v>
@@ -4407,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486335</v>
+        <v>486309</v>
       </c>
       <c r="R38" t="n">
-        <v>6829435</v>
+        <v>6829581</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,7 +4459,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468966</v>
+        <v>121468989</v>
       </c>
       <c r="B39" t="n">
         <v>78616</v>
@@ -4509,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486335</v>
+        <v>486302</v>
       </c>
       <c r="R39" t="n">
-        <v>6829590</v>
+        <v>6829539</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468968</v>
+        <v>121468943</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486325</v>
+        <v>486250</v>
       </c>
       <c r="R40" t="n">
-        <v>6829578</v>
+        <v>6829400</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,7 +4663,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469001</v>
+        <v>121469004</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -4713,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486374</v>
+        <v>486442</v>
       </c>
       <c r="R41" t="n">
-        <v>6829123</v>
+        <v>6829128</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468932</v>
+        <v>121468983</v>
       </c>
       <c r="B42" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4815,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486261</v>
+        <v>486213</v>
       </c>
       <c r="R42" t="n">
-        <v>6829525</v>
+        <v>6829683</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,7 +4867,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121468969</v>
+        <v>121469009</v>
       </c>
       <c r="B43" t="n">
         <v>78616</v>
@@ -4917,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486317</v>
+        <v>486396</v>
       </c>
       <c r="R43" t="n">
-        <v>6829572</v>
+        <v>6829190</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468958</v>
+        <v>121469025</v>
       </c>
       <c r="B44" t="n">
-        <v>80573</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,21 +4985,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486278</v>
+        <v>486353</v>
       </c>
       <c r="R44" t="n">
-        <v>6829675</v>
+        <v>6829553</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5071,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468919</v>
+        <v>121469036</v>
       </c>
       <c r="B45" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,21 +5087,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5111,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486341</v>
+        <v>486261</v>
       </c>
       <c r="R45" t="n">
-        <v>6829217</v>
+        <v>6829744</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468973</v>
+        <v>121469046</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,21 +5189,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486298</v>
+        <v>486324</v>
       </c>
       <c r="R46" t="n">
-        <v>6829599</v>
+        <v>6829398</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,10 +5275,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121469004</v>
+        <v>121468958</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>80573</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486442</v>
+        <v>486278</v>
       </c>
       <c r="R47" t="n">
-        <v>6829128</v>
+        <v>6829675</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,7 +5377,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468976</v>
+        <v>121468973</v>
       </c>
       <c r="B48" t="n">
         <v>78616</v>
@@ -5427,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486293</v>
+        <v>486298</v>
       </c>
       <c r="R48" t="n">
-        <v>6829631</v>
+        <v>6829599</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,7 +5479,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121469009</v>
+        <v>121468969</v>
       </c>
       <c r="B49" t="n">
         <v>78616</v>
@@ -5529,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486396</v>
+        <v>486317</v>
       </c>
       <c r="R49" t="n">
-        <v>6829190</v>
+        <v>6829572</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469036</v>
+        <v>121469015</v>
       </c>
       <c r="B50" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5597,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5621,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486261</v>
+        <v>486323</v>
       </c>
       <c r="R50" t="n">
-        <v>6829744</v>
+        <v>6829408</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5683,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468946</v>
+        <v>121468991</v>
       </c>
       <c r="B51" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,46 +5699,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486392</v>
+        <v>486297</v>
       </c>
       <c r="R51" t="n">
-        <v>6829119</v>
+        <v>6829538</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5807,10 +5785,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468931</v>
+        <v>121468968</v>
       </c>
       <c r="B52" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5823,21 +5801,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486202</v>
+        <v>486325</v>
       </c>
       <c r="R52" t="n">
-        <v>6829676</v>
+        <v>6829578</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5909,10 +5887,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469012</v>
+        <v>121469035</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5925,21 +5903,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5949,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486315</v>
+        <v>486278</v>
       </c>
       <c r="R53" t="n">
-        <v>6829368</v>
+        <v>6829675</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6011,7 +5989,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468977</v>
+        <v>121468995</v>
       </c>
       <c r="B54" t="n">
         <v>78616</v>
@@ -6051,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486269</v>
+        <v>486256</v>
       </c>
       <c r="R54" t="n">
-        <v>6829656</v>
+        <v>6829523</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6113,7 +6091,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121468989</v>
+        <v>121469013</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6153,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486302</v>
+        <v>486318</v>
       </c>
       <c r="R55" t="n">
-        <v>6829539</v>
+        <v>6829376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6215,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468943</v>
+        <v>121468979</v>
       </c>
       <c r="B56" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6231,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6255,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486250</v>
+        <v>486282</v>
       </c>
       <c r="R56" t="n">
-        <v>6829400</v>
+        <v>6829704</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6317,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469043</v>
+        <v>121469034</v>
       </c>
       <c r="B57" t="n">
-        <v>78261</v>
+        <v>88046</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6333,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>510</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6357,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486291</v>
+        <v>486298</v>
       </c>
       <c r="R57" t="n">
-        <v>6829537</v>
+        <v>6829599</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6419,7 +6397,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469020</v>
+        <v>121469018</v>
       </c>
       <c r="B58" t="n">
         <v>78616</v>
@@ -6459,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486312</v>
+        <v>486306</v>
       </c>
       <c r="R58" t="n">
-        <v>6829467</v>
+        <v>6829450</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6521,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121469018</v>
+        <v>121468947</v>
       </c>
       <c r="B59" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6537,21 +6515,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6561,10 +6539,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486306</v>
+        <v>486213</v>
       </c>
       <c r="R59" t="n">
-        <v>6829450</v>
+        <v>6829765</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6623,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468915</v>
+        <v>121468946</v>
       </c>
       <c r="B60" t="n">
-        <v>79234</v>
+        <v>57510</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6639,34 +6617,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486223</v>
+        <v>486392</v>
       </c>
       <c r="R60" t="n">
-        <v>6829705</v>
+        <v>6829119</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6725,10 +6715,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468933</v>
+        <v>121468939</v>
       </c>
       <c r="B61" t="n">
-        <v>78650</v>
+        <v>79205</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6741,21 +6731,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6765,10 +6755,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486317</v>
+        <v>486265</v>
       </c>
       <c r="R61" t="n">
-        <v>6829373</v>
+        <v>6829735</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6827,10 +6817,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121469046</v>
+        <v>121468934</v>
       </c>
       <c r="B62" t="n">
-        <v>78261</v>
+        <v>78650</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6843,21 +6833,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6867,10 +6857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486324</v>
+        <v>486318</v>
       </c>
       <c r="R62" t="n">
-        <v>6829398</v>
+        <v>6829376</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6929,7 +6919,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468984</v>
+        <v>121468994</v>
       </c>
       <c r="B63" t="n">
         <v>78616</v>
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486202</v>
+        <v>486261</v>
       </c>
       <c r="R63" t="n">
-        <v>6829676</v>
+        <v>6829525</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7031,7 +7021,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468982</v>
+        <v>121468984</v>
       </c>
       <c r="B64" t="n">
         <v>78616</v>
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486213</v>
+        <v>486202</v>
       </c>
       <c r="R64" t="n">
-        <v>6829765</v>
+        <v>6829676</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7133,10 +7123,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468929</v>
+        <v>121469008</v>
       </c>
       <c r="B65" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7149,21 +7139,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7173,10 +7163,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486309</v>
+        <v>486416</v>
       </c>
       <c r="R65" t="n">
-        <v>6829581</v>
+        <v>6829192</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7235,7 +7225,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469008</v>
+        <v>121468967</v>
       </c>
       <c r="B66" t="n">
         <v>78616</v>
@@ -7275,10 +7265,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486416</v>
+        <v>486329</v>
       </c>
       <c r="R66" t="n">
-        <v>6829192</v>
+        <v>6829590</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7337,10 +7327,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468987</v>
+        <v>121468915</v>
       </c>
       <c r="B67" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7353,21 +7343,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7377,10 +7367,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486271</v>
+        <v>486223</v>
       </c>
       <c r="R67" t="n">
-        <v>6829568</v>
+        <v>6829705</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7439,7 +7429,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121469015</v>
+        <v>121468985</v>
       </c>
       <c r="B68" t="n">
         <v>78616</v>
@@ -7479,10 +7469,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486323</v>
+        <v>486183</v>
       </c>
       <c r="R68" t="n">
-        <v>6829408</v>
+        <v>6829659</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7541,7 +7531,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468993</v>
+        <v>121468998</v>
       </c>
       <c r="B69" t="n">
         <v>78616</v>
@@ -7581,10 +7571,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486272</v>
+        <v>486366</v>
       </c>
       <c r="R69" t="n">
-        <v>6829527</v>
+        <v>6829176</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7643,7 +7633,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468991</v>
+        <v>121468996</v>
       </c>
       <c r="B70" t="n">
         <v>78616</v>
@@ -7683,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486297</v>
+        <v>486242</v>
       </c>
       <c r="R70" t="n">
-        <v>6829538</v>
+        <v>6829317</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7745,10 +7735,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468934</v>
+        <v>121468914</v>
       </c>
       <c r="B71" t="n">
-        <v>78650</v>
+        <v>79234</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7761,21 +7751,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7785,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486318</v>
+        <v>486317</v>
       </c>
       <c r="R71" t="n">
-        <v>6829376</v>
+        <v>6829572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7847,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121469035</v>
+        <v>121468944</v>
       </c>
       <c r="B72" t="n">
-        <v>78261</v>
+        <v>79205</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7863,21 +7853,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7887,10 +7877,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486278</v>
+        <v>486255</v>
       </c>
       <c r="R72" t="n">
-        <v>6829675</v>
+        <v>6829395</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7949,10 +7939,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468935</v>
+        <v>121469044</v>
       </c>
       <c r="B73" t="n">
-        <v>78650</v>
+        <v>78261</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7965,21 +7955,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7989,10 +7979,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486323</v>
+        <v>486236</v>
       </c>
       <c r="R73" t="n">
-        <v>6829408</v>
+        <v>6829512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8051,7 +8041,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468917</v>
+        <v>121468922</v>
       </c>
       <c r="B74" t="n">
         <v>79234</v>
@@ -8091,10 +8081,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486305</v>
+        <v>486376</v>
       </c>
       <c r="R74" t="n">
-        <v>6829222</v>
+        <v>6829237</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8153,10 +8143,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469034</v>
+        <v>121469047</v>
       </c>
       <c r="B75" t="n">
-        <v>88046</v>
+        <v>77548</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8169,21 +8159,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>6487</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8193,10 +8183,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486298</v>
+        <v>486258</v>
       </c>
       <c r="R75" t="n">
-        <v>6829599</v>
+        <v>6829343</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8255,10 +8245,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469045</v>
+        <v>121468936</v>
       </c>
       <c r="B76" t="n">
-        <v>78261</v>
+        <v>78650</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8271,21 +8261,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8295,10 +8285,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486365</v>
+        <v>486335</v>
       </c>
       <c r="R76" t="n">
-        <v>6829215</v>
+        <v>6829435</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8357,7 +8347,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468995</v>
+        <v>121468976</v>
       </c>
       <c r="B77" t="n">
         <v>78616</v>
@@ -8397,10 +8387,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486256</v>
+        <v>486293</v>
       </c>
       <c r="R77" t="n">
-        <v>6829523</v>
+        <v>6829631</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8459,7 +8449,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121469010</v>
+        <v>121468999</v>
       </c>
       <c r="B78" t="n">
         <v>78616</v>
@@ -8499,10 +8489,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486366</v>
+        <v>486352</v>
       </c>
       <c r="R78" t="n">
-        <v>6829228</v>
+        <v>6829165</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8561,7 +8551,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468983</v>
+        <v>121469005</v>
       </c>
       <c r="B79" t="n">
         <v>78616</v>
@@ -8601,10 +8591,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486213</v>
+        <v>486438</v>
       </c>
       <c r="R79" t="n">
-        <v>6829683</v>
+        <v>6829156</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8663,10 +8653,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468996</v>
+        <v>121468917</v>
       </c>
       <c r="B80" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8679,21 +8669,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8703,10 +8693,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486242</v>
+        <v>486305</v>
       </c>
       <c r="R80" t="n">
-        <v>6829317</v>
+        <v>6829222</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,7 +8755,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468967</v>
+        <v>121468992</v>
       </c>
       <c r="B81" t="n">
         <v>78616</v>
@@ -8805,10 +8795,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486329</v>
+        <v>486291</v>
       </c>
       <c r="R81" t="n">
-        <v>6829590</v>
+        <v>6829537</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,7 +8857,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468979</v>
+        <v>121468987</v>
       </c>
       <c r="B82" t="n">
         <v>78616</v>
@@ -8907,10 +8897,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486282</v>
+        <v>486271</v>
       </c>
       <c r="R82" t="n">
-        <v>6829704</v>
+        <v>6829568</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,10 +8959,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469044</v>
+        <v>121468938</v>
       </c>
       <c r="B83" t="n">
-        <v>78261</v>
+        <v>78650</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8985,21 +8975,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9009,10 +8999,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486236</v>
+        <v>486329</v>
       </c>
       <c r="R83" t="n">
-        <v>6829512</v>
+        <v>6829484</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,10 +9061,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121469023</v>
+        <v>121468919</v>
       </c>
       <c r="B84" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9087,21 +9077,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9111,10 +9101,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486362</v>
+        <v>486341</v>
       </c>
       <c r="R84" t="n">
-        <v>6829525</v>
+        <v>6829217</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,10 +9163,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469028</v>
+        <v>121468918</v>
       </c>
       <c r="B85" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9189,21 +9179,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9213,10 +9203,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486375</v>
+        <v>486321</v>
       </c>
       <c r="R85" t="n">
-        <v>6829566</v>
+        <v>6829248</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,10 +9265,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469006</v>
+        <v>121468955</v>
       </c>
       <c r="B86" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9291,21 +9281,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9315,10 +9305,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486437</v>
+        <v>486321</v>
       </c>
       <c r="R86" t="n">
-        <v>6829175</v>
+        <v>6829248</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9367,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468927</v>
+        <v>121468941</v>
       </c>
       <c r="B87" t="n">
-        <v>74722</v>
+        <v>79205</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9393,21 +9383,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9417,10 +9407,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486283</v>
+        <v>486174</v>
       </c>
       <c r="R87" t="n">
-        <v>6829532</v>
+        <v>6829641</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,10 +9469,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468939</v>
+        <v>121469021</v>
       </c>
       <c r="B88" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9495,21 +9485,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9519,10 +9509,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486265</v>
+        <v>486328</v>
       </c>
       <c r="R88" t="n">
-        <v>6829735</v>
+        <v>6829486</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,7 +9571,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469007</v>
+        <v>121469027</v>
       </c>
       <c r="B89" t="n">
         <v>78616</v>
@@ -9621,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486432</v>
+        <v>486370</v>
       </c>
       <c r="R89" t="n">
-        <v>6829183</v>
+        <v>6829559</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,10 +9673,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121469021</v>
+        <v>121468957</v>
       </c>
       <c r="B90" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9695,38 +9685,47 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486328</v>
+        <v>486210</v>
       </c>
       <c r="R90" t="n">
-        <v>6829486</v>
+        <v>6829556</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9767,6 +9766,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121469023</v>
+        <v>121468959</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>80573</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486362</v>
+        <v>486437</v>
       </c>
       <c r="R30" t="n">
-        <v>6829525</v>
+        <v>6829174</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468959</v>
+        <v>121468929</v>
       </c>
       <c r="B31" t="n">
-        <v>80573</v>
+        <v>78650</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486437</v>
+        <v>486309</v>
       </c>
       <c r="R31" t="n">
-        <v>6829174</v>
+        <v>6829581</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468929</v>
+        <v>121468978</v>
       </c>
       <c r="B32" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486309</v>
+        <v>486279</v>
       </c>
       <c r="R32" t="n">
-        <v>6829581</v>
+        <v>6829687</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468978</v>
+        <v>121469023</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486279</v>
+        <v>486362</v>
       </c>
       <c r="R33" t="n">
-        <v>6829687</v>
+        <v>6829525</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469025</v>
+        <v>121469036</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486353</v>
+        <v>486261</v>
       </c>
       <c r="R44" t="n">
-        <v>6829553</v>
+        <v>6829744</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469036</v>
+        <v>121469046</v>
       </c>
       <c r="B45" t="n">
         <v>78261</v>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486261</v>
+        <v>486324</v>
       </c>
       <c r="R45" t="n">
-        <v>6829744</v>
+        <v>6829398</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121469046</v>
+        <v>121468958</v>
       </c>
       <c r="B46" t="n">
-        <v>78261</v>
+        <v>80573</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486324</v>
+        <v>486278</v>
       </c>
       <c r="R46" t="n">
-        <v>6829398</v>
+        <v>6829675</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468958</v>
+        <v>121468973</v>
       </c>
       <c r="B47" t="n">
-        <v>80573</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486278</v>
+        <v>486298</v>
       </c>
       <c r="R47" t="n">
-        <v>6829675</v>
+        <v>6829599</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468973</v>
+        <v>121469025</v>
       </c>
       <c r="B48" t="n">
         <v>78616</v>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486298</v>
+        <v>486353</v>
       </c>
       <c r="R48" t="n">
-        <v>6829599</v>
+        <v>6829553</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5989,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468995</v>
+        <v>121469034</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
+        <v>88046</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +6005,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486256</v>
+        <v>486298</v>
       </c>
       <c r="R54" t="n">
-        <v>6829523</v>
+        <v>6829599</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469013</v>
+        <v>121468995</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486318</v>
+        <v>486256</v>
       </c>
       <c r="R55" t="n">
-        <v>6829376</v>
+        <v>6829523</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468979</v>
+        <v>121469013</v>
       </c>
       <c r="B56" t="n">
         <v>78616</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486282</v>
+        <v>486318</v>
       </c>
       <c r="R56" t="n">
-        <v>6829704</v>
+        <v>6829376</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469034</v>
+        <v>121468979</v>
       </c>
       <c r="B57" t="n">
-        <v>88046</v>
+        <v>78616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6311,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486298</v>
+        <v>486282</v>
       </c>
       <c r="R57" t="n">
-        <v>6829599</v>
+        <v>6829704</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7633,10 +7633,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468996</v>
+        <v>121469044</v>
       </c>
       <c r="B70" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7649,21 +7649,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486242</v>
+        <v>486236</v>
       </c>
       <c r="R70" t="n">
-        <v>6829317</v>
+        <v>6829512</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7735,10 +7735,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121468914</v>
+        <v>121469047</v>
       </c>
       <c r="B71" t="n">
-        <v>79234</v>
+        <v>77548</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7751,21 +7751,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486317</v>
+        <v>486258</v>
       </c>
       <c r="R71" t="n">
-        <v>6829572</v>
+        <v>6829343</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7837,10 +7837,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468944</v>
+        <v>121468922</v>
       </c>
       <c r="B72" t="n">
-        <v>79205</v>
+        <v>79234</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7853,21 +7853,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486255</v>
+        <v>486376</v>
       </c>
       <c r="R72" t="n">
-        <v>6829395</v>
+        <v>6829237</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121469044</v>
+        <v>121468996</v>
       </c>
       <c r="B73" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7955,21 +7955,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486236</v>
+        <v>486242</v>
       </c>
       <c r="R73" t="n">
-        <v>6829512</v>
+        <v>6829317</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468922</v>
+        <v>121468914</v>
       </c>
       <c r="B74" t="n">
         <v>79234</v>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486376</v>
+        <v>486317</v>
       </c>
       <c r="R74" t="n">
-        <v>6829237</v>
+        <v>6829572</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8143,10 +8143,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121469047</v>
+        <v>121468944</v>
       </c>
       <c r="B75" t="n">
-        <v>77548</v>
+        <v>79205</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486258</v>
+        <v>486255</v>
       </c>
       <c r="R75" t="n">
-        <v>6829343</v>
+        <v>6829395</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468976</v>
+        <v>121468999</v>
       </c>
       <c r="B77" t="n">
         <v>78616</v>
@@ -8387,10 +8387,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486293</v>
+        <v>486352</v>
       </c>
       <c r="R77" t="n">
-        <v>6829631</v>
+        <v>6829165</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468999</v>
+        <v>121468976</v>
       </c>
       <c r="B78" t="n">
         <v>78616</v>
@@ -8489,10 +8489,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486352</v>
+        <v>486293</v>
       </c>
       <c r="R78" t="n">
-        <v>6829165</v>
+        <v>6829631</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9469,7 +9469,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469021</v>
+        <v>121469027</v>
       </c>
       <c r="B88" t="n">
         <v>78616</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486328</v>
+        <v>486370</v>
       </c>
       <c r="R88" t="n">
-        <v>6829486</v>
+        <v>6829559</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9571,7 +9571,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469027</v>
+        <v>121469021</v>
       </c>
       <c r="B89" t="n">
         <v>78616</v>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486370</v>
+        <v>486328</v>
       </c>
       <c r="R89" t="n">
-        <v>6829559</v>
+        <v>6829486</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121469024</v>
+        <v>121468995</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486351</v>
+        <v>486256</v>
       </c>
       <c r="R2" t="n">
-        <v>6829541</v>
+        <v>6829523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468927</v>
+        <v>121468977</v>
       </c>
       <c r="B3" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486283</v>
+        <v>486269</v>
       </c>
       <c r="R3" t="n">
-        <v>6829532</v>
+        <v>6829656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121468961</v>
+        <v>121469027</v>
       </c>
       <c r="B4" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486376</v>
+        <v>486370</v>
       </c>
       <c r="R4" t="n">
-        <v>6829237</v>
+        <v>6829559</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121469001</v>
+        <v>121468976</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486374</v>
+        <v>486293</v>
       </c>
       <c r="R5" t="n">
-        <v>6829123</v>
+        <v>6829631</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121468993</v>
+        <v>121469025</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486272</v>
+        <v>486353</v>
       </c>
       <c r="R6" t="n">
-        <v>6829527</v>
+        <v>6829553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468975</v>
+        <v>121468933</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486298</v>
+        <v>486317</v>
       </c>
       <c r="R7" t="n">
-        <v>6829621</v>
+        <v>6829373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121469006</v>
+        <v>121469034</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>88046</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486437</v>
+        <v>486298</v>
       </c>
       <c r="R8" t="n">
-        <v>6829175</v>
+        <v>6829599</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469012</v>
+        <v>121469017</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486315</v>
+        <v>486335</v>
       </c>
       <c r="R9" t="n">
-        <v>6829368</v>
+        <v>6829435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121468977</v>
+        <v>121469024</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486269</v>
+        <v>486351</v>
       </c>
       <c r="R10" t="n">
-        <v>6829656</v>
+        <v>6829541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121469019</v>
+        <v>121468929</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>486309</v>
       </c>
       <c r="R11" t="n">
-        <v>6829468</v>
+        <v>6829581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121468970</v>
+        <v>121469013</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486315</v>
+        <v>486318</v>
       </c>
       <c r="R12" t="n">
-        <v>6829584</v>
+        <v>6829376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469043</v>
+        <v>121469005</v>
       </c>
       <c r="B13" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486291</v>
+        <v>486438</v>
       </c>
       <c r="R13" t="n">
-        <v>6829537</v>
+        <v>6829156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121469045</v>
+        <v>121468938</v>
       </c>
       <c r="B14" t="n">
-        <v>78261</v>
+        <v>78650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486365</v>
+        <v>486329</v>
       </c>
       <c r="R14" t="n">
-        <v>6829215</v>
+        <v>6829484</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468933</v>
+        <v>121468940</v>
       </c>
       <c r="B15" t="n">
-        <v>78650</v>
+        <v>79205</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486317</v>
+        <v>486207</v>
       </c>
       <c r="R15" t="n">
-        <v>6829373</v>
+        <v>6829684</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468935</v>
+        <v>121468944</v>
       </c>
       <c r="B16" t="n">
-        <v>78650</v>
+        <v>79205</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486323</v>
+        <v>486255</v>
       </c>
       <c r="R16" t="n">
-        <v>6829408</v>
+        <v>6829395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121468982</v>
+        <v>121469020</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486213</v>
+        <v>486312</v>
       </c>
       <c r="R17" t="n">
-        <v>6829765</v>
+        <v>6829467</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468942</v>
+        <v>121468968</v>
       </c>
       <c r="B18" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486165</v>
+        <v>486325</v>
       </c>
       <c r="R18" t="n">
-        <v>6829633</v>
+        <v>6829578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468940</v>
+        <v>121468946</v>
       </c>
       <c r="B19" t="n">
-        <v>79205</v>
+        <v>57510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,34 +2425,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486207</v>
+        <v>486392</v>
       </c>
       <c r="R19" t="n">
-        <v>6829684</v>
+        <v>6829119</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2523,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121468986</v>
+        <v>121469023</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2551,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486259</v>
+        <v>486362</v>
       </c>
       <c r="R20" t="n">
-        <v>6829565</v>
+        <v>6829525</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121468937</v>
+        <v>121469012</v>
       </c>
       <c r="B21" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486310</v>
+        <v>486315</v>
       </c>
       <c r="R21" t="n">
-        <v>6829463</v>
+        <v>6829368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468974</v>
+        <v>121468984</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -2755,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486301</v>
+        <v>486202</v>
       </c>
       <c r="R22" t="n">
-        <v>6829606</v>
+        <v>6829676</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468928</v>
+        <v>121468917</v>
       </c>
       <c r="B23" t="n">
-        <v>74722</v>
+        <v>79234</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2845,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2869,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486313</v>
+        <v>486305</v>
       </c>
       <c r="R23" t="n">
-        <v>6829466</v>
+        <v>6829222</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2931,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468954</v>
+        <v>121468999</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,47 +2943,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486213</v>
+        <v>486352</v>
       </c>
       <c r="R24" t="n">
-        <v>6829562</v>
+        <v>6829165</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,7 +3015,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3031,7 +3033,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121469010</v>
+        <v>121468975</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3071,10 +3073,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486366</v>
+        <v>486298</v>
       </c>
       <c r="R25" t="n">
-        <v>6829228</v>
+        <v>6829621</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3135,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121469017</v>
+        <v>121468941</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3151,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486335</v>
+        <v>486174</v>
       </c>
       <c r="R26" t="n">
-        <v>6829435</v>
+        <v>6829641</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,7 +3237,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469028</v>
+        <v>121469008</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3275,10 +3277,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486375</v>
+        <v>486416</v>
       </c>
       <c r="R27" t="n">
-        <v>6829566</v>
+        <v>6829192</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,7 +3339,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121469020</v>
+        <v>121468992</v>
       </c>
       <c r="B28" t="n">
         <v>78616</v>
@@ -3377,10 +3379,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486312</v>
+        <v>486291</v>
       </c>
       <c r="R28" t="n">
-        <v>6829467</v>
+        <v>6829537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3441,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121468921</v>
+        <v>121468928</v>
       </c>
       <c r="B29" t="n">
-        <v>79234</v>
+        <v>74722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3457,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3481,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486365</v>
+        <v>486313</v>
       </c>
       <c r="R29" t="n">
-        <v>6829163</v>
+        <v>6829466</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3543,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468959</v>
+        <v>121468914</v>
       </c>
       <c r="B30" t="n">
-        <v>80573</v>
+        <v>79234</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486437</v>
+        <v>486317</v>
       </c>
       <c r="R30" t="n">
-        <v>6829174</v>
+        <v>6829572</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121468929</v>
+        <v>121469021</v>
       </c>
       <c r="B31" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3661,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486309</v>
+        <v>486328</v>
       </c>
       <c r="R31" t="n">
-        <v>6829581</v>
+        <v>6829486</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468978</v>
+        <v>121468998</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -3785,10 +3787,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486279</v>
+        <v>486366</v>
       </c>
       <c r="R32" t="n">
-        <v>6829687</v>
+        <v>6829176</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3849,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121469023</v>
+        <v>121468935</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3865,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3889,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486362</v>
+        <v>486323</v>
       </c>
       <c r="R33" t="n">
-        <v>6829525</v>
+        <v>6829408</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3951,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468932</v>
+        <v>121468978</v>
       </c>
       <c r="B34" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3967,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486261</v>
+        <v>486279</v>
       </c>
       <c r="R34" t="n">
-        <v>6829525</v>
+        <v>6829687</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4053,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121468931</v>
+        <v>121469009</v>
       </c>
       <c r="B35" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,21 +4069,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4093,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486202</v>
+        <v>486396</v>
       </c>
       <c r="R35" t="n">
-        <v>6829676</v>
+        <v>6829190</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4155,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121469007</v>
+        <v>121468958</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>80573</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,21 +4171,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4195,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486432</v>
+        <v>486278</v>
       </c>
       <c r="R36" t="n">
-        <v>6829183</v>
+        <v>6829675</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4257,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121468966</v>
+        <v>121468927</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,21 +4273,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486335</v>
+        <v>486283</v>
       </c>
       <c r="R37" t="n">
-        <v>6829590</v>
+        <v>6829532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,7 +4359,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468971</v>
+        <v>121468966</v>
       </c>
       <c r="B38" t="n">
         <v>78616</v>
@@ -4397,10 +4399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486309</v>
+        <v>486335</v>
       </c>
       <c r="R38" t="n">
-        <v>6829581</v>
+        <v>6829590</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4461,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468989</v>
+        <v>121468961</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4477,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4501,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486302</v>
+        <v>486376</v>
       </c>
       <c r="R39" t="n">
-        <v>6829539</v>
+        <v>6829237</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4563,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468943</v>
+        <v>121468982</v>
       </c>
       <c r="B40" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4579,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4603,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486250</v>
+        <v>486213</v>
       </c>
       <c r="R40" t="n">
-        <v>6829400</v>
+        <v>6829765</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,7 +4665,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121469004</v>
+        <v>121468985</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -4703,10 +4705,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486442</v>
+        <v>486183</v>
       </c>
       <c r="R41" t="n">
-        <v>6829128</v>
+        <v>6829659</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4767,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121468983</v>
+        <v>121469046</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4783,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4807,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486213</v>
+        <v>486324</v>
       </c>
       <c r="R42" t="n">
-        <v>6829683</v>
+        <v>6829398</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4867,10 +4869,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469009</v>
+        <v>121469047</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>77548</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4883,21 +4885,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4909,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486396</v>
+        <v>486258</v>
       </c>
       <c r="R43" t="n">
-        <v>6829190</v>
+        <v>6829343</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,10 +4971,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121469036</v>
+        <v>121468959</v>
       </c>
       <c r="B44" t="n">
-        <v>78261</v>
+        <v>80573</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4985,21 +4987,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5009,10 +5011,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486261</v>
+        <v>486437</v>
       </c>
       <c r="R44" t="n">
-        <v>6829744</v>
+        <v>6829174</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,10 +5073,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121469046</v>
+        <v>121468957</v>
       </c>
       <c r="B45" t="n">
-        <v>78261</v>
+        <v>8436</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5083,38 +5085,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486324</v>
+        <v>486210</v>
       </c>
       <c r="R45" t="n">
-        <v>6829398</v>
+        <v>6829556</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,6 +5166,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5173,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468958</v>
+        <v>121468989</v>
       </c>
       <c r="B46" t="n">
-        <v>80573</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5189,21 +5201,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486278</v>
+        <v>486302</v>
       </c>
       <c r="R46" t="n">
-        <v>6829675</v>
+        <v>6829539</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,10 +5287,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468973</v>
+        <v>121468934</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,21 +5303,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5327,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486298</v>
+        <v>486318</v>
       </c>
       <c r="R47" t="n">
-        <v>6829599</v>
+        <v>6829376</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,10 +5389,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121469025</v>
+        <v>121468936</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5393,21 +5405,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5417,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486353</v>
+        <v>486335</v>
       </c>
       <c r="R48" t="n">
-        <v>6829553</v>
+        <v>6829435</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,7 +5491,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468969</v>
+        <v>121468987</v>
       </c>
       <c r="B49" t="n">
         <v>78616</v>
@@ -5519,10 +5531,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486317</v>
+        <v>486271</v>
       </c>
       <c r="R49" t="n">
-        <v>6829572</v>
+        <v>6829568</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5593,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121469015</v>
+        <v>121468937</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5597,21 +5609,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5621,10 +5633,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486323</v>
+        <v>486310</v>
       </c>
       <c r="R50" t="n">
-        <v>6829408</v>
+        <v>6829463</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,10 +5695,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468991</v>
+        <v>121468932</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5699,21 +5711,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5723,10 +5735,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486297</v>
+        <v>486261</v>
       </c>
       <c r="R51" t="n">
-        <v>6829538</v>
+        <v>6829525</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5785,10 +5797,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121468968</v>
+        <v>121469035</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5801,21 +5813,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5837,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486325</v>
+        <v>486278</v>
       </c>
       <c r="R52" t="n">
-        <v>6829578</v>
+        <v>6829675</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5887,10 +5899,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121469035</v>
+        <v>121468954</v>
       </c>
       <c r="B53" t="n">
-        <v>78261</v>
+        <v>8436</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5899,38 +5911,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486278</v>
+        <v>486213</v>
       </c>
       <c r="R53" t="n">
-        <v>6829675</v>
+        <v>6829562</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5971,6 +5992,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5989,10 +6011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121469034</v>
+        <v>121468993</v>
       </c>
       <c r="B54" t="n">
-        <v>88046</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6005,21 +6027,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6051,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486298</v>
+        <v>486272</v>
       </c>
       <c r="R54" t="n">
-        <v>6829599</v>
+        <v>6829527</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,7 +6113,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121468995</v>
+        <v>121469015</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6131,10 +6153,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486256</v>
+        <v>486323</v>
       </c>
       <c r="R55" t="n">
-        <v>6829523</v>
+        <v>6829408</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,10 +6215,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121469013</v>
+        <v>121468947</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6209,21 +6231,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6233,10 +6255,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486318</v>
+        <v>486213</v>
       </c>
       <c r="R56" t="n">
-        <v>6829376</v>
+        <v>6829765</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,7 +6317,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121468979</v>
+        <v>121469004</v>
       </c>
       <c r="B57" t="n">
         <v>78616</v>
@@ -6335,10 +6357,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486282</v>
+        <v>486442</v>
       </c>
       <c r="R57" t="n">
-        <v>6829704</v>
+        <v>6829128</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6419,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121469018</v>
+        <v>121468919</v>
       </c>
       <c r="B58" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6413,21 +6435,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6437,10 +6459,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486306</v>
+        <v>486341</v>
       </c>
       <c r="R58" t="n">
-        <v>6829450</v>
+        <v>6829217</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6521,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468947</v>
+        <v>121468922</v>
       </c>
       <c r="B59" t="n">
-        <v>57510</v>
+        <v>79234</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6515,21 +6537,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6539,10 +6561,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486213</v>
+        <v>486376</v>
       </c>
       <c r="R59" t="n">
-        <v>6829765</v>
+        <v>6829237</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6623,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121468946</v>
+        <v>121469043</v>
       </c>
       <c r="B60" t="n">
-        <v>57510</v>
+        <v>78261</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,46 +6639,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486392</v>
+        <v>486291</v>
       </c>
       <c r="R60" t="n">
-        <v>6829119</v>
+        <v>6829537</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6715,10 +6725,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121468939</v>
+        <v>121469044</v>
       </c>
       <c r="B61" t="n">
-        <v>79205</v>
+        <v>78261</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6731,21 +6741,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6755,10 +6765,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486265</v>
+        <v>486236</v>
       </c>
       <c r="R61" t="n">
-        <v>6829735</v>
+        <v>6829512</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6817,10 +6827,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468934</v>
+        <v>121468996</v>
       </c>
       <c r="B62" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6833,21 +6843,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6857,10 +6867,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486318</v>
+        <v>486242</v>
       </c>
       <c r="R62" t="n">
-        <v>6829376</v>
+        <v>6829317</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6919,10 +6929,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468994</v>
+        <v>121468918</v>
       </c>
       <c r="B63" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6935,21 +6945,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6959,10 +6969,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486261</v>
+        <v>486321</v>
       </c>
       <c r="R63" t="n">
-        <v>6829525</v>
+        <v>6829248</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7021,7 +7031,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121468984</v>
+        <v>121469006</v>
       </c>
       <c r="B64" t="n">
         <v>78616</v>
@@ -7061,10 +7071,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486202</v>
+        <v>486437</v>
       </c>
       <c r="R64" t="n">
-        <v>6829676</v>
+        <v>6829175</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7123,7 +7133,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121469008</v>
+        <v>121468973</v>
       </c>
       <c r="B65" t="n">
         <v>78616</v>
@@ -7163,10 +7173,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486416</v>
+        <v>486298</v>
       </c>
       <c r="R65" t="n">
-        <v>6829192</v>
+        <v>6829599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7225,7 +7235,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121468967</v>
+        <v>121469010</v>
       </c>
       <c r="B66" t="n">
         <v>78616</v>
@@ -7265,10 +7275,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486329</v>
+        <v>486366</v>
       </c>
       <c r="R66" t="n">
-        <v>6829590</v>
+        <v>6829228</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7327,10 +7337,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468915</v>
+        <v>121468983</v>
       </c>
       <c r="B67" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7343,21 +7353,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7367,10 +7377,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486223</v>
+        <v>486213</v>
       </c>
       <c r="R67" t="n">
-        <v>6829705</v>
+        <v>6829683</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7429,7 +7439,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468985</v>
+        <v>121468969</v>
       </c>
       <c r="B68" t="n">
         <v>78616</v>
@@ -7469,10 +7479,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486183</v>
+        <v>486317</v>
       </c>
       <c r="R68" t="n">
-        <v>6829659</v>
+        <v>6829572</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7531,7 +7541,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468998</v>
+        <v>121468986</v>
       </c>
       <c r="B69" t="n">
         <v>78616</v>
@@ -7571,10 +7581,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486366</v>
+        <v>486259</v>
       </c>
       <c r="R69" t="n">
-        <v>6829176</v>
+        <v>6829565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7633,10 +7643,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121469044</v>
+        <v>121468915</v>
       </c>
       <c r="B70" t="n">
-        <v>78261</v>
+        <v>79234</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7649,21 +7659,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7673,10 +7683,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486236</v>
+        <v>486223</v>
       </c>
       <c r="R70" t="n">
-        <v>6829512</v>
+        <v>6829705</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7735,10 +7745,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469047</v>
+        <v>121469036</v>
       </c>
       <c r="B71" t="n">
-        <v>77548</v>
+        <v>78261</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7751,21 +7761,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7785,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486258</v>
+        <v>486261</v>
       </c>
       <c r="R71" t="n">
-        <v>6829343</v>
+        <v>6829744</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7837,10 +7847,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468922</v>
+        <v>121468943</v>
       </c>
       <c r="B72" t="n">
-        <v>79234</v>
+        <v>79205</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7853,21 +7863,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7877,10 +7887,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486376</v>
+        <v>486250</v>
       </c>
       <c r="R72" t="n">
-        <v>6829237</v>
+        <v>6829400</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7939,10 +7949,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468996</v>
+        <v>121468942</v>
       </c>
       <c r="B73" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7955,21 +7965,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7979,10 +7989,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486242</v>
+        <v>486165</v>
       </c>
       <c r="R73" t="n">
-        <v>6829317</v>
+        <v>6829633</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8041,10 +8051,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468914</v>
+        <v>121468994</v>
       </c>
       <c r="B74" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8057,21 +8067,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8081,10 +8091,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486317</v>
+        <v>486261</v>
       </c>
       <c r="R74" t="n">
-        <v>6829572</v>
+        <v>6829525</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8143,10 +8153,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468944</v>
+        <v>121468967</v>
       </c>
       <c r="B75" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8159,21 +8169,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8183,10 +8193,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486255</v>
+        <v>486329</v>
       </c>
       <c r="R75" t="n">
-        <v>6829395</v>
+        <v>6829590</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8245,10 +8255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121468936</v>
+        <v>121469028</v>
       </c>
       <c r="B76" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8261,21 +8271,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8285,10 +8295,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486335</v>
+        <v>486375</v>
       </c>
       <c r="R76" t="n">
-        <v>6829435</v>
+        <v>6829566</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8347,7 +8357,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121468999</v>
+        <v>121469001</v>
       </c>
       <c r="B77" t="n">
         <v>78616</v>
@@ -8387,10 +8397,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486352</v>
+        <v>486374</v>
       </c>
       <c r="R77" t="n">
-        <v>6829165</v>
+        <v>6829123</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8449,7 +8459,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468976</v>
+        <v>121468991</v>
       </c>
       <c r="B78" t="n">
         <v>78616</v>
@@ -8489,10 +8499,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486293</v>
+        <v>486297</v>
       </c>
       <c r="R78" t="n">
-        <v>6829631</v>
+        <v>6829538</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8551,7 +8561,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121469005</v>
+        <v>121468974</v>
       </c>
       <c r="B79" t="n">
         <v>78616</v>
@@ -8591,10 +8601,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486438</v>
+        <v>486301</v>
       </c>
       <c r="R79" t="n">
-        <v>6829156</v>
+        <v>6829606</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8653,10 +8663,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121468917</v>
+        <v>121469007</v>
       </c>
       <c r="B80" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8669,21 +8679,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8693,10 +8703,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486305</v>
+        <v>486432</v>
       </c>
       <c r="R80" t="n">
-        <v>6829222</v>
+        <v>6829183</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8755,7 +8765,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468992</v>
+        <v>121468970</v>
       </c>
       <c r="B81" t="n">
         <v>78616</v>
@@ -8795,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486291</v>
+        <v>486315</v>
       </c>
       <c r="R81" t="n">
-        <v>6829537</v>
+        <v>6829584</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8857,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468987</v>
+        <v>121468921</v>
       </c>
       <c r="B82" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8873,21 +8883,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8897,10 +8907,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486271</v>
+        <v>486365</v>
       </c>
       <c r="R82" t="n">
-        <v>6829568</v>
+        <v>6829163</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8959,10 +8969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121468938</v>
+        <v>121469045</v>
       </c>
       <c r="B83" t="n">
-        <v>78650</v>
+        <v>78261</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8975,21 +8985,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8999,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486329</v>
+        <v>486365</v>
       </c>
       <c r="R83" t="n">
-        <v>6829484</v>
+        <v>6829215</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9061,10 +9071,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468919</v>
+        <v>121468979</v>
       </c>
       <c r="B84" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9077,21 +9087,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9101,10 +9111,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486341</v>
+        <v>486282</v>
       </c>
       <c r="R84" t="n">
-        <v>6829217</v>
+        <v>6829704</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9163,10 +9173,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121468918</v>
+        <v>121469018</v>
       </c>
       <c r="B85" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9179,21 +9189,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9203,10 +9213,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486321</v>
+        <v>486306</v>
       </c>
       <c r="R85" t="n">
-        <v>6829248</v>
+        <v>6829450</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9265,10 +9275,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121468955</v>
+        <v>121469019</v>
       </c>
       <c r="B86" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9281,21 +9291,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9305,10 +9315,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486321</v>
+        <v>486309</v>
       </c>
       <c r="R86" t="n">
-        <v>6829248</v>
+        <v>6829468</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9367,10 +9377,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468941</v>
+        <v>121468955</v>
       </c>
       <c r="B87" t="n">
-        <v>79205</v>
+        <v>78353</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9383,21 +9393,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9407,10 +9417,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486174</v>
+        <v>486321</v>
       </c>
       <c r="R87" t="n">
-        <v>6829641</v>
+        <v>6829248</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9469,7 +9479,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121469027</v>
+        <v>121468971</v>
       </c>
       <c r="B88" t="n">
         <v>78616</v>
@@ -9509,10 +9519,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486370</v>
+        <v>486309</v>
       </c>
       <c r="R88" t="n">
-        <v>6829559</v>
+        <v>6829581</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9571,10 +9581,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121469021</v>
+        <v>121468931</v>
       </c>
       <c r="B89" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9587,21 +9597,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9611,10 +9621,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486328</v>
+        <v>486202</v>
       </c>
       <c r="R89" t="n">
-        <v>6829486</v>
+        <v>6829676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9673,10 +9683,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121468957</v>
+        <v>121468939</v>
       </c>
       <c r="B90" t="n">
-        <v>8436</v>
+        <v>79205</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9685,47 +9695,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486210</v>
+        <v>486265</v>
       </c>
       <c r="R90" t="n">
-        <v>6829556</v>
+        <v>6829735</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9766,7 +9767,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121468995</v>
+        <v>121468929</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486256</v>
+        <v>486309</v>
       </c>
       <c r="R2" t="n">
-        <v>6829523</v>
+        <v>6829581</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121468977</v>
+        <v>121468930</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486269</v>
+        <v>486215</v>
       </c>
       <c r="R3" t="n">
-        <v>6829656</v>
+        <v>6829764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121469027</v>
+        <v>121468931</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486370</v>
+        <v>486202</v>
       </c>
       <c r="R4" t="n">
-        <v>6829559</v>
+        <v>6829676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121468976</v>
+        <v>121468932</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486293</v>
+        <v>486261</v>
       </c>
       <c r="R5" t="n">
-        <v>6829631</v>
+        <v>6829525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121469025</v>
+        <v>121468933</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486353</v>
+        <v>486317</v>
       </c>
       <c r="R6" t="n">
-        <v>6829553</v>
+        <v>6829373</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121468933</v>
+        <v>121468934</v>
       </c>
       <c r="B7" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486317</v>
+        <v>486318</v>
       </c>
       <c r="R7" t="n">
-        <v>6829373</v>
+        <v>6829376</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121469034</v>
+        <v>121468935</v>
       </c>
       <c r="B8" t="n">
-        <v>88046</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486298</v>
+        <v>486323</v>
       </c>
       <c r="R8" t="n">
-        <v>6829599</v>
+        <v>6829408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121469017</v>
+        <v>121468936</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121469024</v>
+        <v>121468937</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486351</v>
+        <v>486310</v>
       </c>
       <c r="R10" t="n">
-        <v>6829541</v>
+        <v>6829463</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121468929</v>
+        <v>121468938</v>
       </c>
       <c r="B11" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486309</v>
+        <v>486329</v>
       </c>
       <c r="R11" t="n">
-        <v>6829581</v>
+        <v>6829484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121469013</v>
+        <v>121469035</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486318</v>
+        <v>486278</v>
       </c>
       <c r="R12" t="n">
-        <v>6829376</v>
+        <v>6829675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121469005</v>
+        <v>121469036</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486438</v>
+        <v>486261</v>
       </c>
       <c r="R13" t="n">
-        <v>6829156</v>
+        <v>6829744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121468938</v>
+        <v>121469037</v>
       </c>
       <c r="B14" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486329</v>
+        <v>486190</v>
       </c>
       <c r="R14" t="n">
-        <v>6829484</v>
+        <v>6829582</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121468940</v>
+        <v>121469038</v>
       </c>
       <c r="B15" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486207</v>
+        <v>486197</v>
       </c>
       <c r="R15" t="n">
-        <v>6829684</v>
+        <v>6829581</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121468944</v>
+        <v>121469040</v>
       </c>
       <c r="B16" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486255</v>
+        <v>486193</v>
       </c>
       <c r="R16" t="n">
-        <v>6829395</v>
+        <v>6829576</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121469020</v>
+        <v>121469041</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486312</v>
+        <v>486275</v>
       </c>
       <c r="R17" t="n">
-        <v>6829467</v>
+        <v>6829559</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121468968</v>
+        <v>121469043</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486325</v>
+        <v>486291</v>
       </c>
       <c r="R18" t="n">
-        <v>6829578</v>
+        <v>6829537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121468946</v>
+        <v>121469044</v>
       </c>
       <c r="B19" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,46 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486392</v>
+        <v>486236</v>
       </c>
       <c r="R19" t="n">
-        <v>6829119</v>
+        <v>6829512</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121469023</v>
+        <v>121469045</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486362</v>
+        <v>486365</v>
       </c>
       <c r="R20" t="n">
-        <v>6829525</v>
+        <v>6829215</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121469012</v>
+        <v>121469046</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486315</v>
+        <v>486324</v>
       </c>
       <c r="R21" t="n">
-        <v>6829368</v>
+        <v>6829398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121468984</v>
+        <v>121469034</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2743,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2767,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486202</v>
+        <v>486298</v>
       </c>
       <c r="R22" t="n">
-        <v>6829676</v>
+        <v>6829599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121468917</v>
+        <v>121468958</v>
       </c>
       <c r="B23" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2869,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486305</v>
+        <v>486278</v>
       </c>
       <c r="R23" t="n">
-        <v>6829222</v>
+        <v>6829675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121468999</v>
+        <v>121468959</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2971,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486352</v>
+        <v>486437</v>
       </c>
       <c r="R24" t="n">
-        <v>6829165</v>
+        <v>6829174</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121468975</v>
+        <v>121468948</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3073,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486298</v>
+        <v>486376</v>
       </c>
       <c r="R25" t="n">
-        <v>6829621</v>
+        <v>6829579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3135,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121468941</v>
+        <v>121468964</v>
       </c>
       <c r="B26" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3175,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486174</v>
+        <v>486359</v>
       </c>
       <c r="R26" t="n">
-        <v>6829641</v>
+        <v>6829595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3237,19 +3100,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121469008</v>
+        <v>121468965</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3277,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486416</v>
+        <v>486347</v>
       </c>
       <c r="R27" t="n">
-        <v>6829192</v>
+        <v>6829602</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3339,19 +3197,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121468992</v>
+        <v>121468966</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3379,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486291</v>
+        <v>486335</v>
       </c>
       <c r="R28" t="n">
-        <v>6829537</v>
+        <v>6829590</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,37 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121468928</v>
+        <v>121468967</v>
       </c>
       <c r="B29" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3481,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486313</v>
+        <v>486329</v>
       </c>
       <c r="R29" t="n">
-        <v>6829466</v>
+        <v>6829590</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,37 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121468914</v>
+        <v>121468968</v>
       </c>
       <c r="B30" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486317</v>
+        <v>486325</v>
       </c>
       <c r="R30" t="n">
-        <v>6829572</v>
+        <v>6829578</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,19 +3488,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121469021</v>
+        <v>121468969</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3685,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486328</v>
+        <v>486317</v>
       </c>
       <c r="R31" t="n">
-        <v>6829486</v>
+        <v>6829572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,19 +3585,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121468998</v>
+        <v>121468970</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3787,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486366</v>
+        <v>486315</v>
       </c>
       <c r="R32" t="n">
-        <v>6829176</v>
+        <v>6829584</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3849,37 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121468935</v>
+        <v>121468971</v>
       </c>
       <c r="B33" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3889,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486323</v>
+        <v>486309</v>
       </c>
       <c r="R33" t="n">
-        <v>6829408</v>
+        <v>6829581</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3951,19 +3779,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121468978</v>
+        <v>121468973</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3991,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486279</v>
+        <v>486298</v>
       </c>
       <c r="R34" t="n">
-        <v>6829687</v>
+        <v>6829599</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,19 +3876,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121469009</v>
+        <v>121468974</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4093,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486396</v>
+        <v>486301</v>
       </c>
       <c r="R35" t="n">
-        <v>6829190</v>
+        <v>6829606</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,37 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121468958</v>
+        <v>121468975</v>
       </c>
       <c r="B36" t="n">
-        <v>80573</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4195,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486278</v>
+        <v>486298</v>
       </c>
       <c r="R36" t="n">
-        <v>6829675</v>
+        <v>6829621</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4257,37 +4070,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121468927</v>
+        <v>121468976</v>
       </c>
       <c r="B37" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486283</v>
+        <v>486293</v>
       </c>
       <c r="R37" t="n">
-        <v>6829532</v>
+        <v>6829631</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4359,19 +4167,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121468966</v>
+        <v>121468977</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4399,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486335</v>
+        <v>486269</v>
       </c>
       <c r="R38" t="n">
-        <v>6829590</v>
+        <v>6829656</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4461,37 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121468961</v>
+        <v>121468978</v>
       </c>
       <c r="B39" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4501,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486376</v>
+        <v>486279</v>
       </c>
       <c r="R39" t="n">
-        <v>6829237</v>
+        <v>6829687</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,19 +4361,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121468982</v>
+        <v>121468979</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4603,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486213</v>
+        <v>486282</v>
       </c>
       <c r="R40" t="n">
-        <v>6829765</v>
+        <v>6829704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4665,19 +4458,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121468985</v>
+        <v>121468980</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4705,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486183</v>
+        <v>486225</v>
       </c>
       <c r="R41" t="n">
-        <v>6829659</v>
+        <v>6829781</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4767,37 +4555,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121469046</v>
+        <v>121468981</v>
       </c>
       <c r="B42" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4807,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486324</v>
+        <v>486225</v>
       </c>
       <c r="R42" t="n">
-        <v>6829398</v>
+        <v>6829778</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4869,37 +4652,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121469047</v>
+        <v>121468982</v>
       </c>
       <c r="B43" t="n">
-        <v>77548</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4909,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486258</v>
+        <v>486213</v>
       </c>
       <c r="R43" t="n">
-        <v>6829343</v>
+        <v>6829765</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,37 +4749,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121468959</v>
+        <v>121468983</v>
       </c>
       <c r="B44" t="n">
-        <v>80573</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5011,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486437</v>
+        <v>486213</v>
       </c>
       <c r="R44" t="n">
-        <v>6829174</v>
+        <v>6829683</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5073,59 +4846,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121468957</v>
+        <v>121468984</v>
       </c>
       <c r="B45" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486210</v>
+        <v>486202</v>
       </c>
       <c r="R45" t="n">
-        <v>6829556</v>
+        <v>6829676</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5166,7 +4925,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5185,19 +4943,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121468989</v>
+        <v>121468985</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5225,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486302</v>
+        <v>486183</v>
       </c>
       <c r="R46" t="n">
-        <v>6829539</v>
+        <v>6829659</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,37 +5040,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121468934</v>
+        <v>121468986</v>
       </c>
       <c r="B47" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5327,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486318</v>
+        <v>486259</v>
       </c>
       <c r="R47" t="n">
-        <v>6829376</v>
+        <v>6829565</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,37 +5137,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121468936</v>
+        <v>121468987</v>
       </c>
       <c r="B48" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486335</v>
+        <v>486271</v>
       </c>
       <c r="R48" t="n">
-        <v>6829435</v>
+        <v>6829568</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,19 +5234,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121468987</v>
+        <v>121468988</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5531,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486271</v>
+        <v>486286</v>
       </c>
       <c r="R49" t="n">
-        <v>6829568</v>
+        <v>6829555</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5593,37 +5331,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121468937</v>
+        <v>121468989</v>
       </c>
       <c r="B50" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5633,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486310</v>
+        <v>486302</v>
       </c>
       <c r="R50" t="n">
-        <v>6829463</v>
+        <v>6829539</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,37 +5428,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121468932</v>
+        <v>121468991</v>
       </c>
       <c r="B51" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5735,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486261</v>
+        <v>486297</v>
       </c>
       <c r="R51" t="n">
-        <v>6829525</v>
+        <v>6829538</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5797,37 +5525,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121469035</v>
+        <v>121468992</v>
       </c>
       <c r="B52" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5837,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486278</v>
+        <v>486291</v>
       </c>
       <c r="R52" t="n">
-        <v>6829675</v>
+        <v>6829537</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5899,59 +5622,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121468954</v>
+        <v>121468993</v>
       </c>
       <c r="B53" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pilkalampinoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486213</v>
+        <v>486272</v>
       </c>
       <c r="R53" t="n">
-        <v>6829562</v>
+        <v>6829527</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5992,7 +5701,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6011,19 +5719,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121468993</v>
+        <v>121468994</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6051,10 +5754,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486272</v>
+        <v>486261</v>
       </c>
       <c r="R54" t="n">
-        <v>6829527</v>
+        <v>6829525</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6113,19 +5816,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121469015</v>
+        <v>121468995</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6153,10 +5851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486323</v>
+        <v>486256</v>
       </c>
       <c r="R55" t="n">
-        <v>6829408</v>
+        <v>6829523</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6215,37 +5913,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121468947</v>
+        <v>121468996</v>
       </c>
       <c r="B56" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6255,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486213</v>
+        <v>486242</v>
       </c>
       <c r="R56" t="n">
-        <v>6829765</v>
+        <v>6829317</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6317,19 +6010,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121469004</v>
+        <v>121468997</v>
       </c>
       <c r="B57" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6357,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486442</v>
+        <v>486218</v>
       </c>
       <c r="R57" t="n">
-        <v>6829128</v>
+        <v>6829277</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6419,37 +6107,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121468919</v>
+        <v>121468998</v>
       </c>
       <c r="B58" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6459,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486341</v>
+        <v>486366</v>
       </c>
       <c r="R58" t="n">
-        <v>6829217</v>
+        <v>6829176</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6521,37 +6204,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121468922</v>
+        <v>121468999</v>
       </c>
       <c r="B59" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6561,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486376</v>
+        <v>486352</v>
       </c>
       <c r="R59" t="n">
-        <v>6829237</v>
+        <v>6829165</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6623,37 +6301,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121469043</v>
+        <v>121469001</v>
       </c>
       <c r="B60" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6663,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486291</v>
+        <v>486374</v>
       </c>
       <c r="R60" t="n">
-        <v>6829537</v>
+        <v>6829123</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6725,37 +6398,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121469044</v>
+        <v>121469003</v>
       </c>
       <c r="B61" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6765,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486236</v>
+        <v>486405</v>
       </c>
       <c r="R61" t="n">
-        <v>6829512</v>
+        <v>6829113</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6827,19 +6495,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121468996</v>
+        <v>121469004</v>
       </c>
       <c r="B62" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6867,10 +6530,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486242</v>
+        <v>486442</v>
       </c>
       <c r="R62" t="n">
-        <v>6829317</v>
+        <v>6829128</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6929,37 +6592,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121468918</v>
+        <v>121469005</v>
       </c>
       <c r="B63" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6969,10 +6627,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486321</v>
+        <v>486438</v>
       </c>
       <c r="R63" t="n">
-        <v>6829248</v>
+        <v>6829156</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,16 +6692,11 @@
         <v>121469006</v>
       </c>
       <c r="B64" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7133,19 +6786,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121468973</v>
+        <v>121469007</v>
       </c>
       <c r="B65" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7173,10 +6821,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486298</v>
+        <v>486432</v>
       </c>
       <c r="R65" t="n">
-        <v>6829599</v>
+        <v>6829183</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7235,19 +6883,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121469010</v>
+        <v>121469008</v>
       </c>
       <c r="B66" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7275,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486366</v>
+        <v>486416</v>
       </c>
       <c r="R66" t="n">
-        <v>6829228</v>
+        <v>6829192</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7337,19 +6980,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121468983</v>
+        <v>121469009</v>
       </c>
       <c r="B67" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7377,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486213</v>
+        <v>486396</v>
       </c>
       <c r="R67" t="n">
-        <v>6829683</v>
+        <v>6829190</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7439,19 +7077,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121468969</v>
+        <v>121469010</v>
       </c>
       <c r="B68" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7479,10 +7112,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486317</v>
+        <v>486366</v>
       </c>
       <c r="R68" t="n">
-        <v>6829572</v>
+        <v>6829228</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7541,19 +7174,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121468986</v>
+        <v>121469011</v>
       </c>
       <c r="B69" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7581,10 +7209,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486259</v>
+        <v>486368</v>
       </c>
       <c r="R69" t="n">
-        <v>6829565</v>
+        <v>6829265</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7643,37 +7271,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121468915</v>
+        <v>121469012</v>
       </c>
       <c r="B70" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7683,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486223</v>
+        <v>486315</v>
       </c>
       <c r="R70" t="n">
-        <v>6829705</v>
+        <v>6829368</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7745,37 +7368,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121469036</v>
+        <v>121469013</v>
       </c>
       <c r="B71" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7785,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486261</v>
+        <v>486318</v>
       </c>
       <c r="R71" t="n">
-        <v>6829744</v>
+        <v>6829376</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7847,37 +7465,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121468943</v>
+        <v>121469014</v>
       </c>
       <c r="B72" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7887,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486250</v>
+        <v>486320</v>
       </c>
       <c r="R72" t="n">
-        <v>6829400</v>
+        <v>6829385</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7949,37 +7562,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121468942</v>
+        <v>121469015</v>
       </c>
       <c r="B73" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7989,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486165</v>
+        <v>486323</v>
       </c>
       <c r="R73" t="n">
-        <v>6829633</v>
+        <v>6829408</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8051,19 +7659,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121468994</v>
+        <v>121469016</v>
       </c>
       <c r="B74" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -8091,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486261</v>
+        <v>486356</v>
       </c>
       <c r="R74" t="n">
-        <v>6829525</v>
+        <v>6829433</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8153,19 +7756,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121468967</v>
+        <v>121469017</v>
       </c>
       <c r="B75" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -8193,10 +7791,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486329</v>
+        <v>486335</v>
       </c>
       <c r="R75" t="n">
-        <v>6829590</v>
+        <v>6829435</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8255,19 +7853,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121469028</v>
+        <v>121469018</v>
       </c>
       <c r="B76" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8295,10 +7888,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486375</v>
+        <v>486306</v>
       </c>
       <c r="R76" t="n">
-        <v>6829566</v>
+        <v>6829450</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8357,19 +7950,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121469001</v>
+        <v>121469019</v>
       </c>
       <c r="B77" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8397,10 +7985,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486374</v>
+        <v>486309</v>
       </c>
       <c r="R77" t="n">
-        <v>6829123</v>
+        <v>6829468</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8459,19 +8047,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121468991</v>
+        <v>121469020</v>
       </c>
       <c r="B78" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8499,10 +8082,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486297</v>
+        <v>486312</v>
       </c>
       <c r="R78" t="n">
-        <v>6829538</v>
+        <v>6829467</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8561,19 +8144,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121468974</v>
+        <v>121469021</v>
       </c>
       <c r="B79" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -8601,10 +8179,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486301</v>
+        <v>486328</v>
       </c>
       <c r="R79" t="n">
-        <v>6829606</v>
+        <v>6829486</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8663,19 +8241,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121469007</v>
+        <v>121469022</v>
       </c>
       <c r="B80" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -8703,10 +8276,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486432</v>
+        <v>486371</v>
       </c>
       <c r="R80" t="n">
-        <v>6829183</v>
+        <v>6829512</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8765,19 +8338,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121468970</v>
+        <v>121469023</v>
       </c>
       <c r="B81" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -8805,10 +8373,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486315</v>
+        <v>486362</v>
       </c>
       <c r="R81" t="n">
-        <v>6829584</v>
+        <v>6829525</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8867,37 +8435,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121468921</v>
+        <v>121469024</v>
       </c>
       <c r="B82" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8907,10 +8470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486365</v>
+        <v>486351</v>
       </c>
       <c r="R82" t="n">
-        <v>6829163</v>
+        <v>6829541</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,37 +8532,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121469045</v>
+        <v>121469025</v>
       </c>
       <c r="B83" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9009,10 +8567,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486365</v>
+        <v>486353</v>
       </c>
       <c r="R83" t="n">
-        <v>6829215</v>
+        <v>6829553</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9071,19 +8629,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121468979</v>
+        <v>121469027</v>
       </c>
       <c r="B84" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -9111,10 +8664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486282</v>
+        <v>486370</v>
       </c>
       <c r="R84" t="n">
-        <v>6829704</v>
+        <v>6829559</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9173,19 +8726,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121469018</v>
+        <v>121469028</v>
       </c>
       <c r="B85" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -9213,10 +8761,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486306</v>
+        <v>486375</v>
       </c>
       <c r="R85" t="n">
-        <v>6829450</v>
+        <v>6829566</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,19 +8823,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121469019</v>
+        <v>121469029</v>
       </c>
       <c r="B86" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -9315,10 +8858,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486309</v>
+        <v>486375</v>
       </c>
       <c r="R86" t="n">
-        <v>6829468</v>
+        <v>6829574</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,37 +8920,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121468955</v>
+        <v>121469030</v>
       </c>
       <c r="B87" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9417,10 +8955,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486321</v>
+        <v>486377</v>
       </c>
       <c r="R87" t="n">
-        <v>6829248</v>
+        <v>6829575</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9479,19 +9017,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121468971</v>
+        <v>121469031</v>
       </c>
       <c r="B88" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -9519,10 +9052,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486309</v>
+        <v>486380</v>
       </c>
       <c r="R88" t="n">
-        <v>6829581</v>
+        <v>6829576</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,37 +9114,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121468931</v>
+        <v>121469032</v>
       </c>
       <c r="B89" t="n">
-        <v>78650</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9621,10 +9149,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486202</v>
+        <v>486385</v>
       </c>
       <c r="R89" t="n">
-        <v>6829676</v>
+        <v>6829580</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9683,15 +9211,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121468939</v>
+        <v>121469048</v>
       </c>
       <c r="B90" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9699,21 +9222,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9723,10 +9246,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486265</v>
+        <v>486196</v>
       </c>
       <c r="R90" t="n">
-        <v>6829735</v>
+        <v>6829671</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9782,6 +9305,3045 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>121468927</v>
+      </c>
+      <c r="B91" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>486283</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6829532</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>121468928</v>
+      </c>
+      <c r="B92" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>486313</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6829466</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121468960</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>486286</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6829552</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>121468961</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>486376</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6829237</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>121468953</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>486283</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6829550</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>121468914</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>486317</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6829572</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>121468915</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>486223</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6829705</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>121468916</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>486286</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6829550</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>121468917</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>486305</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6829222</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>121468918</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>486321</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6829248</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>121468919</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>486341</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6829217</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>121468920</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>486353</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6829187</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>121468921</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>486365</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6829163</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>121468922</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>486376</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6829237</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>121468923</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>486345</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6829273</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>121468924</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>486335</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6829270</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>121468925</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>486277</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6829312</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>121468926</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>486364</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6829530</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>121469047</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>486258</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6829343</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>121468946</v>
+      </c>
+      <c r="B110" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>486392</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6829119</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>121468947</v>
+      </c>
+      <c r="B111" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>486213</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6829765</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>121468954</v>
+      </c>
+      <c r="B112" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>486213</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6829562</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>121468957</v>
+      </c>
+      <c r="B113" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>486210</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6829556</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>121468955</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>486321</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6829248</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>121468956</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>486340</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6829217</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>121468939</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>486265</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6829735</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>121468940</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>486207</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6829684</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>121468941</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>486174</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6829641</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>121468942</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>486165</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6829633</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>121468943</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>486250</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6829400</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>121468944</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Pilkalampinoppi, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>486255</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6829395</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28754-2024 artfynd.xlsx
+++ b/artfynd/A 28754-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AZ121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468930</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468931</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468932</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468933</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468934</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468935</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468936</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468937</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468938</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469035</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469036</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469037</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469038</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469040</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469041</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469043</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469044</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469045</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469046</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469034</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468958</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468959</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468948</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468964</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468965</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468966</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468967</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468968</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468969</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468970</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468971</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468973</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468974</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468975</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468976</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468977</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468978</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468979</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468980</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468981</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468982</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468983</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468984</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468985</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468986</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468987</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468988</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468989</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468991</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468992</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468993</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468994</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468995</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468996</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468997</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6201,6 +6486,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468998</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6298,6 +6588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468999</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6395,6 +6690,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469001</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6492,6 +6792,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469003</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6589,6 +6894,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469004</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6686,6 +6996,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469005</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6783,6 +7098,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469006</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6880,6 +7200,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469007</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6977,6 +7302,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469008</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7074,6 +7404,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469009</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7171,6 +7506,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469010</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7268,6 +7608,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469011</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7365,6 +7710,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469012</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7462,6 +7812,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469013</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7559,6 +7914,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469014</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7656,6 +8016,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469015</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7753,6 +8118,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469016</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7850,6 +8220,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469017</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7947,6 +8322,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469018</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8044,6 +8424,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469019</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8141,6 +8526,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469020</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8238,6 +8628,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469021</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8335,6 +8730,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469022</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8432,6 +8832,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469023</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8529,6 +8934,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469024</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8626,6 +9036,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8723,6 +9138,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469027</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8820,6 +9240,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469028</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8917,6 +9342,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469029</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9014,6 +9444,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469030</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9111,6 +9546,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469031</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9208,6 +9648,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469032</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9305,6 +9750,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469048</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9402,6 +9852,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468927</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9499,6 +9954,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468928</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9596,6 +10056,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468960</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9693,6 +10158,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468961</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9790,6 +10260,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468953</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9887,6 +10362,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468914</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9984,6 +10464,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468915</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10081,6 +10566,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468916</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10178,6 +10668,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468917</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10275,6 +10770,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468918</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10372,6 +10872,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468919</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10469,6 +10974,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468920</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10566,6 +11076,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468921</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10663,6 +11178,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468922</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10760,6 +11280,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468923</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10857,6 +11382,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468924</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10954,6 +11484,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468925</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11051,6 +11586,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468926</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11148,6 +11688,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121469047</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11257,6 +11802,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468946</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11354,6 +11904,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468947</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11461,6 +12016,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468954</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11568,6 +12128,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468957</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11665,6 +12230,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468955</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11762,6 +12332,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468956</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11859,6 +12434,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468939</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11956,6 +12536,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468940</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12053,6 +12638,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468941</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12150,6 +12740,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468942</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12247,6 +12842,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468943</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12344,8 +12944,135 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121468944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>